--- a/exports/歷史文物守護行動_完整題庫.xlsx
+++ b/exports/歷史文物守護行動_完整題庫.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="題庫總覽" sheetId="1" r:id="Rbb9085d4eeaf48aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整題庫" sheetId="2" r:id="R8aa83f79475b4eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="題庫總覽" sheetId="1" r:id="Re872daa535f94804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整題庫" sheetId="2" r:id="R14d1751a0f024675"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -972,7 +972,7 @@
         <x:v>所有候鳥只能沿陸地移動</x:v>
       </x:c>
       <x:c r="L5" s="34" t="str">
-        <x:v>臺灣因面積最大才成為停留點</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="M5" s="34" t="str">
         <x:v>A</x:v>
@@ -996,7 +996,7 @@
         <x:v>選項和題意關係較弱。提示：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="T5" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先看路線連到哪些地區。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="U5" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1014,10 +1014,10 @@
         <x:v>先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="Z5" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AA5" s="34" t="str">
-        <x:v>核對單位、時間、尺度與原始數值</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="AB5" s="34" t="str">
         <x:v>A</x:v>
@@ -1026,10 +1026,10 @@
         <x:v>這是判斷「位置與交流」時要使用的依據。南北相連的路線直接呈現臺灣的相對位置；氣候、移動方式與面積都不是這筆資料能證明的原因。</x:v>
       </x:c>
       <x:c r="AD5" s="34" t="str">
-        <x:v>這是「文化多樣性」的重點；本題要判斷的是「位置與交流」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境與生活」的重點；本題要判斷的是「位置與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE5" s="34" t="str">
-        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「位置與交流」判斷。</x:v>
+        <x:v>這項知識屬於「結論界線」，無法支持本題的「位置與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF5" s="34" t="str">
         <x:v>用區域地圖說明臺灣為何是候鳥驛站。</x:v>
@@ -1064,13 +1064,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J6" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="K6" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="L6" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="M6" s="34" t="str">
         <x:v>A</x:v>
@@ -1088,13 +1088,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住位置與交流的關鍵條件。</x:v>
       </x:c>
       <x:c r="R6" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：先看路線連到哪些地區。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="S6" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先看路線連到哪些地區。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="T6" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先看路線連到哪些地區。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="U6" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1115,7 +1115,7 @@
         <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="AA6" s="34" t="str">
-        <x:v>外力暴露治理不足，促使政策改變</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AB6" s="34" t="str">
         <x:v>A</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>這是「航海動機」的重點；本題要判斷的是「位置與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE6" s="34" t="str">
-        <x:v>這項知識屬於「牡丹社事件」，無法支持本題的「位置與交流」判斷。</x:v>
+        <x:v>這項知識屬於「能源分類」，無法支持本題的「位置與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF6" s="34" t="str">
         <x:v>用區域地圖說明臺灣為何是候鳥驛站。</x:v>
@@ -1162,13 +1162,13 @@
         <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="J7" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="K7" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="L7" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="M7" s="34" t="str">
         <x:v>A</x:v>
@@ -1186,13 +1186,13 @@
         <x:v>證據吻合。選項「臺灣是遷徙與交流的中繼點」能把位置與交流的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R7" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先看路線連到哪些地區。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="S7" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先看路線連到哪些地區。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="T7" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先看路線連到哪些地區。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「位置與交流」。請回看：先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="U7" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1210,10 +1210,10 @@
         <x:v>先看路線連到哪些地區。</x:v>
       </x:c>
       <x:c r="Z7" s="34" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AA7" s="34" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AB7" s="34" t="str">
         <x:v>A</x:v>
@@ -1222,10 +1222,10 @@
         <x:v>這是判斷「位置與交流」時要使用的依據。南北相連的路線直接呈現臺灣的相對位置；氣候、移動方式與面積都不是這筆資料能證明的原因。</x:v>
       </x:c>
       <x:c r="AD7" s="34" t="str">
-        <x:v>這是「遷移原因」的重點；本題要判斷的是「位置與交流」，兩者不能互相代替。</x:v>
+        <x:v>這是「開港背景」的重點；本題要判斷的是「位置與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE7" s="34" t="str">
-        <x:v>這項知識屬於「循環經濟」，無法支持本題的「位置與交流」判斷。</x:v>
+        <x:v>這項知識屬於「分析權衡」，無法支持本題的「位置與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF7" s="34" t="str">
         <x:v>用區域地圖說明臺灣為何是候鳥驛站。</x:v>
@@ -1266,7 +1266,7 @@
         <x:v>只畫教室座位的平面圖</x:v>
       </x:c>
       <x:c r="L8" s="34" t="str">
-        <x:v>只列山峰高度的統計表</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="M8" s="34" t="str">
         <x:v>A</x:v>
@@ -1290,7 +1290,7 @@
         <x:v>這裡混淆了條件與結論。提示：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="T8" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="U8" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1311,7 +1311,7 @@
         <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AA8" s="34" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AB8" s="34" t="str">
         <x:v>A</x:v>
@@ -1323,7 +1323,7 @@
         <x:v>這是「永續漁業」的重點；本題要判斷的是「地圖尺度」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE8" s="34" t="str">
-        <x:v>這項知識屬於「港市與文化」，無法支持本題的「地圖尺度」判斷。</x:v>
+        <x:v>這項知識屬於「開港背景」，無法支持本題的「地圖尺度」判斷。</x:v>
       </x:c>
       <x:c r="AF8" s="34" t="str">
         <x:v>旅行時依問題切換世界、區域與城市地圖。</x:v>
@@ -1358,13 +1358,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J9" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="K9" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="L9" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="M9" s="34" t="str">
         <x:v>A</x:v>
@@ -1382,13 +1382,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把地圖尺度的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R9" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="S9" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="T9" s="34" t="str">
-        <x:v>焦點放錯了。請回看：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="U9" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="AA9" s="34" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB9" s="34" t="str">
         <x:v>A</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>這是「結論界線」的重點；本題要判斷的是「地圖尺度」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE9" s="34" t="str">
-        <x:v>這項知識屬於「消費安全」，無法支持本題的「地圖尺度」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「地圖尺度」判斷。</x:v>
       </x:c>
       <x:c r="AF9" s="34" t="str">
         <x:v>旅行時依問題切換世界、區域與城市地圖。</x:v>
@@ -1456,13 +1456,13 @@
         <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="J10" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="K10" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="L10" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="M10" s="34" t="str">
         <x:v>A</x:v>
@@ -1480,13 +1480,13 @@
         <x:v>答對了；「選能看見臺灣、鄰國與航線的區域圖」同時保留了地圖尺度需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R10" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="S10" s="34" t="str">
-        <x:v>焦點放錯了。請回看：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="T10" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：地圖不是越細越好，要看研究範圍。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「地圖尺度」。請回看：地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="U10" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1504,10 +1504,10 @@
         <x:v>地圖不是越細越好，要看研究範圍。</x:v>
       </x:c>
       <x:c r="Z10" s="34" t="str">
-        <x:v>海防受重視，建省與建設強化治理</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AA10" s="34" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AB10" s="34" t="str">
         <x:v>A</x:v>
@@ -1516,10 +1516,10 @@
         <x:v>這是判斷「地圖尺度」時要使用的依據。地圖尺度要配合問題；相對位置研究需要同時看見臺灣、鄰國和航線。</x:v>
       </x:c>
       <x:c r="AD10" s="34" t="str">
-        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「地圖尺度」，兩者不能互相代替。</x:v>
+        <x:v>這是「地理配對」的重點；本題要判斷的是「地圖尺度」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE10" s="34" t="str">
-        <x:v>這項知識屬於「環境與生活」，無法支持本題的「地圖尺度」判斷。</x:v>
+        <x:v>這項知識屬於「權利權衡」，無法支持本題的「地圖尺度」判斷。</x:v>
       </x:c>
       <x:c r="AF10" s="34" t="str">
         <x:v>旅行時依問題切換世界、區域與城市地圖。</x:v>
@@ -1560,7 +1560,7 @@
         <x:v>人口集中在西部把山擠高</x:v>
       </x:c>
       <x:c r="L11" s="34" t="str">
-        <x:v>四周海水每天把中央山脈推高</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="M11" s="34" t="str">
         <x:v>A</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>這項判斷忽略重要限制。請想想：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="T11" s="34" t="str">
-        <x:v>焦點放錯了。請回看：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="U11" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1605,7 +1605,7 @@
         <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AA11" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AB11" s="34" t="str">
         <x:v>A</x:v>
@@ -1617,7 +1617,7 @@
         <x:v>這是「貿易影響」的重點；本題要判斷的是「板塊與地形」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE11" s="34" t="str">
-        <x:v>這項知識屬於「能源分類」，無法支持本題的「板塊與地形」判斷。</x:v>
+        <x:v>這項知識屬於「地理配對」，無法支持本題的「板塊與地形」判斷。</x:v>
       </x:c>
       <x:c r="AF11" s="34" t="str">
         <x:v>遇到地震新聞時，用板塊位置解釋風險。</x:v>
@@ -1652,13 +1652,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J12" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="K12" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="L12" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="M12" s="34" t="str">
         <x:v>A</x:v>
@@ -1676,13 +1676,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了板塊與地形需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R12" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="S12" s="34" t="str">
-        <x:v>焦點放錯了。請回看：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="T12" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="U12" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1703,7 +1703,7 @@
         <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AA12" s="34" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AB12" s="34" t="str">
         <x:v>A</x:v>
@@ -1715,7 +1715,7 @@
         <x:v>這是「開港背景」的重點；本題要判斷的是「板塊與地形」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE12" s="34" t="str">
-        <x:v>這項知識屬於「分析權衡」，無法支持本題的「板塊與地形」判斷。</x:v>
+        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「板塊與地形」判斷。</x:v>
       </x:c>
       <x:c r="AF12" s="34" t="str">
         <x:v>遇到地震新聞時，用板塊位置解釋風險。</x:v>
@@ -1750,13 +1750,13 @@
         <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="J13" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="K13" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="L13" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="M13" s="34" t="str">
         <x:v>A</x:v>
@@ -1774,13 +1774,13 @@
         <x:v>你的判讀可被查證：板塊交界造成多山與地震。這正是板塊與地形要比較的核心。</x:v>
       </x:c>
       <x:c r="R13" s="34" t="str">
-        <x:v>焦點放錯了。請回看：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="S13" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="T13" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：找能一次解釋兩個現象的地質條件。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「板塊與地形」。請回看：找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="U13" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1798,10 +1798,10 @@
         <x:v>找能一次解釋兩個現象的地質條件。</x:v>
       </x:c>
       <x:c r="Z13" s="34" t="str">
-        <x:v>保存證據，再循正式管道申訴</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AA13" s="34" t="str">
-        <x:v>查明進口木材是否來自永續來源</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="AB13" s="34" t="str">
         <x:v>A</x:v>
@@ -1810,10 +1810,10 @@
         <x:v>這是判斷「板塊與地形」時要使用的依據。板塊互相作用能同時解釋造山和地震；緯線、人口與潮汐無法建立這組因果。</x:v>
       </x:c>
       <x:c r="AD13" s="34" t="str">
-        <x:v>這是「消費權益」的重點；本題要判斷的是「板塊與地形」，兩者不能互相代替。</x:v>
+        <x:v>這是「循環經濟」的重點；本題要判斷的是「板塊與地形」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE13" s="34" t="str">
-        <x:v>這項知識屬於「森林供應鏈」，無法支持本題的「板塊與地形」判斷。</x:v>
+        <x:v>這項知識屬於「航海動機」，無法支持本題的「板塊與地形」判斷。</x:v>
       </x:c>
       <x:c r="AF13" s="34" t="str">
         <x:v>遇到地震新聞時，用板塊位置解釋風險。</x:v>
@@ -1854,7 +1854,7 @@
         <x:v>只選照片顏色較漂亮的一處</x:v>
       </x:c>
       <x:c r="L14" s="34" t="str">
-        <x:v>認定所有海岸都應建相同港口</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="M14" s="34" t="str">
         <x:v>A</x:v>
@@ -1878,7 +1878,7 @@
         <x:v>焦點放錯了。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="T14" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="U14" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1899,7 +1899,7 @@
         <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AA14" s="34" t="str">
-        <x:v>訂規則、維修配置與歸還責任</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AB14" s="34" t="str">
         <x:v>A</x:v>
@@ -1911,7 +1911,7 @@
         <x:v>這是「水利開墾」的重點；本題要判斷的是「海岸變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE14" s="34" t="str">
-        <x:v>這項知識屬於「共享資源」，無法支持本題的「海岸變遷」判斷。</x:v>
+        <x:v>這項知識屬於「循環經濟」，無法支持本題的「海岸變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF14" s="34" t="str">
         <x:v>開發海岸前，同時評估港口、養殖與保育需求。</x:v>
@@ -1946,13 +1946,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J15" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="K15" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="L15" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="M15" s="34" t="str">
         <x:v>A</x:v>
@@ -1970,13 +1970,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是海岸變遷要比較的核心。</x:v>
       </x:c>
       <x:c r="R15" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="S15" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="T15" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="U15" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -1994,10 +1994,10 @@
         <x:v>把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="Z15" s="34" t="str">
-        <x:v>依地理條件發展能源並評估影響</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AA15" s="34" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AB15" s="34" t="str">
         <x:v>A</x:v>
@@ -2006,10 +2006,10 @@
         <x:v>這是判斷「海岸變遷」時要使用的依據。海岸利用受形狀、風浪與泥沙共同影響，人口或美感不能代替環境證據。</x:v>
       </x:c>
       <x:c r="AD15" s="34" t="str">
-        <x:v>這是「地理配對」的重點；本題要判斷的是「海岸變遷」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費安全」的重點；本題要判斷的是「海岸變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE15" s="34" t="str">
-        <x:v>這項知識屬於「權利權衡」，無法支持本題的「海岸變遷」判斷。</x:v>
+        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「海岸變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF15" s="34" t="str">
         <x:v>開發海岸前，同時評估港口、養殖與保育需求。</x:v>
@@ -2044,13 +2044,13 @@
         <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="J16" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="K16" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="L16" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="M16" s="34" t="str">
         <x:v>A</x:v>
@@ -2068,13 +2068,13 @@
         <x:v>判斷精準。「比較地形、風浪、泥沙與停靠條件」直接回應海岸變遷，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R16" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="S16" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="T16" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把船舶需要的條件和海岸特性對照。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「海岸變遷」。請回看：把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="U16" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -2092,10 +2092,10 @@
         <x:v>把船舶需要的條件和海岸特性對照。</x:v>
       </x:c>
       <x:c r="Z16" s="34" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AA16" s="34" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="AB16" s="34" t="str">
         <x:v>A</x:v>
@@ -2104,10 +2104,10 @@
         <x:v>這是判斷「海岸變遷」時要使用的依據。海岸利用受形狀、風浪與泥沙共同影響，人口或美感不能代替環境證據。</x:v>
       </x:c>
       <x:c r="AD16" s="34" t="str">
-        <x:v>這是「共識與程序」的重點；本題要判斷的是「海岸變遷」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境與生活」的重點；本題要判斷的是「海岸變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE16" s="34" t="str">
-        <x:v>這項知識屬於「問題形成」，無法支持本題的「海岸變遷」判斷。</x:v>
+        <x:v>這項知識屬於「結論界線」，無法支持本題的「海岸變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF16" s="34" t="str">
         <x:v>開發海岸前，同時評估港口、養殖與保育需求。</x:v>
@@ -2148,7 +2148,7 @@
         <x:v>居民只吃稻米，從不採集狩獵</x:v>
       </x:c>
       <x:c r="L17" s="34" t="str">
-        <x:v>器物能證明遺址是昨天形成</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="M17" s="34" t="str">
         <x:v>A</x:v>
@@ -2172,7 +2172,7 @@
         <x:v>這項推論缺少證據。請確認：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="T17" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="U17" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -2193,7 +2193,7 @@
         <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="AA17" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AB17" s="34" t="str">
         <x:v>A</x:v>
@@ -2205,7 +2205,7 @@
         <x:v>這是「牡丹社事件」的重點；本題要判斷的是「史前證據」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE17" s="34" t="str">
-        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「史前證據」判斷。</x:v>
+        <x:v>這項知識屬於「環境與生活」，無法支持本題的「史前證據」判斷。</x:v>
       </x:c>
       <x:c r="AF17" s="34" t="str">
         <x:v>參觀遺址時，區分證據支持的可能與猜測。</x:v>
@@ -2240,13 +2240,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J18" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="K18" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="L18" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="M18" s="34" t="str">
         <x:v>A</x:v>
@@ -2264,13 +2264,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應史前證據，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R18" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="S18" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="T18" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="U18" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -2288,10 +2288,10 @@
         <x:v>把三種遺物放在一起判斷，不要過度肯定。</x:v>
       </x:c>
       <x:c r="Z18" s="34" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AA18" s="34" t="str">
-        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB18" s="34" t="str">
         <x:v>A</x:v>
@@ -2300,10 +2300,10 @@
         <x:v>這是判斷「史前證據」時要使用的依據。工具、容器與作物遺留可共同支持農耕和定居的可能，但不能推到文字、單一飲食或精確日期。</x:v>
       </x:c>
       <x:c r="AD18" s="34" t="str">
-        <x:v>這是「循環經濟」的重點；本題要判斷的是「史前證據」，兩者不能互相代替。</x:v>
+        <x:v>這是「分析權衡」的重點；本題要判斷的是「史前證據」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE18" s="34" t="str">
-        <x:v>這項知識屬於「航海動機」，無法支持本題的「史前證據」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「史前證據」判斷。</x:v>
       </x:c>
       <x:c r="AF18" s="34" t="str">
         <x:v>參觀遺址時，區分證據支持的可能與猜測。</x:v>
@@ -2338,13 +2338,13 @@
         <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="J19" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="K19" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="L19" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="M19" s="34" t="str">
         <x:v>A</x:v>
@@ -2362,13 +2362,13 @@
         <x:v>這項選擇成立：遺物顯示可能已有農耕定居生活。它抓住史前證據的關鍵條件。</x:v>
       </x:c>
       <x:c r="R19" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="S19" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="T19" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把三種遺物放在一起推論，不要過度肯定。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「史前證據」。請回看：把三種遺物放在一起推論，不要過度肯定。</x:v>
       </x:c>
       <x:c r="U19" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -2386,10 +2386,10 @@
         <x:v>把三種遺物放在一起判斷，不要過度肯定。</x:v>
       </x:c>
       <x:c r="Z19" s="34" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AA19" s="34" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AB19" s="34" t="str">
         <x:v>A</x:v>
@@ -2398,10 +2398,10 @@
         <x:v>這是判斷「史前證據」時要使用的依據。工具、容器與作物遺留可共同支持農耕和定居的可能，但不能推到文字、單一飲食或精確日期。</x:v>
       </x:c>
       <x:c r="AD19" s="34" t="str">
-        <x:v>這是「永續農業」的重點；本題要判斷的是「史前證據」，兩者不能互相代替。</x:v>
+        <x:v>這是「森林供應鏈」的重點；本題要判斷的是「史前證據」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE19" s="34" t="str">
-        <x:v>這項知識屬於「遷移原因」，無法支持本題的「史前證據」判斷。</x:v>
+        <x:v>這項知識屬於「開港背景」，無法支持本題的「史前證據」判斷。</x:v>
       </x:c>
       <x:c r="AF19" s="34" t="str">
         <x:v>參觀遺址時，區分證據支持的可能與猜測。</x:v>
@@ -2442,7 +2442,7 @@
         <x:v>只整理觀光廣告的共同印象</x:v>
       </x:c>
       <x:c r="L20" s="35" t="str">
-        <x:v>依居住縣市直接猜測文化</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="M20" s="35" t="str">
         <x:v>A</x:v>
@@ -2466,7 +2466,7 @@
         <x:v>選項和題意關係較弱。提示：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="T20" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="U20" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2487,7 +2487,7 @@
         <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="AA20" s="35" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AB20" s="35" t="str">
         <x:v>A</x:v>
@@ -2499,7 +2499,7 @@
         <x:v>這是「多元觀點」的重點；本題要判斷的是「文化多樣性」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE20" s="35" t="str">
-        <x:v>這項知識屬於「電力與生活」，無法支持本題的「文化多樣性」判斷。</x:v>
+        <x:v>這項知識屬於「能源分類」，無法支持本題的「文化多樣性」判斷。</x:v>
       </x:c>
       <x:c r="AF20" s="35" t="str">
         <x:v>文化海報要標族名與資料來源。</x:v>
@@ -2534,13 +2534,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J21" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="K21" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="L21" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="M21" s="35" t="str">
         <x:v>A</x:v>
@@ -2558,13 +2558,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住文化多樣性的關鍵條件。</x:v>
       </x:c>
       <x:c r="R21" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="S21" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="T21" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="U21" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2585,7 +2585,7 @@
         <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AA21" s="35" t="str">
-        <x:v>訪談多方並搭配噪音與發電資料</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="AB21" s="35" t="str">
         <x:v>A</x:v>
@@ -2597,7 +2597,7 @@
         <x:v>這是「港市與文化」的重點；本題要判斷的是「文化多樣性」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE21" s="35" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「文化多樣性」判斷。</x:v>
+        <x:v>這項知識屬於「行動評估」，無法支持本題的「文化多樣性」判斷。</x:v>
       </x:c>
       <x:c r="AF21" s="35" t="str">
         <x:v>文化海報要標族名與資料來源。</x:v>
@@ -2632,13 +2632,13 @@
         <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="J22" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="K22" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="L22" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="M22" s="35" t="str">
         <x:v>A</x:v>
@@ -2656,13 +2656,13 @@
         <x:v>證據吻合。選項「分族查資料，再比較文化異同」能把文化多樣性的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R22" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="S22" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="T22" s="35" t="str">
-        <x:v>焦點放錯了。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「文化多樣性」。請回看：確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="U22" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2680,10 +2680,10 @@
         <x:v>確認資料談的是哪一族、由誰陳述。</x:v>
       </x:c>
       <x:c r="Z22" s="35" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AA22" s="35" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AB22" s="35" t="str">
         <x:v>A</x:v>
@@ -2692,10 +2692,10 @@
         <x:v>這是判斷「文化多樣性」時要使用的依據。文化和環境、歷史及自我認同有關，應讓各族群資料被清楚區分，避免刻板化。</x:v>
       </x:c>
       <x:c r="AD22" s="35" t="str">
-        <x:v>這是「消費安全」的重點；本題要判斷的是「文化多樣性」，兩者不能互相代替。</x:v>
+        <x:v>這是「共享資源」的重點；本題要判斷的是「文化多樣性」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE22" s="35" t="str">
-        <x:v>這項知識屬於「永續漁業」，無法支持本題的「文化多樣性」判斷。</x:v>
+        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「文化多樣性」判斷。</x:v>
       </x:c>
       <x:c r="AF22" s="35" t="str">
         <x:v>文化海報要標族名與資料來源。</x:v>
@@ -2736,7 +2736,7 @@
         <x:v>住山區就一定不和外界交流</x:v>
       </x:c>
       <x:c r="L23" s="35" t="str">
-        <x:v>傳統生活方式永遠不會改變</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="M23" s="35" t="str">
         <x:v>A</x:v>
@@ -2760,7 +2760,7 @@
         <x:v>這裡混淆了條件與結論。提示：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="T23" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：不要只用自然或個人單一原因。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="U23" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2781,7 +2781,7 @@
         <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="AA23" s="35" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB23" s="35" t="str">
         <x:v>A</x:v>
@@ -2793,7 +2793,7 @@
         <x:v>這是「移民與季風」的重點；本題要判斷的是「環境與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE23" s="35" t="str">
-        <x:v>這項知識屬於「理財風險」，無法支持本題的「環境與生活」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「環境與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF23" s="35" t="str">
         <x:v>比較地方飲食時，也追查食材環境與交流史。</x:v>
@@ -2828,13 +2828,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J24" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="K24" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="L24" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="M24" s="35" t="str">
         <x:v>A</x:v>
@@ -2852,13 +2852,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把環境與生活的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R24" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：不要只用自然或個人單一原因。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="S24" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：不要只用自然或個人單一原因。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="T24" s="35" t="str">
-        <x:v>焦點放錯了。請回看：不要只用自然或個人單一原因。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="U24" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2876,10 +2876,10 @@
         <x:v>不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="Z24" s="35" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="AA24" s="35" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AB24" s="35" t="str">
         <x:v>A</x:v>
@@ -2888,10 +2888,10 @@
         <x:v>這是判斷「環境與生活」時要使用的依據。自然環境提供條件，人群仍會依文化與歷史作選擇，且文化會延續也會調整。</x:v>
       </x:c>
       <x:c r="AD24" s="35" t="str">
-        <x:v>這是「能源分類」的重點；本題要判斷的是「環境與生活」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境正義」的重點；本題要判斷的是「環境與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE24" s="35" t="str">
-        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「環境與生活」判斷。</x:v>
+        <x:v>這項知識屬於「地方轉型」，無法支持本題的「環境與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF24" s="35" t="str">
         <x:v>比較地方飲食時，也追查食材環境與交流史。</x:v>
@@ -2926,13 +2926,13 @@
         <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="J25" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="K25" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="L25" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="M25" s="35" t="str">
         <x:v>A</x:v>
@@ -2950,13 +2950,13 @@
         <x:v>答對了；「環境、季節與歷史共同影響生活」同時保留了環境與生活需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R25" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：不要只用自然或個人單一原因。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="S25" s="35" t="str">
-        <x:v>焦點放錯了。請回看：不要只用自然或個人單一原因。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="T25" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：不要只用自然或個人單一原因。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「環境與生活」。請回看：不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="U25" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -2974,10 +2974,10 @@
         <x:v>不要只用自然或個人單一原因。</x:v>
       </x:c>
       <x:c r="Z25" s="35" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AA25" s="35" t="str">
-        <x:v>貿易增加，也改變土地與族群關係</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB25" s="35" t="str">
         <x:v>A</x:v>
@@ -2986,10 +2986,10 @@
         <x:v>這是判斷「環境與生活」時要使用的依據。自然環境提供條件，人群仍會依文化與歷史作選擇，且文化會延續也會調整。</x:v>
       </x:c>
       <x:c r="AD25" s="35" t="str">
-        <x:v>這是「分析權衡」的重點；本題要判斷的是「環境與生活」，兩者不能互相代替。</x:v>
+        <x:v>這是「位置與交流」的重點；本題要判斷的是「環境與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE25" s="35" t="str">
-        <x:v>這項知識屬於「貿易影響」，無法支持本題的「環境與生活」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「環境與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF25" s="35" t="str">
         <x:v>比較地方飲食時，也追查食材環境與交流史。</x:v>
@@ -3030,7 +3030,7 @@
         <x:v>有禮貌就完全不需要法律</x:v>
       </x:c>
       <x:c r="L26" s="35" t="str">
-        <x:v>法律的目的只是讓大家想法相同</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="M26" s="35" t="str">
         <x:v>A</x:v>
@@ -3054,7 +3054,7 @@
         <x:v>這項判斷忽略重要限制。請想想：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="T26" s="35" t="str">
-        <x:v>焦點放錯了。請回看：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="U26" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3075,7 +3075,7 @@
         <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="AA26" s="35" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AB26" s="35" t="str">
         <x:v>A</x:v>
@@ -3087,7 +3087,7 @@
         <x:v>這是「人物與交流」的重點；本題要判斷的是「規範與法律」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE26" s="35" t="str">
-        <x:v>這項知識屬於「行動評估」，無法支持本題的「規範與法律」判斷。</x:v>
+        <x:v>這項知識屬於「位置與交流」，無法支持本題的「規範與法律」判斷。</x:v>
       </x:c>
       <x:c r="AF26" s="35" t="str">
         <x:v>訂班規時說明目的，也標出涉及法律的界線。</x:v>
@@ -3122,13 +3122,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J27" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="K27" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="L27" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="M27" s="35" t="str">
         <x:v>A</x:v>
@@ -3146,13 +3146,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了規範與法律需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R27" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="S27" s="35" t="str">
-        <x:v>焦點放錯了。請回看：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="T27" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="U27" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3170,10 +3170,10 @@
         <x:v>比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="Z27" s="35" t="str">
-        <x:v>訂規則、維修配置與歸還責任</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AA27" s="35" t="str">
-        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AB27" s="35" t="str">
         <x:v>A</x:v>
@@ -3182,10 +3182,10 @@
         <x:v>這是判斷「規範與法律」時要使用的依據。生活規範常靠習慣與團體約定；涉及公共安全和權利時，法律提供強制標準與救濟。</x:v>
       </x:c>
       <x:c r="AD27" s="35" t="str">
-        <x:v>這是「共享資源」的重點；本題要判斷的是「規範與法律」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元觀點」的重點；本題要判斷的是「規範與法律」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE27" s="35" t="str">
-        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「規範與法律」判斷。</x:v>
+        <x:v>這項知識屬於「多元資料」，無法支持本題的「規範與法律」判斷。</x:v>
       </x:c>
       <x:c r="AF27" s="35" t="str">
         <x:v>訂班規時說明目的，也標出涉及法律的界線。</x:v>
@@ -3220,13 +3220,13 @@
         <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="J28" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="K28" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="L28" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="M28" s="35" t="str">
         <x:v>A</x:v>
@@ -3244,13 +3244,13 @@
         <x:v>你的判讀可被查證：規範與法律的形成及強制力不同。這正是規範與法律要比較的核心。</x:v>
       </x:c>
       <x:c r="R28" s="35" t="str">
-        <x:v>焦點放錯了。請回看：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="S28" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="T28" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：比較由誰制定、如何執行、保護誰。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「規範與法律」。請回看：比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="U28" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3268,10 +3268,10 @@
         <x:v>比較由誰制定、如何執行、保護誰。</x:v>
       </x:c>
       <x:c r="Z28" s="35" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AA28" s="35" t="str">
-        <x:v>合作修水圳，訂分水與維修規則</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AB28" s="35" t="str">
         <x:v>A</x:v>
@@ -3280,10 +3280,10 @@
         <x:v>這是判斷「規範與法律」時要使用的依據。生活規範常靠習慣與團體約定；涉及公共安全和權利時，法律提供強制標準與救濟。</x:v>
       </x:c>
       <x:c r="AD28" s="35" t="str">
-        <x:v>這是「史前證據」的重點；本題要判斷的是「規範與法律」，兩者不能互相代替。</x:v>
+        <x:v>這是「永續漁業」的重點；本題要判斷的是「規範與法律」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE28" s="35" t="str">
-        <x:v>這項知識屬於「水利開墾」，無法支持本題的「規範與法律」判斷。</x:v>
+        <x:v>這項知識屬於「港市與文化」，無法支持本題的「規範與法律」判斷。</x:v>
       </x:c>
       <x:c r="AF28" s="35" t="str">
         <x:v>訂班規時說明目的，也標出涉及法律的界線。</x:v>
@@ -3324,7 +3324,7 @@
         <x:v>只要有人反對就應立刻取消</x:v>
       </x:c>
       <x:c r="L29" s="35" t="str">
-        <x:v>標示改變表示不再需要禮讓</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="M29" s="35" t="str">
         <x:v>A</x:v>
@@ -3348,7 +3348,7 @@
         <x:v>焦點放錯了。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="T29" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：把規範的目的和形式分開看。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="U29" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3369,7 +3369,7 @@
         <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="AA29" s="35" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AB29" s="35" t="str">
         <x:v>A</x:v>
@@ -3381,7 +3381,7 @@
         <x:v>這是「環境正義」的重點；本題要判斷的是「規範變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE29" s="35" t="str">
-        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「規範變遷」判斷。</x:v>
+        <x:v>這項知識屬於「永續漁業」，無法支持本題的「規範變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF29" s="35" t="str">
         <x:v>遇到新規定時，比較改前改後處理的問題。</x:v>
@@ -3416,13 +3416,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J30" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="K30" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="L30" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="M30" s="35" t="str">
         <x:v>A</x:v>
@@ -3440,13 +3440,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是規範變遷要比較的核心。</x:v>
       </x:c>
       <x:c r="R30" s="35" t="str">
-        <x:v>焦點放錯了。請回看：把規範的目的和形式分開看。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="S30" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：把規範的目的和形式分開看。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="T30" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：把規範的目的和形式分開看。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="U30" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3464,10 +3464,10 @@
         <x:v>把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="Z30" s="35" t="str">
-        <x:v>臺灣是遷徙與交流的中繼點</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AA30" s="35" t="str">
-        <x:v>核對單位、時間、尺度與原始數值</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="AB30" s="35" t="str">
         <x:v>A</x:v>
@@ -3476,10 +3476,10 @@
         <x:v>這是判斷「規範變遷」時要使用的依據。規範服務共同生活，能因新需求修正；改變做法不等於放棄互助價值。</x:v>
       </x:c>
       <x:c r="AD30" s="35" t="str">
-        <x:v>這是「位置與交流」的重點；本題要判斷的是「規範變遷」，兩者不能互相代替。</x:v>
+        <x:v>這是「海岸變遷」的重點；本題要判斷的是「規範變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE30" s="35" t="str">
-        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「規範變遷」判斷。</x:v>
+        <x:v>這項知識屬於「移民與季風」，無法支持本題的「規範變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF30" s="35" t="str">
         <x:v>遇到新規定時，比較改前改後處理的問題。</x:v>
@@ -3514,13 +3514,13 @@
         <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="J31" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="K31" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="L31" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="M31" s="35" t="str">
         <x:v>A</x:v>
@@ -3538,13 +3538,13 @@
         <x:v>判斷精準。「規範可調整，互助目的仍保留」直接回應規範變遷，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R31" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：把規範的目的和形式分開看。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="S31" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：把規範的目的和形式分開看。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="T31" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把規範的目的和形式分開看。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「規範變遷」。請回看：把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="U31" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3562,10 +3562,10 @@
         <x:v>把規範的目的和形式分開看。</x:v>
       </x:c>
       <x:c r="Z31" s="35" t="str">
-        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AA31" s="35" t="str">
-        <x:v>外力暴露治理不足，促使政策改變</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="AB31" s="35" t="str">
         <x:v>A</x:v>
@@ -3574,10 +3574,10 @@
         <x:v>這是判斷「規範變遷」時要使用的依據。規範服務共同生活，能因新需求修正；改變做法不等於放棄互助價值。</x:v>
       </x:c>
       <x:c r="AD31" s="35" t="str">
-        <x:v>這是「航海動機」的重點；本題要判斷的是「規範變遷」，兩者不能互相代替。</x:v>
+        <x:v>這是「圖表判讀」的重點；本題要判斷的是「規範變遷」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE31" s="35" t="str">
-        <x:v>這項知識屬於「牡丹社事件」，無法支持本題的「規範變遷」判斷。</x:v>
+        <x:v>這項知識屬於「環境正義」，無法支持本題的「規範變遷」判斷。</x:v>
       </x:c>
       <x:c r="AF31" s="35" t="str">
         <x:v>遇到新規定時，比較改前改後處理的問題。</x:v>
@@ -3618,7 +3618,7 @@
         <x:v>完全不記錄獵物數量與季節</x:v>
       </x:c>
       <x:c r="L32" s="35" t="str">
-        <x:v>只由未受影響的人秘密決定</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="M32" s="35" t="str">
         <x:v>A</x:v>
@@ -3642,7 +3642,7 @@
         <x:v>這項推論缺少證據。請確認：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="T32" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="U32" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3660,10 +3660,10 @@
         <x:v>先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="Z32" s="35" t="str">
-        <x:v>訪談多方並搭配噪音與發電資料</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AA32" s="35" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB32" s="35" t="str">
         <x:v>A</x:v>
@@ -3672,10 +3672,10 @@
         <x:v>這是判斷「權利權衡」時要使用的依據。衝突同時涉及文化權利與生態永續，相關者參與和可查證資料都是公平決策的基礎。</x:v>
       </x:c>
       <x:c r="AD32" s="35" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「分析權衡」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE32" s="35" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「權利權衡」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「權利權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF32" s="35" t="str">
         <x:v>校園環境爭議也應讓使用者與生態觀點參與。</x:v>
@@ -3710,13 +3710,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J33" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="K33" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="L33" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="M33" s="35" t="str">
         <x:v>A</x:v>
@@ -3734,13 +3734,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應權利權衡，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R33" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="S33" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="T33" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="U33" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3758,10 +3758,10 @@
         <x:v>先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="Z33" s="35" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AA33" s="35" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="AB33" s="35" t="str">
         <x:v>A</x:v>
@@ -3770,10 +3770,10 @@
         <x:v>這是判斷「權利權衡」時要使用的依據。衝突同時涉及文化權利與生態永續，相關者參與和可查證資料都是公平決策的基礎。</x:v>
       </x:c>
       <x:c r="AD33" s="35" t="str">
-        <x:v>這是「永續漁業」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE33" s="35" t="str">
-        <x:v>這項知識屬於「港市與文化」，無法支持本題的「權利權衡」判斷。</x:v>
+        <x:v>這項知識屬於「人物與交流」，無法支持本題的「權利權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF33" s="35" t="str">
         <x:v>校園環境爭議也應讓使用者與生態觀點參與。</x:v>
@@ -3808,13 +3808,13 @@
         <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="J34" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="K34" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="L34" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="M34" s="35" t="str">
         <x:v>A</x:v>
@@ -3832,13 +3832,13 @@
         <x:v>這項選擇成立：相關各方應依資料協商文化與保育。它抓住權利權衡的關鍵條件。</x:v>
       </x:c>
       <x:c r="R34" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="S34" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="T34" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先列各方重視的價值與共同可查的資料。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「權利權衡」。請回看：先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="U34" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -3856,10 +3856,10 @@
         <x:v>先列各方重視的價值與共同可查的資料。</x:v>
       </x:c>
       <x:c r="Z34" s="35" t="str">
-        <x:v>限定結論範圍並說明調查限制</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AA34" s="35" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AB34" s="35" t="str">
         <x:v>A</x:v>
@@ -3868,10 +3868,10 @@
         <x:v>這是判斷「權利權衡」時要使用的依據。衝突同時涉及文化權利與生態永續，相關者參與和可查證資料都是公平決策的基礎。</x:v>
       </x:c>
       <x:c r="AD34" s="35" t="str">
-        <x:v>這是「結論界線」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「港市與文化」的重點；本題要判斷的是「權利權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE34" s="35" t="str">
-        <x:v>這項知識屬於「消費安全」，無法支持本題的「權利權衡」判斷。</x:v>
+        <x:v>這項知識屬於「多元觀點」，無法支持本題的「權利權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF34" s="35" t="str">
         <x:v>校園環境爭議也應讓使用者與生態觀點參與。</x:v>
@@ -3912,7 +3912,7 @@
         <x:v>把坡地挖得更陡利於排水</x:v>
       </x:c>
       <x:c r="L35" s="34" t="str">
-        <x:v>只加化學藥劑就能固定土壤</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="M35" s="34" t="str">
         <x:v>A</x:v>
@@ -3936,7 +3936,7 @@
         <x:v>選項和題意關係較弱。提示：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="T35" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="U35" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -3957,7 +3957,7 @@
         <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AA35" s="34" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="AB35" s="34" t="str">
         <x:v>A</x:v>
@@ -3969,7 +3969,7 @@
         <x:v>這是「經濟北移」的重點；本題要判斷的是「永續農業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE35" s="34" t="str">
-        <x:v>這項知識屬於「共識與程序」，無法支持本題的「永續農業」判斷。</x:v>
+        <x:v>這項知識屬於「行動評估」，無法支持本題的「永續農業」判斷。</x:v>
       </x:c>
       <x:c r="AF35" s="34" t="str">
         <x:v>校園菜園保留覆蓋並觀察雨後逕流。</x:v>
@@ -4004,13 +4004,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J36" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="K36" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="L36" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="M36" s="34" t="str">
         <x:v>A</x:v>
@@ -4028,13 +4028,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住永續農業的關鍵條件。</x:v>
       </x:c>
       <x:c r="R36" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="S36" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="T36" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="U36" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4052,10 +4052,10 @@
         <x:v>方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="Z36" s="34" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="AA36" s="34" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB36" s="34" t="str">
         <x:v>A</x:v>
@@ -4064,10 +4064,10 @@
         <x:v>這是判斷「永續農業」時要使用的依據。多層植被與覆蓋能降低沖蝕並維持產出；清林、挖陡或只靠藥劑會忽略水土風險。</x:v>
       </x:c>
       <x:c r="AD36" s="34" t="str">
-        <x:v>這是「理財風險」的重點；本題要判斷的是「永續農業」，兩者不能互相代替。</x:v>
+        <x:v>這是「能源提問」的重點；本題要判斷的是「永續農業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE36" s="34" t="str">
-        <x:v>這項知識屬於「權利權衡」，無法支持本題的「永續農業」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「永續農業」判斷。</x:v>
       </x:c>
       <x:c r="AF36" s="34" t="str">
         <x:v>校園菜園保留覆蓋並觀察雨後逕流。</x:v>
@@ -4102,13 +4102,13 @@
         <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="J37" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="K37" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="L37" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="M37" s="34" t="str">
         <x:v>A</x:v>
@@ -4126,13 +4126,13 @@
         <x:v>證據吻合。選項「保留植被並依坡度調整耕作」能把永續農業的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R37" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="S37" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="T37" s="34" t="str">
-        <x:v>焦點放錯了。請回看：方案要同時回應生產與土壤流失。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「永續農業」。請回看：方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="U37" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4150,10 +4150,10 @@
         <x:v>方案要同時回應生產與土壤流失。</x:v>
       </x:c>
       <x:c r="Z37" s="34" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AA37" s="34" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AB37" s="34" t="str">
         <x:v>A</x:v>
@@ -4162,10 +4162,10 @@
         <x:v>這是判斷「永續農業」時要使用的依據。多層植被與覆蓋能降低沖蝕並維持產出；清林、挖陡或只靠藥劑會忽略水土風險。</x:v>
       </x:c>
       <x:c r="AD37" s="34" t="str">
-        <x:v>這是「海岸變遷」的重點；本題要判斷的是「永續農業」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境與生活」的重點；本題要判斷的是「永續農業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE37" s="34" t="str">
-        <x:v>這項知識屬於「移民與季風」，無法支持本題的「永續農業」判斷。</x:v>
+        <x:v>這項知識屬於「族群衝突」，無法支持本題的「永續農業」判斷。</x:v>
       </x:c>
       <x:c r="AF37" s="34" t="str">
         <x:v>校園菜園保留覆蓋並觀察雨後逕流。</x:v>
@@ -4206,7 +4206,7 @@
         <x:v>有疑慮就否定所有畜牧</x:v>
       </x:c>
       <x:c r="L38" s="34" t="str">
-        <x:v>只聽業者宣傳，不查監測</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="M38" s="34" t="str">
         <x:v>A</x:v>
@@ -4230,7 +4230,7 @@
         <x:v>這裡混淆了條件與結論。提示：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="T38" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="U38" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4251,7 +4251,7 @@
         <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="AA38" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AB38" s="34" t="str">
         <x:v>A</x:v>
@@ -4263,7 +4263,7 @@
         <x:v>這是「能源代價」的重點；本題要判斷的是「畜牧權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE38" s="34" t="str">
-        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「畜牧權衡」判斷。</x:v>
+        <x:v>這項知識屬於「環境與生活」，無法支持本題的「畜牧權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF38" s="34" t="str">
         <x:v>參訪農場時觀察生產量，也看環境管理。</x:v>
@@ -4298,13 +4298,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J39" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="K39" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="L39" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="M39" s="34" t="str">
         <x:v>A</x:v>
@@ -4322,13 +4322,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把畜牧權衡的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R39" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="S39" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="T39" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="U39" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4346,10 +4346,10 @@
         <x:v>把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="Z39" s="34" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AA39" s="34" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="AB39" s="34" t="str">
         <x:v>A</x:v>
@@ -4358,10 +4358,10 @@
         <x:v>這是判斷「畜牧權衡」時要使用的依據。畜牧涉及經濟、動物、健康與環境多重結果，不能用價格或單一立場代替完整評估。</x:v>
       </x:c>
       <x:c r="AD39" s="34" t="str">
-        <x:v>這是「行動評估」的重點；本題要判斷的是「畜牧權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「板塊與地形」的重點；本題要判斷的是「畜牧權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE39" s="34" t="str">
-        <x:v>這項知識屬於「多元資料」，無法支持本題的「畜牧權衡」判斷。</x:v>
+        <x:v>這項知識屬於「行動省思」，無法支持本題的「畜牧權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF39" s="34" t="str">
         <x:v>參訪農場時觀察生產量，也看環境管理。</x:v>
@@ -4396,13 +4396,13 @@
         <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="J40" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="K40" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="L40" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="M40" s="34" t="str">
         <x:v>A</x:v>
@@ -4420,13 +4420,13 @@
         <x:v>答對了；「比較供應、動物、傳染病與廢水管理」同時保留了畜牧權衡需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R40" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="S40" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="T40" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把經濟、社會與環境三面向都列出。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「畜牧權衡」。請回看：把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="U40" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4444,10 +4444,10 @@
         <x:v>把經濟、社會與環境三面向都列出。</x:v>
       </x:c>
       <x:c r="Z40" s="34" t="str">
-        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AA40" s="34" t="str">
-        <x:v>比較具體貢獻、限制與在地回應</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AB40" s="34" t="str">
         <x:v>A</x:v>
@@ -4456,10 +4456,10 @@
         <x:v>這是判斷「畜牧權衡」時要使用的依據。畜牧涉及經濟、動物、健康與環境多重結果，不能用價格或單一立場代替完整評估。</x:v>
       </x:c>
       <x:c r="AD40" s="34" t="str">
-        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「畜牧權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「問題形成」的重點；本題要判斷的是「畜牧權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE40" s="34" t="str">
-        <x:v>這項知識屬於「人物與交流」，無法支持本題的「畜牧權衡」判斷。</x:v>
+        <x:v>這項知識屬於「地理配對」，無法支持本題的「畜牧權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF40" s="34" t="str">
         <x:v>參訪農場時觀察生產量，也看環境管理。</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>永久禁止所有人接近海洋</x:v>
       </x:c>
       <x:c r="L41" s="34" t="str">
-        <x:v>只增加更大的漁船與漁網</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="M41" s="34" t="str">
         <x:v>A</x:v>
@@ -4524,7 +4524,7 @@
         <x:v>這項判斷忽略重要限制。請想想：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="T41" s="34" t="str">
-        <x:v>焦點放錯了。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="U41" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4542,10 +4542,10 @@
         <x:v>想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="Z41" s="34" t="str">
-        <x:v>比較設置前後的發電、用電與環境</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AA41" s="34" t="str">
-        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AB41" s="34" t="str">
         <x:v>A</x:v>
@@ -4554,10 +4554,10 @@
         <x:v>這是判斷「永續漁業」時要使用的依據。讓魚群有繁殖時間並提供轉型支持，才能同時處理生態與生計；無限制捕撈會惡化枯竭。</x:v>
       </x:c>
       <x:c r="AD41" s="34" t="str">
-        <x:v>這是「能源提問」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元觀點」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE41" s="34" t="str">
-        <x:v>這項知識屬於「時序空間」，無法支持本題的「永續漁業」判斷。</x:v>
+        <x:v>這項知識屬於「貿易影響」，無法支持本題的「永續漁業」判斷。</x:v>
       </x:c>
       <x:c r="AF41" s="34" t="str">
         <x:v>買海鮮時參考季節與永續標示。</x:v>
@@ -4592,13 +4592,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J42" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="K42" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="L42" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="M42" s="34" t="str">
         <x:v>A</x:v>
@@ -4616,13 +4616,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了永續漁業需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R42" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="S42" s="34" t="str">
-        <x:v>焦點放錯了。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="T42" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="U42" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4640,10 +4640,10 @@
         <x:v>想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="Z42" s="34" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AA42" s="34" t="str">
-        <x:v>分析資源、語言、組織與治理</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AB42" s="34" t="str">
         <x:v>A</x:v>
@@ -4652,10 +4652,10 @@
         <x:v>這是判斷「永續漁業」時要使用的依據。讓魚群有繁殖時間並提供轉型支持，才能同時處理生態與生計；無限制捕撈會惡化枯竭。</x:v>
       </x:c>
       <x:c r="AD42" s="34" t="str">
-        <x:v>這是「環境與生活」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
+        <x:v>這是「權利權衡」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE42" s="34" t="str">
-        <x:v>這項知識屬於「族群衝突」，無法支持本題的「永續漁業」判斷。</x:v>
+        <x:v>這項知識屬於「經濟北移」，無法支持本題的「永續漁業」判斷。</x:v>
       </x:c>
       <x:c r="AF42" s="34" t="str">
         <x:v>買海鮮時參考季節與永續標示。</x:v>
@@ -4690,13 +4690,13 @@
         <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="J43" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="K43" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="L43" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="M43" s="34" t="str">
         <x:v>A</x:v>
@@ -4714,13 +4714,13 @@
         <x:v>你的判讀可被查證：設禁漁期、尺寸限制並協助轉型。這正是永續漁業要比較的核心。</x:v>
       </x:c>
       <x:c r="R43" s="34" t="str">
-        <x:v>焦點放錯了。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="S43" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="T43" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：想想魚群如何恢復，漁民如何度過調整期。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「永續漁業」。請回看：想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="U43" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4738,10 +4738,10 @@
         <x:v>想想魚群如何恢復，漁民如何度過調整期。</x:v>
       </x:c>
       <x:c r="Z43" s="34" t="str">
-        <x:v>核對單位、時間、尺度與原始數值</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AA43" s="34" t="str">
-        <x:v>風險分配與居民參與需要公平</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="AB43" s="34" t="str">
         <x:v>A</x:v>
@@ -4750,10 +4750,10 @@
         <x:v>這是判斷「永續漁業」時要使用的依據。讓魚群有繁殖時間並提供轉型支持，才能同時處理生態與生計；無限制捕撈會惡化枯竭。</x:v>
       </x:c>
       <x:c r="AD43" s="34" t="str">
-        <x:v>這是「圖表判讀」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
+        <x:v>這是「族群衝突」的重點；本題要判斷的是「永續漁業」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE43" s="34" t="str">
-        <x:v>這項知識屬於「環境正義」，無法支持本題的「永續漁業」判斷。</x:v>
+        <x:v>這項知識屬於「能源提問」，無法支持本題的「永續漁業」判斷。</x:v>
       </x:c>
       <x:c r="AF43" s="34" t="str">
         <x:v>買海鮮時參考季節與永續標示。</x:v>
@@ -4794,7 +4794,7 @@
         <x:v>本地不砍樹就沒有任何環境責任</x:v>
       </x:c>
       <x:c r="L44" s="34" t="str">
-        <x:v>所有人工林都應永遠禁止利用</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="M44" s="34" t="str">
         <x:v>A</x:v>
@@ -4818,7 +4818,7 @@
         <x:v>焦點放錯了。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="T44" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：環境影響可能跨國移動。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="U44" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4836,10 +4836,10 @@
         <x:v>環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="Z44" s="34" t="str">
-        <x:v>板塊交界造成多山與地震</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AA44" s="34" t="str">
-        <x:v>查紀錄、調方法，再用同指標測量</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AB44" s="34" t="str">
         <x:v>A</x:v>
@@ -4848,10 +4848,10 @@
         <x:v>這是判斷「森林供應鏈」時要使用的依據。木材需求可能把環境壓力移到國外，因此仍需追查供應鏈與永續林業。</x:v>
       </x:c>
       <x:c r="AD44" s="34" t="str">
-        <x:v>這是「板塊與地形」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
+        <x:v>這是「海岸變遷」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE44" s="34" t="str">
-        <x:v>這項知識屬於「行動省思」，無法支持本題的「森林供應鏈」判斷。</x:v>
+        <x:v>這項知識屬於「水利開墾」，無法支持本題的「森林供應鏈」判斷。</x:v>
       </x:c>
       <x:c r="AF44" s="34" t="str">
         <x:v>購買木製品時查看來源與認證。</x:v>
@@ -4886,13 +4886,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J45" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="K45" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="L45" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="M45" s="34" t="str">
         <x:v>A</x:v>
@@ -4910,13 +4910,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是森林供應鏈要比較的核心。</x:v>
       </x:c>
       <x:c r="R45" s="34" t="str">
-        <x:v>焦點放錯了。請回看：環境影響可能跨國移動。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="S45" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：環境影響可能跨國移動。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="T45" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：環境影響可能跨國移動。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="U45" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -4934,10 +4934,10 @@
         <x:v>環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="Z45" s="34" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AA45" s="34" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="AB45" s="34" t="str">
         <x:v>A</x:v>
@@ -4946,10 +4946,10 @@
         <x:v>這是判斷「森林供應鏈」時要使用的依據。木材需求可能把環境壓力移到國外，因此仍需追查供應鏈與永續林業。</x:v>
       </x:c>
       <x:c r="AD45" s="34" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元資料」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE45" s="34" t="str">
-        <x:v>這項知識屬於「電力與生活」，無法支持本題的「森林供應鏈」判斷。</x:v>
+        <x:v>這項知識屬於「能源代價」，無法支持本題的「森林供應鏈」判斷。</x:v>
       </x:c>
       <x:c r="AF45" s="34" t="str">
         <x:v>購買木製品時查看來源與認證。</x:v>
@@ -4984,13 +4984,13 @@
         <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="J46" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="K46" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="L46" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="M46" s="34" t="str">
         <x:v>A</x:v>
@@ -5008,13 +5008,13 @@
         <x:v>判斷精準。「查明進口木材是否來自永續來源」直接回應森林供應鏈，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R46" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：環境影響可能跨國移動。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="S46" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：環境影響可能跨國移動。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="T46" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：環境影響可能跨國移動。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「森林供應鏈」。請回看：環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="U46" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -5032,10 +5032,10 @@
         <x:v>環境影響可能跨國移動。</x:v>
       </x:c>
       <x:c r="Z46" s="34" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="AA46" s="34" t="str">
-        <x:v>訪談多方並搭配噪音與發電資料</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AB46" s="34" t="str">
         <x:v>A</x:v>
@@ -5044,10 +5044,10 @@
         <x:v>這是判斷「森林供應鏈」時要使用的依據。木材需求可能把環境壓力移到國外，因此仍需追查供應鏈與永續林業。</x:v>
       </x:c>
       <x:c r="AD46" s="34" t="str">
-        <x:v>這是「港市與文化」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
+        <x:v>這是「電力與生活」的重點；本題要判斷的是「森林供應鏈」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE46" s="34" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「森林供應鏈」判斷。</x:v>
+        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「森林供應鏈」判斷。</x:v>
       </x:c>
       <x:c r="AF46" s="34" t="str">
         <x:v>購買木製品時查看來源與認證。</x:v>
@@ -5088,7 +5088,7 @@
         <x:v>只計算紀念品種類</x:v>
       </x:c>
       <x:c r="L47" s="34" t="str">
-        <x:v>認定遊客增加就必然人人受益</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="M47" s="34" t="str">
         <x:v>A</x:v>
@@ -5112,7 +5112,7 @@
         <x:v>這項推論缺少證據。請確認：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="T47" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="U47" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -5130,10 +5130,10 @@
         <x:v>問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="Z47" s="34" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AA47" s="34" t="str">
-        <x:v>商品與港口帶動北部市鎮發展</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="AB47" s="34" t="str">
         <x:v>A</x:v>
@@ -5142,10 +5142,10 @@
         <x:v>這是判斷「地方轉型」時要使用的依據。地方轉型不只追求人潮，還要看文化、社會、經濟與環境是否長期改善。</x:v>
       </x:c>
       <x:c r="AD47" s="34" t="str">
-        <x:v>這是「權利權衡」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
+        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE47" s="34" t="str">
-        <x:v>這項知識屬於「經濟北移」，無法支持本題的「地方轉型」判斷。</x:v>
+        <x:v>這項知識屬於「牡丹社事件」，無法支持本題的「地方轉型」判斷。</x:v>
       </x:c>
       <x:c r="AF47" s="34" t="str">
         <x:v>參訪舊產業場址時，也了解勞動與環境代價。</x:v>
@@ -5180,13 +5180,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J48" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="K48" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="L48" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="M48" s="34" t="str">
         <x:v>A</x:v>
@@ -5204,13 +5204,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應地方轉型，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R48" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="S48" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="T48" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="U48" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -5228,10 +5228,10 @@
         <x:v>問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="Z48" s="34" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AA48" s="34" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="AB48" s="34" t="str">
         <x:v>A</x:v>
@@ -5240,10 +5240,10 @@
         <x:v>這是判斷「地方轉型」時要使用的依據。地方轉型不只追求人潮，還要看文化、社會、經濟與環境是否長期改善。</x:v>
       </x:c>
       <x:c r="AD48" s="34" t="str">
-        <x:v>這是「移民與季風」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
+        <x:v>這是「經濟北移」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE48" s="34" t="str">
-        <x:v>這項知識屬於「理財風險」，無法支持本題的「地方轉型」判斷。</x:v>
+        <x:v>這項知識屬於「共識與程序」，無法支持本題的「地方轉型」判斷。</x:v>
       </x:c>
       <x:c r="AF48" s="34" t="str">
         <x:v>參訪舊產業場址時，也了解勞動與環境代價。</x:v>
@@ -5278,13 +5278,13 @@
         <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="J49" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="K49" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="L49" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="M49" s="34" t="str">
         <x:v>A</x:v>
@@ -5302,13 +5302,13 @@
         <x:v>這項選擇成立：長期追蹤保存、參與、就業與環境。它抓住地方轉型的關鍵條件。</x:v>
       </x:c>
       <x:c r="R49" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="S49" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="T49" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：問誰參與、誰受益、保存了什麼。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「地方轉型」。請回看：問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="U49" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -5326,10 +5326,10 @@
         <x:v>問誰參與、誰受益、保存了什麼。</x:v>
       </x:c>
       <x:c r="Z49" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="AA49" s="34" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AB49" s="34" t="str">
         <x:v>A</x:v>
@@ -5338,10 +5338,10 @@
         <x:v>這是判斷「地方轉型」時要使用的依據。地方轉型不只追求人潮，還要看文化、社會、經濟與環境是否長期改善。</x:v>
       </x:c>
       <x:c r="AD49" s="34" t="str">
-        <x:v>這是「能源分類」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
+        <x:v>這是「理財風險」的重點；本題要判斷的是「地方轉型」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE49" s="34" t="str">
-        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「地方轉型」判斷。</x:v>
+        <x:v>這項知識屬於「權利權衡」，無法支持本題的「地方轉型」判斷。</x:v>
       </x:c>
       <x:c r="AF49" s="34" t="str">
         <x:v>參訪舊產業場址時，也了解勞動與環境代價。</x:v>
@@ -5382,7 +5382,7 @@
         <x:v>居民不再需要任何貿易</x:v>
       </x:c>
       <x:c r="L50" s="35" t="str">
-        <x:v>城牆變高直接堵住海洋</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="M50" s="35" t="str">
         <x:v>A</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>選項和題意關係較弱。提示：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="T50" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="U50" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5424,10 +5424,10 @@
         <x:v>連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="Z50" s="35" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="AA50" s="35" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AB50" s="35" t="str">
         <x:v>A</x:v>
@@ -5436,10 +5436,10 @@
         <x:v>這是判斷「潟湖與港口」時要使用的依據。泥沙堆積會改變水深與海岸線，進一步影響船舶和聚落經濟。</x:v>
       </x:c>
       <x:c r="AD50" s="35" t="str">
-        <x:v>這是「循環經濟」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
+        <x:v>這是「能源提問」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE50" s="35" t="str">
-        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「潟湖與港口」判斷。</x:v>
+        <x:v>這項知識屬於「森林供應鏈」，無法支持本題的「潟湖與港口」判斷。</x:v>
       </x:c>
       <x:c r="AF50" s="35" t="str">
         <x:v>用古今地圖找海岸線和港道變化。</x:v>
@@ -5474,13 +5474,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J51" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="K51" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="L51" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="M51" s="35" t="str">
         <x:v>A</x:v>
@@ -5498,13 +5498,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住潟湖與港口的關鍵條件。</x:v>
       </x:c>
       <x:c r="R51" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="S51" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="T51" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="U51" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5522,10 +5522,10 @@
         <x:v>連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="Z51" s="35" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AA51" s="35" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AB51" s="35" t="str">
         <x:v>A</x:v>
@@ -5534,10 +5534,10 @@
         <x:v>這是判斷「潟湖與港口」時要使用的依據。泥沙堆積會改變水深與海岸線，進一步影響船舶和聚落經濟。</x:v>
       </x:c>
       <x:c r="AD51" s="35" t="str">
-        <x:v>這是「文化多樣性」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範變遷」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE51" s="35" t="str">
-        <x:v>這項知識屬於「遷移原因」，無法支持本題的「潟湖與港口」判斷。</x:v>
+        <x:v>這項知識屬於「開港背景」，無法支持本題的「潟湖與港口」判斷。</x:v>
       </x:c>
       <x:c r="AF51" s="35" t="str">
         <x:v>用古今地圖找海岸線和港道變化。</x:v>
@@ -5572,13 +5572,13 @@
         <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="J52" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="K52" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="L52" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="M52" s="35" t="str">
         <x:v>A</x:v>
@@ -5596,13 +5596,13 @@
         <x:v>證據吻合。選項「泥沙堆積使船難進出，港口轉移」能把潟湖與港口的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R52" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="S52" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="T52" s="35" t="str">
-        <x:v>焦點放錯了。請回看：連起泥沙、水深、船隻與港市。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「潟湖與港口」。請回看：連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="U52" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5620,10 +5620,10 @@
         <x:v>連起泥沙、水深、船隻與港市。</x:v>
       </x:c>
       <x:c r="Z52" s="35" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="AA52" s="35" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AB52" s="35" t="str">
         <x:v>A</x:v>
@@ -5632,10 +5632,10 @@
         <x:v>這是判斷「潟湖與港口」時要使用的依據。泥沙堆積會改變水深與海岸線，進一步影響船舶和聚落經濟。</x:v>
       </x:c>
       <x:c r="AD52" s="35" t="str">
-        <x:v>這是「多元資料」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
+        <x:v>這是「遷移原因」的重點；本題要判斷的是「潟湖與港口」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE52" s="35" t="str">
-        <x:v>這項知識屬於「能源代價」，無法支持本題的「潟湖與港口」判斷。</x:v>
+        <x:v>這項知識屬於「循環經濟」，無法支持本題的「潟湖與港口」判斷。</x:v>
       </x:c>
       <x:c r="AF52" s="35" t="str">
         <x:v>用古今地圖找海岸線和港道變化。</x:v>
@@ -5676,7 +5676,7 @@
         <x:v>臺灣控制全世界所有商品</x:v>
       </x:c>
       <x:c r="L53" s="35" t="str">
-        <x:v>只因山峰高度適合觀光</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="M53" s="35" t="str">
         <x:v>A</x:v>
@@ -5700,7 +5700,7 @@
         <x:v>這裡混淆了條件與結論。提示：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="T53" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從航路、商品和競爭思考。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="U53" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5718,10 +5718,10 @@
         <x:v>從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="Z53" s="35" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AA53" s="35" t="str">
-        <x:v>限定結論範圍並說明調查限制</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="AB53" s="35" t="str">
         <x:v>A</x:v>
@@ -5730,10 +5730,10 @@
         <x:v>這是判斷「航海動機」時要使用的依據。航路位置與商業競爭能解釋多方進入臺灣；其他說法在地理或因果上不成立。</x:v>
       </x:c>
       <x:c r="AD53" s="35" t="str">
-        <x:v>這是「地圖尺度」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
+        <x:v>這是「板塊與地形」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE53" s="35" t="str">
-        <x:v>這項知識屬於「結論界線」，無法支持本題的「航海動機」判斷。</x:v>
+        <x:v>這項知識屬於「移民與季風」，無法支持本題的「航海動機」判斷。</x:v>
       </x:c>
       <x:c r="AF53" s="35" t="str">
         <x:v>分析企業選址時，也分開位置優勢與宣傳。</x:v>
@@ -5768,13 +5768,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J54" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="K54" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="L54" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="M54" s="35" t="str">
         <x:v>A</x:v>
@@ -5792,13 +5792,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把航海動機的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R54" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：從航路、商品和競爭思考。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="S54" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從航路、商品和競爭思考。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="T54" s="35" t="str">
-        <x:v>焦點放錯了。請回看：從航路、商品和競爭思考。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="U54" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5816,10 +5816,10 @@
         <x:v>從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="Z54" s="35" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AA54" s="35" t="str">
-        <x:v>海防受重視，建省與建設強化治理</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AB54" s="35" t="str">
         <x:v>A</x:v>
@@ -5828,10 +5828,10 @@
         <x:v>這是判斷「航海動機」時要使用的依據。航路位置與商業競爭能解釋多方進入臺灣；其他說法在地理或因果上不成立。</x:v>
       </x:c>
       <x:c r="AD54" s="35" t="str">
-        <x:v>這是「永續漁業」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
+        <x:v>這是「問題形成」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE54" s="35" t="str">
-        <x:v>這項知識屬於「清法戰爭與建省」，無法支持本題的「航海動機」判斷。</x:v>
+        <x:v>這項知識屬於「地理配對」，無法支持本題的「航海動機」判斷。</x:v>
       </x:c>
       <x:c r="AF54" s="35" t="str">
         <x:v>分析企業選址時，也分開位置優勢與宣傳。</x:v>
@@ -5866,13 +5866,13 @@
         <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="J55" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="K55" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="L55" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="M55" s="35" t="str">
         <x:v>A</x:v>
@@ -5890,13 +5890,13 @@
         <x:v>答對了；「臺灣鄰近航路，利於貿易競爭」同時保留了航海動機需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R55" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從航路、商品和競爭思考。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="S55" s="35" t="str">
-        <x:v>焦點放錯了。請回看：從航路、商品和競爭思考。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="T55" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：從航路、商品和競爭思考。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「航海動機」。請回看：從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="U55" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -5914,10 +5914,10 @@
         <x:v>從航路、商品和競爭思考。</x:v>
       </x:c>
       <x:c r="Z55" s="35" t="str">
-        <x:v>分析資源、語言、組織與治理</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="AA55" s="35" t="str">
-        <x:v>比較設置前後的發電、用電與環境</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="AB55" s="35" t="str">
         <x:v>A</x:v>
@@ -5926,10 +5926,10 @@
         <x:v>這是判斷「航海動機」時要使用的依據。航路位置與商業競爭能解釋多方進入臺灣；其他說法在地理或因果上不成立。</x:v>
       </x:c>
       <x:c r="AD55" s="35" t="str">
-        <x:v>這是「族群衝突」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
+        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「航海動機」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE55" s="35" t="str">
-        <x:v>這項知識屬於「能源提問」，無法支持本題的「航海動機」判斷。</x:v>
+        <x:v>這項知識屬於「地圖尺度」，無法支持本題的「航海動機」判斷。</x:v>
       </x:c>
       <x:c r="AF55" s="35" t="str">
         <x:v>分析企業選址時，也分開位置優勢與宣傳。</x:v>
@@ -5970,7 +5970,7 @@
         <x:v>西班牙只在南部，荷蘭只在北部</x:v>
       </x:c>
       <x:c r="L56" s="35" t="str">
-        <x:v>清帝國建省後才進入大航海時代</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="M56" s="35" t="str">
         <x:v>A</x:v>
@@ -5994,7 +5994,7 @@
         <x:v>這項判斷忽略重要限制。請想想：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="T56" s="35" t="str">
-        <x:v>焦點放錯了。請回看：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="U56" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6012,10 +6012,10 @@
         <x:v>抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="Z56" s="35" t="str">
-        <x:v>規範可調整，互助目的仍保留</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AA56" s="35" t="str">
-        <x:v>通商壓力、物產與航路共同促成開港</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="AB56" s="35" t="str">
         <x:v>A</x:v>
@@ -6024,10 +6024,10 @@
         <x:v>這是判斷「時序空間」時要使用的依據。事件需同時核對十七世紀先後和南北據點；錯置其中一項就會改變歷史解釋。</x:v>
       </x:c>
       <x:c r="AD56" s="35" t="str">
-        <x:v>這是「規範變遷」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
+        <x:v>這是「權利權衡」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE56" s="35" t="str">
-        <x:v>這項知識屬於「開港背景」，無法支持本題的「時序空間」判斷。</x:v>
+        <x:v>這項知識屬於「人物與交流」，無法支持本題的「時序空間」判斷。</x:v>
       </x:c>
       <x:c r="AF56" s="35" t="str">
         <x:v>做時間線時，每筆都標日期、地點和行動者。</x:v>
@@ -6062,13 +6062,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J57" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="K57" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="L57" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="M57" s="35" t="str">
         <x:v>A</x:v>
@@ -6086,13 +6086,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了時序空間需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R57" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="S57" s="35" t="str">
-        <x:v>焦點放錯了。請回看：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="T57" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="U57" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6110,10 +6110,10 @@
         <x:v>抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="Z57" s="35" t="str">
-        <x:v>查紀錄、調方法，再用同指標測量</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AA57" s="35" t="str">
-        <x:v>保存證據，再循正式管道申訴</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AB57" s="35" t="str">
         <x:v>A</x:v>
@@ -6122,10 +6122,10 @@
         <x:v>這是判斷「時序空間」時要使用的依據。事件需同時核對十七世紀先後和南北據點；錯置其中一項就會改變歷史解釋。</x:v>
       </x:c>
       <x:c r="AD57" s="35" t="str">
-        <x:v>這是「行動省思」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
+        <x:v>這是「開港背景」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE57" s="35" t="str">
-        <x:v>這項知識屬於「消費權益」，無法支持本題的「時序空間」判斷。</x:v>
+        <x:v>這項知識屬於「分析權衡」，無法支持本題的「時序空間」判斷。</x:v>
       </x:c>
       <x:c r="AF57" s="35" t="str">
         <x:v>做時間線時，每筆都標日期、地點和行動者。</x:v>
@@ -6160,13 +6160,13 @@
         <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="J58" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="K58" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="L58" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="M58" s="35" t="str">
         <x:v>A</x:v>
@@ -6184,13 +6184,13 @@
         <x:v>你的判讀可被查證：南荷北西，後由鄭成功驅逐荷蘭。這正是時序空間要比較的核心。</x:v>
       </x:c>
       <x:c r="R58" s="35" t="str">
-        <x:v>焦點放錯了。請回看：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="S58" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="T58" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：抓住南荷北西與 1662 年前後。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「時序空間」。請回看：抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="U58" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6208,10 +6208,10 @@
         <x:v>抓住南荷北西與 1662 年前後。</x:v>
       </x:c>
       <x:c r="Z58" s="35" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AA58" s="35" t="str">
-        <x:v>板塊交界造成多山與地震</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AB58" s="35" t="str">
         <x:v>A</x:v>
@@ -6220,10 +6220,10 @@
         <x:v>這是判斷「時序空間」時要使用的依據。事件需同時核對十七世紀先後和南北據點；錯置其中一項就會改變歷史解釋。</x:v>
       </x:c>
       <x:c r="AD58" s="35" t="str">
-        <x:v>這是「電力與生活」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費權益」的重點；本題要判斷的是「時序空間」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE58" s="35" t="str">
-        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「時序空間」判斷。</x:v>
+        <x:v>這項知識屬於「規範變遷」，無法支持本題的「時序空間」判斷。</x:v>
       </x:c>
       <x:c r="AF58" s="35" t="str">
         <x:v>做時間線時，每筆都標日期、地點和行動者。</x:v>
@@ -6264,7 +6264,7 @@
         <x:v>把口述全部當傳說刪掉</x:v>
       </x:c>
       <x:c r="L59" s="35" t="str">
-        <x:v>因說法不同就判定事件沒發生</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="M59" s="35" t="str">
         <x:v>A</x:v>
@@ -6288,7 +6288,7 @@
         <x:v>焦點放錯了。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="T59" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：問誰在命名、根據什麼。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="U59" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6306,10 +6306,10 @@
         <x:v>問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="Z59" s="35" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AA59" s="35" t="str">
-        <x:v>依地理條件發展能源並評估影響</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="AB59" s="35" t="str">
         <x:v>A</x:v>
@@ -6318,10 +6318,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。用詞反映權力與立場，差異本身就是史料；應比較來源而非先消除異議。</x:v>
       </x:c>
       <x:c r="AD59" s="35" t="str">
-        <x:v>這是「問題形成」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元資料」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE59" s="35" t="str">
-        <x:v>這項知識屬於「地理配對」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「環境正義」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF59" s="35" t="str">
         <x:v>讀新聞時比較不同媒體如何描述同一事件。</x:v>
@@ -6356,13 +6356,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J60" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="K60" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="L60" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="M60" s="35" t="str">
         <x:v>A</x:v>
@@ -6380,13 +6380,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是多元觀點要比較的核心。</x:v>
       </x:c>
       <x:c r="R60" s="35" t="str">
-        <x:v>焦點放錯了。請回看：問誰在命名、根據什麼。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="S60" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：問誰在命名、根據什麼。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="T60" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰在命名、根據什麼。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="U60" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6404,10 +6404,10 @@
         <x:v>問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="Z60" s="35" t="str">
-        <x:v>商品與港口帶動北部市鎮發展</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AA60" s="35" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="AB60" s="35" t="str">
         <x:v>A</x:v>
@@ -6416,10 +6416,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。用詞反映權力與立場，差異本身就是史料；應比較來源而非先消除異議。</x:v>
       </x:c>
       <x:c r="AD60" s="35" t="str">
-        <x:v>這是「經濟北移」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「地理配對」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE60" s="35" t="str">
-        <x:v>這項知識屬於「共識與程序」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「史前證據」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF60" s="35" t="str">
         <x:v>讀新聞時比較不同媒體如何描述同一事件。</x:v>
@@ -6454,13 +6454,13 @@
         <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="J61" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="K61" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="L61" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="M61" s="35" t="str">
         <x:v>A</x:v>
@@ -6478,13 +6478,13 @@
         <x:v>判斷精準。「比較雙方立場、目的與證據」直接回應多元觀點，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R61" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：問誰在命名、根據什麼。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="S61" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰在命名、根據什麼。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="T61" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問誰在命名、根據什麼。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「多元觀點」。請回看：問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="U61" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6502,10 +6502,10 @@
         <x:v>問誰在命名、根據什麼。</x:v>
       </x:c>
       <x:c r="Z61" s="35" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="AA61" s="35" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB61" s="35" t="str">
         <x:v>A</x:v>
@@ -6514,10 +6514,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。用詞反映權力與立場，差異本身就是史料；應比較來源而非先消除異議。</x:v>
       </x:c>
       <x:c r="AD61" s="35" t="str">
-        <x:v>這是「理財風險」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「共識與程序」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE61" s="35" t="str">
-        <x:v>這項知識屬於「權利權衡」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF61" s="35" t="str">
         <x:v>讀新聞時比較不同媒體如何描述同一事件。</x:v>
@@ -6558,7 +6558,7 @@
         <x:v>所有居民同樣獲利且沒有衝突</x:v>
       </x:c>
       <x:c r="L62" s="35" t="str">
-        <x:v>貿易一開始，傳統文化立即消失</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="M62" s="35" t="str">
         <x:v>A</x:v>
@@ -6582,7 +6582,7 @@
         <x:v>這項推論缺少證據。請確認：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="T62" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="U62" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6600,10 +6600,10 @@
         <x:v>不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="Z62" s="35" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AA62" s="35" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="AB62" s="35" t="str">
         <x:v>A</x:v>
@@ -6612,10 +6612,10 @@
         <x:v>這是判斷「貿易影響」時要使用的依據。貿易會牽動生產、土地和權力，合作、利益與衝突可能同時出現。</x:v>
       </x:c>
       <x:c r="AD62" s="35" t="str">
-        <x:v>這是「遷移原因」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
+        <x:v>這是「族群衝突」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE62" s="35" t="str">
-        <x:v>這項知識屬於「循環經濟」，無法支持本題的「貿易影響」判斷。</x:v>
+        <x:v>這項知識屬於「能源提問」，無法支持本題的「貿易影響」判斷。</x:v>
       </x:c>
       <x:c r="AF62" s="35" t="str">
         <x:v>分析開發案時，列出受益者與承擔成本者。</x:v>
@@ -6650,13 +6650,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J63" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="K63" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="L63" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="M63" s="35" t="str">
         <x:v>A</x:v>
@@ -6674,13 +6674,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應貿易影響，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R63" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="S63" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="T63" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="U63" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6698,10 +6698,10 @@
         <x:v>不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="Z63" s="35" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AA63" s="35" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="AB63" s="35" t="str">
         <x:v>A</x:v>
@@ -6710,10 +6710,10 @@
         <x:v>這是判斷「貿易影響」時要使用的依據。貿易會牽動生產、土地和權力，合作、利益與衝突可能同時出現。</x:v>
       </x:c>
       <x:c r="AD63" s="35" t="str">
-        <x:v>這是「能源代價」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
+        <x:v>這是「循環經濟」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE63" s="35" t="str">
-        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「貿易影響」判斷。</x:v>
+        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「貿易影響」判斷。</x:v>
       </x:c>
       <x:c r="AF63" s="35" t="str">
         <x:v>分析開發案時，列出受益者與承擔成本者。</x:v>
@@ -6748,13 +6748,13 @@
         <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="J64" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="K64" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="L64" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="M64" s="35" t="str">
         <x:v>A</x:v>
@@ -6772,13 +6772,13 @@
         <x:v>這項選擇成立：貿易增加，也改變土地與族群關係。它抓住貿易影響的關鍵條件。</x:v>
       </x:c>
       <x:c r="R64" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="S64" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="T64" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：不要只看貨物，也看生產者與權力。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「貿易影響」。請回看：不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="U64" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -6796,10 +6796,10 @@
         <x:v>不要只看貨物，也看生產者與權力。</x:v>
       </x:c>
       <x:c r="Z64" s="35" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AA64" s="35" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AB64" s="35" t="str">
         <x:v>A</x:v>
@@ -6808,10 +6808,10 @@
         <x:v>這是判斷「貿易影響」時要使用的依據。貿易會牽動生產、土地和權力，合作、利益與衝突可能同時出現。</x:v>
       </x:c>
       <x:c r="AD64" s="35" t="str">
-        <x:v>這是「行動評估」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境與生活」的重點；本題要判斷的是「貿易影響」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE64" s="35" t="str">
-        <x:v>這項知識屬於「多元資料」，無法支持本題的「貿易影響」判斷。</x:v>
+        <x:v>這項知識屬於「族群衝突」，無法支持本題的「貿易影響」判斷。</x:v>
       </x:c>
       <x:c r="AF64" s="35" t="str">
         <x:v>分析開發案時，列出受益者與承擔成本者。</x:v>
@@ -6852,7 +6852,7 @@
         <x:v>臺灣是不是永遠最漂亮</x:v>
       </x:c>
       <x:c r="L65" s="34" t="str">
-        <x:v>請每人說一個喜歡的顏色</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="M65" s="34" t="str">
         <x:v>A</x:v>
@@ -6876,7 +6876,7 @@
         <x:v>選項和題意關係較弱。提示：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="T65" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="U65" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -6894,10 +6894,10 @@
         <x:v>把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="Z65" s="34" t="str">
-        <x:v>規範與法律的形成及強制力不同</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AA65" s="34" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AB65" s="34" t="str">
         <x:v>A</x:v>
@@ -6906,10 +6906,10 @@
         <x:v>這是判斷「問題形成」時要使用的依據。可探究問題要有地點、時間、變化與資料對象，才能蒐證而不只是表態。</x:v>
       </x:c>
       <x:c r="AD65" s="34" t="str">
-        <x:v>這是「規範與法律」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範變遷」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE65" s="34" t="str">
-        <x:v>這項知識屬於「港市與文化」，無法支持本題的「問題形成」判斷。</x:v>
+        <x:v>這項知識屬於「經濟北移」，無法支持本題的「問題形成」判斷。</x:v>
       </x:c>
       <x:c r="AF65" s="34" t="str">
         <x:v>把校園浪費很多改寫成可測量問題。</x:v>
@@ -6944,13 +6944,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J66" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="K66" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="L66" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="M66" s="34" t="str">
         <x:v>A</x:v>
@@ -6968,13 +6968,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住問題形成的關鍵條件。</x:v>
       </x:c>
       <x:c r="R66" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="S66" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="T66" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="U66" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -6992,10 +6992,10 @@
         <x:v>把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="Z66" s="34" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AA66" s="34" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AB66" s="34" t="str">
         <x:v>A</x:v>
@@ -7004,10 +7004,10 @@
         <x:v>這是判斷「問題形成」時要使用的依據。可探究問題要有地點、時間、變化與資料對象，才能蒐證而不只是表態。</x:v>
       </x:c>
       <x:c r="AD66" s="34" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
+        <x:v>這是「港市與文化」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE66" s="34" t="str">
-        <x:v>這項知識屬於「消費安全」，無法支持本題的「問題形成」判斷。</x:v>
+        <x:v>這項知識屬於「多元觀點」，無法支持本題的「問題形成」判斷。</x:v>
       </x:c>
       <x:c r="AF66" s="34" t="str">
         <x:v>把校園浪費很多改寫成可測量問題。</x:v>
@@ -7042,13 +7042,13 @@
         <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="J67" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="K67" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="L67" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="M67" s="34" t="str">
         <x:v>A</x:v>
@@ -7066,13 +7066,13 @@
         <x:v>證據吻合。選項「聚焦特定海岸、時間與不同觀點」能把問題形成的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R67" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="S67" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="T67" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把大題目縮成可觀察的時空範圍。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「問題形成」。請回看：把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="U67" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7090,10 +7090,10 @@
         <x:v>把大題目縮成可觀察的時空範圍。</x:v>
       </x:c>
       <x:c r="Z67" s="34" t="str">
-        <x:v>海防受重視，建省與建設強化治理</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AA67" s="34" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AB67" s="34" t="str">
         <x:v>A</x:v>
@@ -7102,10 +7102,10 @@
         <x:v>這是判斷「問題形成」時要使用的依據。可探究問題要有地點、時間、變化與資料對象，才能蒐證而不只是表態。</x:v>
       </x:c>
       <x:c r="AD67" s="34" t="str">
-        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費安全」的重點；本題要判斷的是「問題形成」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE67" s="34" t="str">
-        <x:v>這項知識屬於「地圖尺度」，無法支持本題的「問題形成」判斷。</x:v>
+        <x:v>這項知識屬於「規範與法律」，無法支持本題的「問題形成」判斷。</x:v>
       </x:c>
       <x:c r="AF67" s="34" t="str">
         <x:v>把校園浪費很多改寫成可測量問題。</x:v>
@@ -7146,7 +7146,7 @@
         <x:v>只問最支持改建的店家</x:v>
       </x:c>
       <x:c r="L68" s="34" t="str">
-        <x:v>只靠組員的童年記憶</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="M68" s="34" t="str">
         <x:v>A</x:v>
@@ -7170,7 +7170,7 @@
         <x:v>這裡混淆了條件與結論。提示：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="T68" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="U68" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7188,10 +7188,10 @@
         <x:v>來源要涵蓋不同時間與受到影響的人。</x:v>
       </x:c>
       <x:c r="Z68" s="34" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AA68" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="AB68" s="34" t="str">
         <x:v>A</x:v>
@@ -7200,10 +7200,10 @@
         <x:v>這是判斷「多元資料」時要使用的依據。歷史、空間與不同使用者資料能交叉檢查；單一宣傳或立場容易偏誤。</x:v>
       </x:c>
       <x:c r="AD68" s="34" t="str">
-        <x:v>這是「地方轉型」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
+        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE68" s="34" t="str">
-        <x:v>這項知識屬於「能源分類」，無法支持本題的「多元資料」判斷。</x:v>
+        <x:v>這項知識屬於「能源代價」，無法支持本題的「多元資料」判斷。</x:v>
       </x:c>
       <x:c r="AF68" s="34" t="str">
         <x:v>訪談名單刻意納入不同立場。</x:v>
@@ -7238,13 +7238,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J69" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="K69" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="L69" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="M69" s="34" t="str">
         <x:v>A</x:v>
@@ -7262,13 +7262,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把多元資料的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R69" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="S69" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="T69" s="34" t="str">
-        <x:v>焦點放錯了。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="U69" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7286,10 +7286,10 @@
         <x:v>來源要涵蓋不同時間與受到影響的人。</x:v>
       </x:c>
       <x:c r="Z69" s="34" t="str">
-        <x:v>通商壓力、物產與航路共同促成開港</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AA69" s="34" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AB69" s="34" t="str">
         <x:v>A</x:v>
@@ -7298,10 +7298,10 @@
         <x:v>這是判斷「多元資料」時要使用的依據。歷史、空間與不同使用者資料能交叉檢查；單一宣傳或立場容易偏誤。</x:v>
       </x:c>
       <x:c r="AD69" s="34" t="str">
-        <x:v>這是「開港背景」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
+        <x:v>這是「能源分類」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE69" s="34" t="str">
-        <x:v>這項知識屬於「分析權衡」，無法支持本題的「多元資料」判斷。</x:v>
+        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「多元資料」判斷。</x:v>
       </x:c>
       <x:c r="AF69" s="34" t="str">
         <x:v>訪談名單刻意納入不同立場。</x:v>
@@ -7336,13 +7336,13 @@
         <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="J70" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="K70" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="L70" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="M70" s="34" t="str">
         <x:v>A</x:v>
@@ -7360,13 +7360,13 @@
         <x:v>答對了；「結合檔案、觀察與多方訪談」同時保留了多元資料需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R70" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="S70" s="34" t="str">
-        <x:v>焦點放錯了。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="T70" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：來源要涵蓋不同時間與利害關係人。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「多元資料」。請回看：來源要涵蓋不同時間與利害關係人。</x:v>
       </x:c>
       <x:c r="U70" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7384,10 +7384,10 @@
         <x:v>來源要涵蓋不同時間與受到影響的人。</x:v>
       </x:c>
       <x:c r="Z70" s="34" t="str">
-        <x:v>保存證據，再循正式管道申訴</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AA70" s="34" t="str">
-        <x:v>規範可調整，互助目的仍保留</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AB70" s="34" t="str">
         <x:v>A</x:v>
@@ -7396,10 +7396,10 @@
         <x:v>這是判斷「多元資料」時要使用的依據。歷史、空間與不同使用者資料能交叉檢查；單一宣傳或立場容易偏誤。</x:v>
       </x:c>
       <x:c r="AD70" s="34" t="str">
-        <x:v>這是「消費權益」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
+        <x:v>這是「分析權衡」的重點；本題要判斷的是「多元資料」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE70" s="34" t="str">
-        <x:v>這項知識屬於「規範變遷」，無法支持本題的「多元資料」判斷。</x:v>
+        <x:v>這項知識屬於「地方轉型」，無法支持本題的「多元資料」判斷。</x:v>
       </x:c>
       <x:c r="AF70" s="34" t="str">
         <x:v>訪談名單刻意納入不同立場。</x:v>
@@ -7440,7 +7440,7 @@
         <x:v>只看顏色決定可信度</x:v>
       </x:c>
       <x:c r="L71" s="34" t="str">
-        <x:v>截掉標題後讓大家投票</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="M71" s="34" t="str">
         <x:v>A</x:v>
@@ -7464,7 +7464,7 @@
         <x:v>這項判斷忽略重要限制。請想想：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="T71" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先確認圖表四要素。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="U71" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7482,10 +7482,10 @@
         <x:v>先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="Z71" s="34" t="str">
-        <x:v>合作修水圳，訂分水與維修規則</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="AA71" s="34" t="str">
-        <x:v>訂規則、維修配置與歸還責任</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AB71" s="34" t="str">
         <x:v>A</x:v>
@@ -7494,10 +7494,10 @@
         <x:v>這是判斷「圖表判讀」時要使用的依據。圖表外觀會受尺度影響，判斷前必須讀標題、座標、單位和數值。</x:v>
       </x:c>
       <x:c r="AD71" s="34" t="str">
-        <x:v>這是「水利開墾」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
+        <x:v>這是「遷移原因」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE71" s="34" t="str">
-        <x:v>這項知識屬於「共享資源」，無法支持本題的「圖表判讀」判斷。</x:v>
+        <x:v>這項知識屬於「循環經濟」，無法支持本題的「圖表判讀」判斷。</x:v>
       </x:c>
       <x:c r="AF71" s="34" t="str">
         <x:v>看到誇張圖表時，重畫同尺度再比較。</x:v>
@@ -7532,13 +7532,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J72" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="K72" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="L72" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="M72" s="34" t="str">
         <x:v>A</x:v>
@@ -7556,13 +7556,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了圖表判讀需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R72" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先確認圖表四要素。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="S72" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先確認圖表四要素。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="T72" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：先確認圖表四要素。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="U72" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7580,10 +7580,10 @@
         <x:v>先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="Z72" s="34" t="str">
-        <x:v>依地理條件發展能源並評估影響</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AA72" s="34" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="AB72" s="34" t="str">
         <x:v>A</x:v>
@@ -7592,10 +7592,10 @@
         <x:v>這是判斷「圖表判讀」時要使用的依據。圖表外觀會受尺度影響，判斷前必須讀標題、座標、單位和數值。</x:v>
       </x:c>
       <x:c r="AD72" s="34" t="str">
-        <x:v>這是「地理配對」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
+        <x:v>這是「共享資源」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE72" s="34" t="str">
-        <x:v>這項知識屬於「史前證據」，無法支持本題的「圖表判讀」判斷。</x:v>
+        <x:v>這項知識屬於「永續農業」，無法支持本題的「圖表判讀」判斷。</x:v>
       </x:c>
       <x:c r="AF72" s="34" t="str">
         <x:v>看到誇張圖表時，重畫同尺度再比較。</x:v>
@@ -7630,13 +7630,13 @@
         <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="J73" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="K73" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="L73" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="M73" s="34" t="str">
         <x:v>A</x:v>
@@ -7654,13 +7654,13 @@
         <x:v>你的判讀可被查證：核對單位、時間、尺度與原始數值。這正是圖表判讀要比較的核心。</x:v>
       </x:c>
       <x:c r="R73" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先確認圖表四要素。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="S73" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：先確認圖表四要素。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="T73" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：先確認圖表四要素。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「圖表判讀」。請回看：先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="U73" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7678,10 +7678,10 @@
         <x:v>先確認圖表四要素。</x:v>
       </x:c>
       <x:c r="Z73" s="34" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="AA73" s="34" t="str">
-        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AB73" s="34" t="str">
         <x:v>A</x:v>
@@ -7690,10 +7690,10 @@
         <x:v>這是判斷「圖表判讀」時要使用的依據。圖表外觀會受尺度影響，判斷前必須讀標題、座標、單位和數值。</x:v>
       </x:c>
       <x:c r="AD73" s="34" t="str">
-        <x:v>這是「共識與程序」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
+        <x:v>這是「史前證據」的重點；本題要判斷的是「圖表判讀」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE73" s="34" t="str">
-        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「圖表判讀」判斷。</x:v>
+        <x:v>這項知識屬於「水利開墾」，無法支持本題的「圖表判讀」判斷。</x:v>
       </x:c>
       <x:c r="AF73" s="34" t="str">
         <x:v>看到誇張圖表時，重畫同尺度再比較。</x:v>
@@ -7734,7 +7734,7 @@
         <x:v>樣本小所以任何發現都不能寫</x:v>
       </x:c>
       <x:c r="L74" s="34" t="str">
-        <x:v>刪掉人數就能讓結論更有力</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="M74" s="34" t="str">
         <x:v>A</x:v>
@@ -7758,7 +7758,7 @@
         <x:v>焦點放錯了。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="T74" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：問資料能支持到多大的群體。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="U74" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7776,10 +7776,10 @@
         <x:v>問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="Z74" s="34" t="str">
-        <x:v>外力暴露治理不足，促使政策改變</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="AA74" s="34" t="str">
-        <x:v>臺灣是遷徙與交流的中繼點</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AB74" s="34" t="str">
         <x:v>A</x:v>
@@ -7788,10 +7788,10 @@
         <x:v>這是判斷「結論界線」時要使用的依據。結論的範圍不能超過資料；小研究仍有價值，但必須誠實交代限制。</x:v>
       </x:c>
       <x:c r="AD74" s="34" t="str">
-        <x:v>這是「牡丹社事件」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
+        <x:v>這是「電力與生活」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE74" s="34" t="str">
-        <x:v>這項知識屬於「位置與交流」，無法支持本題的「結論界線」判斷。</x:v>
+        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「結論界線」判斷。</x:v>
       </x:c>
       <x:c r="AF74" s="34" t="str">
         <x:v>報告班級調查時標明樣本與日期。</x:v>
@@ -7826,13 +7826,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J75" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="K75" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="L75" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="M75" s="34" t="str">
         <x:v>A</x:v>
@@ -7850,13 +7850,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是結論界線要比較的核心。</x:v>
       </x:c>
       <x:c r="R75" s="34" t="str">
-        <x:v>焦點放錯了。請回看：問資料能支持到多大的群體。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="S75" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：問資料能支持到多大的群體。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="T75" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：問資料能支持到多大的群體。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="U75" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7874,10 +7874,10 @@
         <x:v>問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="Z75" s="34" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AA75" s="34" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="AB75" s="34" t="str">
         <x:v>A</x:v>
@@ -7886,10 +7886,10 @@
         <x:v>這是判斷「結論界線」時要使用的依據。結論的範圍不能超過資料；小研究仍有價值，但必須誠實交代限制。</x:v>
       </x:c>
       <x:c r="AD75" s="34" t="str">
-        <x:v>這是「循環經濟」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
+        <x:v>這是「位置與交流」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE75" s="34" t="str">
-        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「結論界線」判斷。</x:v>
+        <x:v>這項知識屬於「時序空間」，無法支持本題的「結論界線」判斷。</x:v>
       </x:c>
       <x:c r="AF75" s="34" t="str">
         <x:v>報告班級調查時標明樣本與日期。</x:v>
@@ -7924,13 +7924,13 @@
         <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="J76" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="K76" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="L76" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="M76" s="34" t="str">
         <x:v>A</x:v>
@@ -7948,13 +7948,13 @@
         <x:v>判斷精準。「限定結論範圍並說明調查限制」直接回應結論界線，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R76" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：問資料能支持到多大的群體。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="S76" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：問資料能支持到多大的群體。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="T76" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問資料能支持到多大的群體。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「結論界線」。請回看：問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="U76" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -7972,10 +7972,10 @@
         <x:v>問資料能支持到多大的群體。</x:v>
       </x:c>
       <x:c r="Z76" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AA76" s="34" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AB76" s="34" t="str">
         <x:v>A</x:v>
@@ -7984,10 +7984,10 @@
         <x:v>這是判斷「結論界線」時要使用的依據。結論的範圍不能超過資料；小研究仍有價值，但必須誠實交代限制。</x:v>
       </x:c>
       <x:c r="AD76" s="34" t="str">
-        <x:v>這是「文化多樣性」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
+        <x:v>這是「地方轉型」的重點；本題要判斷的是「結論界線」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE76" s="34" t="str">
-        <x:v>這項知識屬於「遷移原因」，無法支持本題的「結論界線」判斷。</x:v>
+        <x:v>這項知識屬於「能源分類」，無法支持本題的「結論界線」判斷。</x:v>
       </x:c>
       <x:c r="AF76" s="34" t="str">
         <x:v>報告班級調查時標明樣本與日期。</x:v>
@@ -8028,7 +8028,7 @@
         <x:v>宣布問題無法解決並停止記錄</x:v>
       </x:c>
       <x:c r="L77" s="34" t="str">
-        <x:v>責怪沒受訪的人不配合</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="M77" s="34" t="str">
         <x:v>A</x:v>
@@ -8052,7 +8052,7 @@
         <x:v>這項推論缺少證據。請確認：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="T77" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="U77" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -8070,10 +8070,10 @@
         <x:v>找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="Z77" s="34" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="AA77" s="34" t="str">
-        <x:v>規範與法律的形成及強制力不同</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AB77" s="34" t="str">
         <x:v>A</x:v>
@@ -8082,10 +8082,10 @@
         <x:v>這是判斷「行動省思」時要使用的依據。探究是循環歷程，未達標也是資料；依紀錄修正比美化或放棄更能改進。</x:v>
       </x:c>
       <x:c r="AD77" s="34" t="str">
-        <x:v>這是「消費安全」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
+        <x:v>這是「理財風險」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE77" s="34" t="str">
-        <x:v>這項知識屬於「規範與法律」，無法支持本題的「行動省思」判斷。</x:v>
+        <x:v>這項知識屬於「權利權衡」，無法支持本題的「行動省思」判斷。</x:v>
       </x:c>
       <x:c r="AF77" s="34" t="str">
         <x:v>活動後用同一指標比較並記錄修改理由。</x:v>
@@ -8120,13 +8120,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J78" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="K78" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="L78" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="M78" s="34" t="str">
         <x:v>A</x:v>
@@ -8144,13 +8144,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應行動省思，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R78" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="S78" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="T78" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="U78" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -8168,10 +8168,10 @@
         <x:v>找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="Z78" s="34" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AA78" s="34" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AB78" s="34" t="str">
         <x:v>A</x:v>
@@ -8180,10 +8180,10 @@
         <x:v>這是判斷「行動省思」時要使用的依據。探究是循環歷程，未達標也是資料；依紀錄修正比美化或放棄更能改進。</x:v>
       </x:c>
       <x:c r="AD78" s="34" t="str">
-        <x:v>這是「地圖尺度」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範與法律」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE78" s="34" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「行動省思」判斷。</x:v>
+        <x:v>這項知識屬於「港市與文化」，無法支持本題的「行動省思」判斷。</x:v>
       </x:c>
       <x:c r="AF78" s="34" t="str">
         <x:v>活動後用同一指標比較並記錄修改理由。</x:v>
@@ -8218,13 +8218,13 @@
         <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="J79" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="K79" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="L79" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="M79" s="34" t="str">
         <x:v>A</x:v>
@@ -8242,13 +8242,13 @@
         <x:v>這項選擇成立：查紀錄、調方法，再用同指標測量。它抓住行動省思的關鍵條件。</x:v>
       </x:c>
       <x:c r="R79" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="S79" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="T79" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：找出哪個環節沒做到，再設新一輪檢查。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「行動省思」。請回看：找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="U79" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -8266,10 +8266,10 @@
         <x:v>找出哪個環節沒做到，再設新一輪檢查。</x:v>
       </x:c>
       <x:c r="Z79" s="34" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AA79" s="34" t="str">
-        <x:v>海防受重視，建省與建設強化治理</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB79" s="34" t="str">
         <x:v>A</x:v>
@@ -8278,10 +8278,10 @@
         <x:v>這是判斷「行動省思」時要使用的依據。探究是循環歷程，未達標也是資料；依紀錄修正比美化或放棄更能改進。</x:v>
       </x:c>
       <x:c r="AD79" s="34" t="str">
-        <x:v>這是「永續漁業」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
+        <x:v>這是「水利開墾」的重點；本題要判斷的是「行動省思」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE79" s="34" t="str">
-        <x:v>這項知識屬於「清法戰爭與建省」，無法支持本題的「行動省思」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「行動省思」判斷。</x:v>
       </x:c>
       <x:c r="AF79" s="34" t="str">
         <x:v>活動後用同一指標比較並記錄修改理由。</x:v>
@@ -8322,7 +8322,7 @@
         <x:v>有季風就不需船員經驗</x:v>
       </x:c>
       <x:c r="L80" s="35" t="str">
-        <x:v>季風只影響農作，和航海無關</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="M80" s="35" t="str">
         <x:v>A</x:v>
@@ -8346,7 +8346,7 @@
         <x:v>選項和題意關係較弱。提示：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="T80" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把船的動力和風向連起來。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="U80" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8364,10 +8364,10 @@
         <x:v>把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="Z80" s="35" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AA80" s="35" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB80" s="35" t="str">
         <x:v>A</x:v>
@@ -8376,10 +8376,10 @@
         <x:v>這是判斷「移民與季風」時要使用的依據。帆船依賴風力，季節風向會改變航路條件；船況、海象與經驗仍影響安全。</x:v>
       </x:c>
       <x:c r="AD80" s="35" t="str">
-        <x:v>這是「問題形成」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元資料」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE80" s="35" t="str">
-        <x:v>這項知識屬於「理財風險」，無法支持本題的「移民與季風」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「移民與季風」判斷。</x:v>
       </x:c>
       <x:c r="AF80" s="35" t="str">
         <x:v>海上活動要依預報評估而非只看日期。</x:v>
@@ -8414,13 +8414,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J81" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="K81" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="L81" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="M81" s="35" t="str">
         <x:v>A</x:v>
@@ -8438,13 +8438,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住移民與季風的關鍵條件。</x:v>
       </x:c>
       <x:c r="R81" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：把船的動力和風向連起來。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="S81" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把船的動力和風向連起來。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="T81" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把船的動力和風向連起來。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="U81" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8462,10 +8462,10 @@
         <x:v>把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="Z81" s="35" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="AA81" s="35" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AB81" s="35" t="str">
         <x:v>A</x:v>
@@ -8474,10 +8474,10 @@
         <x:v>這是判斷「移民與季風」時要使用的依據。帆船依賴風力，季節風向會改變航路條件；船況、海象與經驗仍影響安全。</x:v>
       </x:c>
       <x:c r="AD81" s="35" t="str">
-        <x:v>這是「能源分類」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
+        <x:v>這是「理財風險」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE81" s="35" t="str">
-        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「移民與季風」判斷。</x:v>
+        <x:v>這項知識屬於「權利權衡」，無法支持本題的「移民與季風」判斷。</x:v>
       </x:c>
       <x:c r="AF81" s="35" t="str">
         <x:v>海上活動要依預報評估而非只看日期。</x:v>
@@ -8512,13 +8512,13 @@
         <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="J82" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="K82" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="L82" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="M82" s="35" t="str">
         <x:v>A</x:v>
@@ -8536,13 +8536,13 @@
         <x:v>證據吻合。選項「季風影響航程與風險，但不保證安全」能把移民與季風的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R82" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把船的動力和風向連起來。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="S82" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把船的動力和風向連起來。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="T82" s="35" t="str">
-        <x:v>焦點放錯了。請回看：把船的動力和風向連起來。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「移民與季風」。請回看：把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="U82" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8560,10 +8560,10 @@
         <x:v>把船的動力和風向連起來。</x:v>
       </x:c>
       <x:c r="Z82" s="35" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AA82" s="35" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB82" s="35" t="str">
         <x:v>A</x:v>
@@ -8572,10 +8572,10 @@
         <x:v>這是判斷「移民與季風」時要使用的依據。帆船依賴風力，季節風向會改變航路條件；船況、海象與經驗仍影響安全。</x:v>
       </x:c>
       <x:c r="AD82" s="35" t="str">
-        <x:v>這是「分析權衡」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
+        <x:v>這是「海岸變遷」的重點；本題要判斷的是「移民與季風」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE82" s="35" t="str">
-        <x:v>這項知識屬於「地方轉型」，無法支持本題的「移民與季風」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「移民與季風」判斷。</x:v>
       </x:c>
       <x:c r="AF82" s="35" t="str">
         <x:v>海上活動要依預報評估而非只看日期。</x:v>
@@ -8616,7 +8616,7 @@
         <x:v>每戶各自搶水，不必協調</x:v>
       </x:c>
       <x:c r="L83" s="35" t="str">
-        <x:v>工程完成後永遠不需管理</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="M83" s="35" t="str">
         <x:v>A</x:v>
@@ -8640,7 +8640,7 @@
         <x:v>這裡混淆了條件與結論。提示：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="T83" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：工程和共同管理缺一不可。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="U83" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8658,10 +8658,10 @@
         <x:v>工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="Z83" s="35" t="str">
-        <x:v>比較具體貢獻、限制與在地回應</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="AA83" s="35" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="AB83" s="35" t="str">
         <x:v>A</x:v>
@@ -8670,10 +8670,10 @@
         <x:v>這是判斷「水利開墾」時要使用的依據。水利工程可調節水量，但跨越多人土地，必須持續分配、維修並處理洪旱。</x:v>
       </x:c>
       <x:c r="AD83" s="35" t="str">
-        <x:v>這是「人物與交流」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
+        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE83" s="35" t="str">
-        <x:v>這項知識屬於「行動評估」，無法支持本題的「水利開墾」判斷。</x:v>
+        <x:v>這項知識屬於「地圖尺度」，無法支持本題的「水利開墾」判斷。</x:v>
       </x:c>
       <x:c r="AF83" s="35" t="str">
         <x:v>共用設備也要約定使用和維護責任。</x:v>
@@ -8708,13 +8708,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J84" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="K84" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="L84" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="M84" s="35" t="str">
         <x:v>A</x:v>
@@ -8732,13 +8732,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把水利開墾的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R84" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：工程和共同管理缺一不可。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="S84" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：工程和共同管理缺一不可。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="T84" s="35" t="str">
-        <x:v>焦點放錯了。請回看：工程和共同管理缺一不可。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="U84" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8756,10 +8756,10 @@
         <x:v>工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="Z84" s="35" t="str">
-        <x:v>訂規則、維修配置與歸還責任</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="AA84" s="35" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="AB84" s="35" t="str">
         <x:v>A</x:v>
@@ -8768,10 +8768,10 @@
         <x:v>這是判斷「水利開墾」時要使用的依據。水利工程可調節水量，但跨越多人土地，必須持續分配、維修並處理洪旱。</x:v>
       </x:c>
       <x:c r="AD84" s="35" t="str">
-        <x:v>這是「共享資源」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
+        <x:v>這是「行動評估」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE84" s="35" t="str">
-        <x:v>這項知識屬於「永續農業」，無法支持本題的「水利開墾」判斷。</x:v>
+        <x:v>這項知識屬於「航海動機」，無法支持本題的「水利開墾」判斷。</x:v>
       </x:c>
       <x:c r="AF84" s="35" t="str">
         <x:v>共用設備也要約定使用和維護責任。</x:v>
@@ -8806,13 +8806,13 @@
         <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="J85" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="K85" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="L85" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="M85" s="35" t="str">
         <x:v>A</x:v>
@@ -8830,13 +8830,13 @@
         <x:v>答對了；「合作修水圳，訂分水與維修規則」同時保留了水利開墾需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R85" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：工程和共同管理缺一不可。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="S85" s="35" t="str">
-        <x:v>焦點放錯了。請回看：工程和共同管理缺一不可。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="T85" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：工程和共同管理缺一不可。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「水利開墾」。請回看：工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="U85" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8854,10 +8854,10 @@
         <x:v>工程和共同管理缺一不可。</x:v>
       </x:c>
       <x:c r="Z85" s="35" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AA85" s="35" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="AB85" s="35" t="str">
         <x:v>A</x:v>
@@ -8866,10 +8866,10 @@
         <x:v>這是判斷「水利開墾」時要使用的依據。水利工程可調節水量，但跨越多人土地，必須持續分配、維修並處理洪旱。</x:v>
       </x:c>
       <x:c r="AD85" s="35" t="str">
-        <x:v>這是「史前證據」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
+        <x:v>這是「森林供應鏈」的重點；本題要判斷的是「水利開墾」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE85" s="35" t="str">
-        <x:v>這項知識屬於「多元資料」，無法支持本題的「水利開墾」判斷。</x:v>
+        <x:v>這項知識屬於「電力與生活」，無法支持本題的「水利開墾」判斷。</x:v>
       </x:c>
       <x:c r="AF85" s="35" t="str">
         <x:v>共用設備也要約定使用和維護責任。</x:v>
@@ -8910,7 +8910,7 @@
         <x:v>移民都不知道海上有危險</x:v>
       </x:c>
       <x:c r="L86" s="35" t="str">
-        <x:v>每個人的移民目的完全相同</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="M86" s="35" t="str">
         <x:v>A</x:v>
@@ -8934,7 +8934,7 @@
         <x:v>這項判斷忽略重要限制。請想想：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="T86" s="35" t="str">
-        <x:v>焦點放錯了。請回看：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="U86" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -8952,10 +8952,10 @@
         <x:v>從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="Z86" s="35" t="str">
-        <x:v>風險分配與居民參與需要公平</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AA86" s="35" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AB86" s="35" t="str">
         <x:v>A</x:v>
@@ -8964,10 +8964,10 @@
         <x:v>這是判斷「遷移原因」時要使用的依據。人口移動同時受推力、拉力與制度約束，限制並不等於完全阻止。</x:v>
       </x:c>
       <x:c r="AD86" s="35" t="str">
-        <x:v>這是「環境正義」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費權益」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE86" s="35" t="str">
-        <x:v>這項知識屬於「環境與生活」，無法支持本題的「遷移原因」判斷。</x:v>
+        <x:v>這項知識屬於「規範變遷」，無法支持本題的「遷移原因」判斷。</x:v>
       </x:c>
       <x:c r="AF86" s="35" t="str">
         <x:v>分析人口移動時避免只用單一原因。</x:v>
@@ -9002,13 +9002,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J87" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="K87" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="L87" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="M87" s="35" t="str">
         <x:v>A</x:v>
@@ -9026,13 +9026,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了遷移原因需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R87" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="S87" s="35" t="str">
-        <x:v>焦點放錯了。請回看：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="T87" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="U87" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9050,10 +9050,10 @@
         <x:v>從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="Z87" s="35" t="str">
-        <x:v>臺灣是遷徙與交流的中繼點</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AA87" s="35" t="str">
-        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="AB87" s="35" t="str">
         <x:v>A</x:v>
@@ -9062,10 +9062,10 @@
         <x:v>這是判斷「遷移原因」時要使用的依據。人口移動同時受推力、拉力與制度約束，限制並不等於完全阻止。</x:v>
       </x:c>
       <x:c r="AD87" s="35" t="str">
-        <x:v>這是「位置與交流」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
+        <x:v>這是「環境與生活」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE87" s="35" t="str">
-        <x:v>這項知識屬於「時序空間」，無法支持本題的「遷移原因」判斷。</x:v>
+        <x:v>這項知識屬於「結論界線」，無法支持本題的「遷移原因」判斷。</x:v>
       </x:c>
       <x:c r="AF87" s="35" t="str">
         <x:v>分析人口移動時避免只用單一原因。</x:v>
@@ -9100,13 +9100,13 @@
         <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="J88" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="K88" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="L88" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="M88" s="35" t="str">
         <x:v>A</x:v>
@@ -9124,13 +9124,13 @@
         <x:v>你的判讀可被查證：生活、機會與政策共同影響移動。這正是遷移原因要比較的核心。</x:v>
       </x:c>
       <x:c r="R88" s="35" t="str">
-        <x:v>焦點放錯了。請回看：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="S88" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="T88" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：從原鄉、目的地和政策三面向想。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「遷移原因」。請回看：從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="U88" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9148,10 +9148,10 @@
         <x:v>從原鄉、目的地和政策三面向想。</x:v>
       </x:c>
       <x:c r="Z88" s="35" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AA88" s="35" t="str">
-        <x:v>外力暴露治理不足，促使政策改變</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="AB88" s="35" t="str">
         <x:v>A</x:v>
@@ -9160,10 +9160,10 @@
         <x:v>這是判斷「遷移原因」時要使用的依據。人口移動同時受推力、拉力與制度約束，限制並不等於完全阻止。</x:v>
       </x:c>
       <x:c r="AD88" s="35" t="str">
-        <x:v>這是「畜牧權衡」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
+        <x:v>這是「問題形成」的重點；本題要判斷的是「遷移原因」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE88" s="35" t="str">
-        <x:v>這項知識屬於「牡丹社事件」，無法支持本題的「遷移原因」判斷。</x:v>
+        <x:v>這項知識屬於「理財風險」，無法支持本題的「遷移原因」判斷。</x:v>
       </x:c>
       <x:c r="AF88" s="35" t="str">
         <x:v>分析人口移動時避免只用單一原因。</x:v>
@@ -9204,7 +9204,7 @@
         <x:v>所有衝突都由天氣造成</x:v>
       </x:c>
       <x:c r="L89" s="35" t="str">
-        <x:v>群體名稱本身就是完整原因</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="M89" s="35" t="str">
         <x:v>A</x:v>
@@ -9228,7 +9228,7 @@
         <x:v>焦點放錯了。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="T89" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="U89" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9246,10 +9246,10 @@
         <x:v>追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="Z89" s="35" t="str">
-        <x:v>訪談多方並搭配噪音與發電資料</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="AA89" s="35" t="str">
-        <x:v>查明進口木材是否來自永續來源</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AB89" s="35" t="str">
         <x:v>A</x:v>
@@ -9258,10 +9258,10 @@
         <x:v>這是判斷「族群衝突」時要使用的依據。社會衝突常涉及資源、制度和權力，情緒標籤會遮蔽真正的時空脈絡。</x:v>
       </x:c>
       <x:c r="AD89" s="35" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
+        <x:v>這是「共識與程序」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE89" s="35" t="str">
-        <x:v>這項知識屬於「森林供應鏈」，無法支持本題的「族群衝突」判斷。</x:v>
+        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「族群衝突」判斷。</x:v>
       </x:c>
       <x:c r="AF89" s="35" t="str">
         <x:v>處理校園衝突時，也釐清資源與溝通機制。</x:v>
@@ -9296,13 +9296,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J90" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="K90" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="L90" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="M90" s="35" t="str">
         <x:v>A</x:v>
@@ -9320,13 +9320,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是族群衝突要比較的核心。</x:v>
       </x:c>
       <x:c r="R90" s="35" t="str">
-        <x:v>焦點放錯了。請回看：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="S90" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="T90" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="U90" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9344,10 +9344,10 @@
         <x:v>追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="Z90" s="35" t="str">
-        <x:v>規範與法律的形成及強制力不同</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="AA90" s="35" t="str">
-        <x:v>查紀錄、調方法，再用同指標測量</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="AB90" s="35" t="str">
         <x:v>A</x:v>
@@ -9356,10 +9356,10 @@
         <x:v>這是判斷「族群衝突」時要使用的依據。社會衝突常涉及資源、制度和權力，情緒標籤會遮蔽真正的時空脈絡。</x:v>
       </x:c>
       <x:c r="AD90" s="35" t="str">
-        <x:v>這是「規範與法律」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
+        <x:v>這是「航海動機」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE90" s="35" t="str">
-        <x:v>這項知識屬於「行動省思」，無法支持本題的「族群衝突」判斷。</x:v>
+        <x:v>這項知識屬於「能源代價」，無法支持本題的「族群衝突」判斷。</x:v>
       </x:c>
       <x:c r="AF90" s="35" t="str">
         <x:v>處理校園衝突時，也釐清資源與溝通機制。</x:v>
@@ -9394,13 +9394,13 @@
         <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="J91" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="K91" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="L91" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="M91" s="35" t="str">
         <x:v>A</x:v>
@@ -9418,13 +9418,13 @@
         <x:v>判斷精準。「分析資源、語言、組織與治理」直接回應族群衝突，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R91" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="S91" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="T91" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：追問爭什麼資源、規則由誰決定。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「族群衝突」。請回看：追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="U91" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9442,10 +9442,10 @@
         <x:v>追問爭什麼資源、規則由誰決定。</x:v>
       </x:c>
       <x:c r="Z91" s="35" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="AA91" s="35" t="str">
-        <x:v>停止交易並改用官方查證與付款</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="AB91" s="35" t="str">
         <x:v>A</x:v>
@@ -9454,10 +9454,10 @@
         <x:v>這是判斷「族群衝突」時要使用的依據。社會衝突常涉及資源、制度和權力，情緒標籤會遮蔽真正的時空脈絡。</x:v>
       </x:c>
       <x:c r="AD91" s="35" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
+        <x:v>這是「人物與交流」的重點；本題要判斷的是「族群衝突」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE91" s="35" t="str">
-        <x:v>這項知識屬於「消費安全」，無法支持本題的「族群衝突」判斷。</x:v>
+        <x:v>這項知識屬於「行動評估」，無法支持本題的「族群衝突」判斷。</x:v>
       </x:c>
       <x:c r="AF91" s="35" t="str">
         <x:v>處理校園衝突時，也釐清資源與溝通機制。</x:v>
@@ -9498,7 +9498,7 @@
         <x:v>港市繁榮後永遠不會轉移</x:v>
       </x:c>
       <x:c r="L92" s="35" t="str">
-        <x:v>教育擴展只會有好處且人人相同</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="M92" s="35" t="str">
         <x:v>A</x:v>
@@ -9522,7 +9522,7 @@
         <x:v>這項推論缺少證據。請確認：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="T92" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="U92" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9540,10 +9540,10 @@
         <x:v>同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="Z92" s="35" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AA92" s="35" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB92" s="35" t="str">
         <x:v>A</x:v>
@@ -9552,10 +9552,10 @@
         <x:v>這是判斷「港市與文化」時要使用的依據。港市與制度發展帶來交流和機會，也可能改變族群土地、語言與權力。</x:v>
       </x:c>
       <x:c r="AD92" s="35" t="str">
-        <x:v>這是「海岸變遷」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
+        <x:v>這是「文化多樣性」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE92" s="35" t="str">
-        <x:v>這項知識屬於「問題形成」，無法支持本題的「港市與文化」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「港市與文化」判斷。</x:v>
       </x:c>
       <x:c r="AF92" s="35" t="str">
         <x:v>地方俗語要放回形成的年代與條件。</x:v>
@@ -9590,13 +9590,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J93" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="K93" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="L93" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="M93" s="35" t="str">
         <x:v>A</x:v>
@@ -9614,13 +9614,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應港市與文化，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R93" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="S93" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="T93" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="U93" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9638,10 +9638,10 @@
         <x:v>同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="Z93" s="35" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="AA93" s="35" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="AB93" s="35" t="str">
         <x:v>A</x:v>
@@ -9650,10 +9650,10 @@
         <x:v>這是判斷「港市與文化」時要使用的依據。港市與制度發展帶來交流和機會，也可能改變族群土地、語言與權力。</x:v>
       </x:c>
       <x:c r="AD93" s="35" t="str">
-        <x:v>這是「地方轉型」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
+        <x:v>這是「結論界線」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE93" s="35" t="str">
-        <x:v>這項知識屬於「能源分類」，無法支持本題的「港市與文化」判斷。</x:v>
+        <x:v>這項知識屬於「能源提問」，無法支持本題的「港市與文化」判斷。</x:v>
       </x:c>
       <x:c r="AF93" s="35" t="str">
         <x:v>地方俗語要放回形成的年代與條件。</x:v>
@@ -9688,13 +9688,13 @@
         <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="J94" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="K94" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="L94" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="M94" s="35" t="str">
         <x:v>A</x:v>
@@ -9712,13 +9712,13 @@
         <x:v>這項選擇成立：港市帶動文化，但各族群影響不同。它抓住港市與文化的關鍵條件。</x:v>
       </x:c>
       <x:c r="R94" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="S94" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="T94" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：同時看經濟成長與不同群體經驗。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「港市與文化」。請回看：同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="U94" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -9736,10 +9736,10 @@
         <x:v>同時看經濟成長與不同群體經驗。</x:v>
       </x:c>
       <x:c r="Z94" s="35" t="str">
-        <x:v>通商壓力、物產與航路共同促成開港</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AA94" s="35" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AB94" s="35" t="str">
         <x:v>A</x:v>
@@ -9748,10 +9748,10 @@
         <x:v>這是判斷「港市與文化」時要使用的依據。港市與制度發展帶來交流和機會，也可能改變族群土地、語言與權力。</x:v>
       </x:c>
       <x:c r="AD94" s="35" t="str">
-        <x:v>這是「開港背景」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
+        <x:v>這是「能源分類」的重點；本題要判斷的是「港市與文化」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE94" s="35" t="str">
-        <x:v>這項知識屬於「分析權衡」，無法支持本題的「港市與文化」判斷。</x:v>
+        <x:v>這項知識屬於「環境與生活」，無法支持本題的「港市與文化」判斷。</x:v>
       </x:c>
       <x:c r="AF94" s="35" t="str">
         <x:v>地方俗語要放回形成的年代與條件。</x:v>
@@ -9792,7 +9792,7 @@
         <x:v>因臺灣主動停止所有貿易</x:v>
       </x:c>
       <x:c r="L95" s="34" t="str">
-        <x:v>因北部沒有茶與樟腦</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="M95" s="34" t="str">
         <x:v>A</x:v>
@@ -9816,7 +9816,7 @@
         <x:v>選項和題意關係較弱。提示：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="T95" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="U95" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -9834,10 +9834,10 @@
         <x:v>從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="Z95" s="34" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AA95" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AB95" s="34" t="str">
         <x:v>A</x:v>
@@ -9846,10 +9846,10 @@
         <x:v>這是判斷「開港背景」時要使用的依據。開港牽涉國際政治、商品需求與交通位置，不能用單一技術或錯誤物產解釋。</x:v>
       </x:c>
       <x:c r="AD95" s="34" t="str">
-        <x:v>這是「能源代價」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費安全」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE95" s="34" t="str">
-        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「開港背景」判斷。</x:v>
+        <x:v>這項知識屬於「規範與法律」，無法支持本題的「開港背景」判斷。</x:v>
       </x:c>
       <x:c r="AF95" s="34" t="str">
         <x:v>分析市場開放時區分外力與地方條件。</x:v>
@@ -9884,13 +9884,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J96" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="K96" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="L96" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="M96" s="34" t="str">
         <x:v>A</x:v>
@@ -9908,13 +9908,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住開港背景的關鍵條件。</x:v>
       </x:c>
       <x:c r="R96" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="S96" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="T96" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="U96" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -9932,10 +9932,10 @@
         <x:v>從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="Z96" s="34" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AA96" s="34" t="str">
-        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB96" s="34" t="str">
         <x:v>A</x:v>
@@ -9944,10 +9944,10 @@
         <x:v>這是判斷「開港背景」時要使用的依據。開港牽涉國際政治、商品需求與交通位置，不能用單一技術或錯誤物產解釋。</x:v>
       </x:c>
       <x:c r="AD96" s="34" t="str">
-        <x:v>這是「行動評估」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
+        <x:v>這是「文化多樣性」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE96" s="34" t="str">
-        <x:v>這項知識屬於「航海動機」，無法支持本題的「開港背景」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「開港背景」判斷。</x:v>
       </x:c>
       <x:c r="AF96" s="34" t="str">
         <x:v>分析市場開放時區分外力與地方條件。</x:v>
@@ -9982,13 +9982,13 @@
         <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="J97" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="K97" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="L97" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="M97" s="34" t="str">
         <x:v>A</x:v>
@@ -10006,13 +10006,13 @@
         <x:v>證據吻合。選項「通商壓力、物產與航路共同促成開港」能把開港背景的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R97" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="S97" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="T97" s="34" t="str">
-        <x:v>焦點放錯了。請回看：從外部壓力、商品和位置三面向想。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「開港背景」。請回看：從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="U97" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10030,10 +10030,10 @@
         <x:v>從外部壓力、商品和位置三面向想。</x:v>
       </x:c>
       <x:c r="Z97" s="34" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AA97" s="34" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AB97" s="34" t="str">
         <x:v>A</x:v>
@@ -10042,10 +10042,10 @@
         <x:v>這是判斷「開港背景」時要使用的依據。開港牽涉國際政治、商品需求與交通位置，不能用單一技術或錯誤物產解釋。</x:v>
       </x:c>
       <x:c r="AD97" s="34" t="str">
-        <x:v>這是「永續農業」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
+        <x:v>這是「貿易影響」的重點；本題要判斷的是「開港背景」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE97" s="34" t="str">
-        <x:v>這項知識屬於「遷移原因」，無法支持本題的「開港背景」判斷。</x:v>
+        <x:v>這項知識屬於「消費權益」，無法支持本題的「開港背景」判斷。</x:v>
       </x:c>
       <x:c r="AF97" s="34" t="str">
         <x:v>分析市場開放時區分外力與地方條件。</x:v>
@@ -10086,7 +10086,7 @@
         <x:v>北部土地突然變得最大</x:v>
       </x:c>
       <x:c r="L98" s="34" t="str">
-        <x:v>只因行政名稱改變</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="M98" s="34" t="str">
         <x:v>A</x:v>
@@ -10110,7 +10110,7 @@
         <x:v>這裡混淆了條件與結論。提示：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="T98" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="U98" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10128,10 +10128,10 @@
         <x:v>連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="Z98" s="34" t="str">
-        <x:v>比較設置前後的發電、用電與環境</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AA98" s="34" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AB98" s="34" t="str">
         <x:v>A</x:v>
@@ -10140,10 +10140,10 @@
         <x:v>這是判斷「經濟北移」時要使用的依據。商品產地、運輸出口與城市成長形成因果鏈；重心轉移是逐步過程。</x:v>
       </x:c>
       <x:c r="AD98" s="34" t="str">
-        <x:v>這是「能源提問」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
+        <x:v>這是「分析權衡」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE98" s="34" t="str">
-        <x:v>這項知識屬於「永續漁業」，無法支持本題的「經濟北移」判斷。</x:v>
+        <x:v>這項知識屬於「地方轉型」，無法支持本題的「經濟北移」判斷。</x:v>
       </x:c>
       <x:c r="AF98" s="34" t="str">
         <x:v>解釋商圈興起時，也找主要產業與交通。</x:v>
@@ -10178,13 +10178,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J99" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="K99" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="L99" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="M99" s="34" t="str">
         <x:v>A</x:v>
@@ -10202,13 +10202,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把經濟北移的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R99" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="S99" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="T99" s="34" t="str">
-        <x:v>焦點放錯了。請回看：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="U99" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10226,10 +10226,10 @@
         <x:v>連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="Z99" s="34" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AA99" s="34" t="str">
-        <x:v>限定結論範圍並說明調查限制</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AB99" s="34" t="str">
         <x:v>A</x:v>
@@ -10238,10 +10238,10 @@
         <x:v>這是判斷「經濟北移」時要使用的依據。商品產地、運輸出口與城市成長形成因果鏈；重心轉移是逐步過程。</x:v>
       </x:c>
       <x:c r="AD99" s="34" t="str">
-        <x:v>這是「環境與生活」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
+        <x:v>這是「地方轉型」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE99" s="34" t="str">
-        <x:v>這項知識屬於「結論界線」，無法支持本題的「經濟北移」判斷。</x:v>
+        <x:v>這項知識屬於「能源分類」，無法支持本題的「經濟北移」判斷。</x:v>
       </x:c>
       <x:c r="AF99" s="34" t="str">
         <x:v>解釋商圈興起時，也找主要產業與交通。</x:v>
@@ -10276,13 +10276,13 @@
         <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="J100" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="K100" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="L100" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="M100" s="34" t="str">
         <x:v>A</x:v>
@@ -10300,13 +10300,13 @@
         <x:v>答對了；「商品與港口帶動北部市鎮發展」同時保留了經濟北移需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R100" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="S100" s="34" t="str">
-        <x:v>焦點放錯了。請回看：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="T100" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：連結商品、產地、港口和市鎮。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「經濟北移」。請回看：連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="U100" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10324,10 +10324,10 @@
         <x:v>連結商品、產地、港口和市鎮。</x:v>
       </x:c>
       <x:c r="Z100" s="34" t="str">
-        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AA100" s="34" t="str">
-        <x:v>風險分配與居民參與需要公平</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="AB100" s="34" t="str">
         <x:v>A</x:v>
@@ -10336,10 +10336,10 @@
         <x:v>這是判斷「經濟北移」時要使用的依據。商品產地、運輸出口與城市成長形成因果鏈；重心轉移是逐步過程。</x:v>
       </x:c>
       <x:c r="AD100" s="34" t="str">
-        <x:v>這是「時序空間」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
+        <x:v>這是「水利開墾」的重點；本題要判斷的是「經濟北移」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE100" s="34" t="str">
-        <x:v>這項知識屬於「環境正義」，無法支持本題的「經濟北移」判斷。</x:v>
+        <x:v>這項知識屬於「共識與程序」，無法支持本題的「經濟北移」判斷。</x:v>
       </x:c>
       <x:c r="AF100" s="34" t="str">
         <x:v>解釋商圈興起時，也找主要產業與交通。</x:v>
@@ -10380,7 +10380,7 @@
         <x:v>只歌頌貢獻而不查受影響者</x:v>
       </x:c>
       <x:c r="L101" s="34" t="str">
-        <x:v>因是外國人就否定全部成果</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="M101" s="34" t="str">
         <x:v>A</x:v>
@@ -10404,7 +10404,7 @@
         <x:v>這項判斷忽略重要限制。請想想：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="T101" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先辨身分與行動，再談影響。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="U101" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10422,10 +10422,10 @@
         <x:v>先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="Z101" s="34" t="str">
-        <x:v>板塊交界造成多山與地震</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="AA101" s="34" t="str">
-        <x:v>貿易增加，也改變土地與族群關係</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AB101" s="34" t="str">
         <x:v>A</x:v>
@@ -10434,10 +10434,10 @@
         <x:v>這是判斷「人物與交流」時要使用的依據。人物行動各異，歷史評估既要看具體貢獻，也不能忽略目的、限制和在地回應。</x:v>
       </x:c>
       <x:c r="AD101" s="34" t="str">
-        <x:v>這是「板塊與地形」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
+        <x:v>這是「史前證據」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE101" s="34" t="str">
-        <x:v>這項知識屬於「貿易影響」，無法支持本題的「人物與交流」判斷。</x:v>
+        <x:v>這項知識屬於「多元資料」，無法支持本題的「人物與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF101" s="34" t="str">
         <x:v>人物報告要以事蹟和多方資料支持。</x:v>
@@ -10472,13 +10472,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J102" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="K102" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="L102" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="M102" s="34" t="str">
         <x:v>A</x:v>
@@ -10496,13 +10496,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了人物與交流需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R102" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先辨身分與行動，再談影響。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="S102" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先辨身分與行動，再談影響。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="T102" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：先辨身分與行動，再談影響。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="U102" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10520,10 +10520,10 @@
         <x:v>先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="Z102" s="34" t="str">
-        <x:v>查明進口木材是否來自永續來源</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AA102" s="34" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AB102" s="34" t="str">
         <x:v>A</x:v>
@@ -10532,10 +10532,10 @@
         <x:v>這是判斷「人物與交流」時要使用的依據。人物行動各異，歷史評估既要看具體貢獻，也不能忽略目的、限制和在地回應。</x:v>
       </x:c>
       <x:c r="AD102" s="34" t="str">
-        <x:v>這是「森林供應鏈」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
+        <x:v>這是「圖表判讀」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE102" s="34" t="str">
-        <x:v>這項知識屬於「電力與生活」，無法支持本題的「人物與交流」判斷。</x:v>
+        <x:v>這項知識屬於「循環經濟」，無法支持本題的「人物與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF102" s="34" t="str">
         <x:v>人物報告要以事蹟和多方資料支持。</x:v>
@@ -10570,13 +10570,13 @@
         <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="J103" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="K103" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="L103" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="M103" s="34" t="str">
         <x:v>A</x:v>
@@ -10594,13 +10594,13 @@
         <x:v>你的判讀可被查證：比較具體貢獻、限制與在地回應。這正是人物與交流要比較的核心。</x:v>
       </x:c>
       <x:c r="R103" s="34" t="str">
-        <x:v>焦點放錯了。請回看：先辨身分與行動，再談影響。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="S103" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：先辨身分與行動，再談影響。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="T103" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：先辨身分與行動，再談影響。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「人物與交流」。請回看：先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="U103" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10618,10 +10618,10 @@
         <x:v>先辨身分與行動，再談影響。</x:v>
       </x:c>
       <x:c r="Z103" s="34" t="str">
-        <x:v>查紀錄、調方法，再用同指標測量</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="AA103" s="34" t="str">
-        <x:v>訪談多方並搭配噪音與發電資料</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AB103" s="34" t="str">
         <x:v>A</x:v>
@@ -10630,10 +10630,10 @@
         <x:v>這是判斷「人物與交流」時要使用的依據。人物行動各異，歷史評估既要看具體貢獻，也不能忽略目的、限制和在地回應。</x:v>
       </x:c>
       <x:c r="AD103" s="34" t="str">
-        <x:v>這是「行動省思」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
+        <x:v>這是「電力與生活」的重點；本題要判斷的是「人物與交流」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE103" s="34" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「人物與交流」判斷。</x:v>
+        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「人物與交流」判斷。</x:v>
       </x:c>
       <x:c r="AF103" s="34" t="str">
         <x:v>人物報告要以事蹟和多方資料支持。</x:v>
@@ -10674,7 +10674,7 @@
         <x:v>清廷因四季變化才改革</x:v>
       </x:c>
       <x:c r="L104" s="34" t="str">
-        <x:v>所有地方衝突已自動消失</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="M104" s="34" t="str">
         <x:v>A</x:v>
@@ -10698,7 +10698,7 @@
         <x:v>焦點放錯了。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="T104" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="U104" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10716,10 +10716,10 @@
         <x:v>把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="Z104" s="34" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="AA104" s="34" t="str">
-        <x:v>合作修水圳，訂分水與維修規則</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AB104" s="34" t="str">
         <x:v>A</x:v>
@@ -10728,10 +10728,10 @@
         <x:v>這是判斷「牡丹社事件」時要使用的依據。國際危機讓清廷注意臺灣的戰略地位與治理缺口，政策因此轉變。</x:v>
       </x:c>
       <x:c r="AD104" s="34" t="str">
-        <x:v>這是「權利權衡」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
+        <x:v>這是「畜牧權衡」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE104" s="34" t="str">
-        <x:v>這項知識屬於「水利開墾」，無法支持本題的「牡丹社事件」判斷。</x:v>
+        <x:v>這項知識屬於「族群衝突」，無法支持本題的「牡丹社事件」判斷。</x:v>
       </x:c>
       <x:c r="AF104" s="34" t="str">
         <x:v>分析危機後改革時指出它揭露的漏洞。</x:v>
@@ -10766,13 +10766,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J105" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="K105" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="L105" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="M105" s="34" t="str">
         <x:v>A</x:v>
@@ -10790,13 +10790,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是牡丹社事件要比較的核心。</x:v>
       </x:c>
       <x:c r="R105" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="S105" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="T105" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="U105" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10814,10 +10814,10 @@
         <x:v>把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="Z105" s="34" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AA105" s="34" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="AB105" s="34" t="str">
         <x:v>A</x:v>
@@ -10826,10 +10826,10 @@
         <x:v>這是判斷「牡丹社事件」時要使用的依據。國際危機讓清廷注意臺灣的戰略地位與治理缺口，政策因此轉變。</x:v>
       </x:c>
       <x:c r="AD105" s="34" t="str">
-        <x:v>這是「問題形成」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
+        <x:v>這是「港市與文化」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE105" s="34" t="str">
-        <x:v>這項知識屬於「理財風險」，無法支持本題的「牡丹社事件」判斷。</x:v>
+        <x:v>這項知識屬於「地圖尺度」，無法支持本題的「牡丹社事件」判斷。</x:v>
       </x:c>
       <x:c r="AF105" s="34" t="str">
         <x:v>分析危機後改革時指出它揭露的漏洞。</x:v>
@@ -10864,13 +10864,13 @@
         <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="J106" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="K106" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="L106" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="M106" s="34" t="str">
         <x:v>A</x:v>
@@ -10888,13 +10888,13 @@
         <x:v>判斷精準。「外力暴露治理不足，促使政策改變」直接回應牡丹社事件，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R106" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="S106" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="T106" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把事件、暴露問題和政策變化連起來。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「牡丹社事件」。請回看：把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="U106" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -10912,10 +10912,10 @@
         <x:v>把事件、暴露問題和政策變化連起來。</x:v>
       </x:c>
       <x:c r="Z106" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="AA106" s="34" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AB106" s="34" t="str">
         <x:v>A</x:v>
@@ -10924,10 +10924,10 @@
         <x:v>這是判斷「牡丹社事件」時要使用的依據。國際危機讓清廷注意臺灣的戰略地位與治理缺口，政策因此轉變。</x:v>
       </x:c>
       <x:c r="AD106" s="34" t="str">
-        <x:v>這是「能源分類」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
+        <x:v>這是「理財風險」的重點；本題要判斷的是「牡丹社事件」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE106" s="34" t="str">
-        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「牡丹社事件」判斷。</x:v>
+        <x:v>這項知識屬於「永續漁業」，無法支持本題的「牡丹社事件」判斷。</x:v>
       </x:c>
       <x:c r="AF106" s="34" t="str">
         <x:v>分析危機後改革時指出它揭露的漏洞。</x:v>
@@ -10968,7 +10968,7 @@
         <x:v>戰爭只因臺灣稻米價格</x:v>
       </x:c>
       <x:c r="L107" s="34" t="str">
-        <x:v>鐵路出現後就不需道路與船舶</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="M107" s="34" t="str">
         <x:v>A</x:v>
@@ -10992,7 +10992,7 @@
         <x:v>這項推論缺少證據。請確認：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="T107" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="U107" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -11010,10 +11010,10 @@
         <x:v>區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="Z107" s="34" t="str">
-        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AA107" s="34" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AB107" s="34" t="str">
         <x:v>A</x:v>
@@ -11022,10 +11022,10 @@
         <x:v>這是判斷「清法戰爭與建省」時要使用的依據。戰爭凸顯戰略位置，建省與新建設提高治理能力，但執行需時間且有成本。</x:v>
       </x:c>
       <x:c r="AD107" s="34" t="str">
-        <x:v>這是「航海動機」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
+        <x:v>這是「貿易影響」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE107" s="34" t="str">
-        <x:v>這項知識屬於「能源代價」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
+        <x:v>這項知識屬於「消費權益」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
       </x:c>
       <x:c r="AF107" s="34" t="str">
         <x:v>評估制度改革時區分宣布與實際成效。</x:v>
@@ -11060,13 +11060,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J108" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="K108" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="L108" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="M108" s="34" t="str">
         <x:v>A</x:v>
@@ -11084,13 +11084,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應清法戰爭與建省，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R108" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="S108" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="T108" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="U108" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -11108,10 +11108,10 @@
         <x:v>區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="Z108" s="34" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AA108" s="34" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AB108" s="34" t="str">
         <x:v>A</x:v>
@@ -11120,10 +11120,10 @@
         <x:v>這是判斷「清法戰爭與建省」時要使用的依據。戰爭凸顯戰略位置，建省與新建設提高治理能力，但執行需時間且有成本。</x:v>
       </x:c>
       <x:c r="AD108" s="34" t="str">
-        <x:v>這是「遷移原因」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費權益」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE108" s="34" t="str">
-        <x:v>這項知識屬於「行動評估」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
+        <x:v>這項知識屬於「規範變遷」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
       </x:c>
       <x:c r="AF108" s="34" t="str">
         <x:v>評估制度改革時區分宣布與實際成效。</x:v>
@@ -11158,13 +11158,13 @@
         <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="J109" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="K109" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="L109" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="M109" s="34" t="str">
         <x:v>A</x:v>
@@ -11182,13 +11182,13 @@
         <x:v>這項選擇成立：海防受重視，建省與建設強化治理。它抓住清法戰爭與建省的關鍵條件。</x:v>
       </x:c>
       <x:c r="R109" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="S109" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="T109" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「清法戰爭與建省」。請回看：區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="U109" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -11206,10 +11206,10 @@
         <x:v>區分戰爭起因、臺灣受波及原因與後續政策。</x:v>
       </x:c>
       <x:c r="Z109" s="34" t="str">
-        <x:v>訂規則、維修配置與歸還責任</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AA109" s="34" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB109" s="34" t="str">
         <x:v>A</x:v>
@@ -11218,10 +11218,10 @@
         <x:v>這是判斷「清法戰爭與建省」時要使用的依據。戰爭凸顯戰略位置，建省與新建設提高治理能力，但執行需時間且有成本。</x:v>
       </x:c>
       <x:c r="AD109" s="34" t="str">
-        <x:v>這是「共享資源」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
+        <x:v>這是「板塊與地形」的重點；本題要判斷的是「清法戰爭與建省」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE109" s="34" t="str">
-        <x:v>這項知識屬於「永續農業」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「清法戰爭與建省」判斷。</x:v>
       </x:c>
       <x:c r="AF109" s="34" t="str">
         <x:v>評估制度改革時區分宣布與實際成效。</x:v>
@@ -11262,7 +11262,7 @@
         <x:v>有電後不會再發生火災</x:v>
       </x:c>
       <x:c r="L110" s="35" t="str">
-        <x:v>電力只影響工廠，不影響家庭</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="M110" s="35" t="str">
         <x:v>A</x:v>
@@ -11286,7 +11286,7 @@
         <x:v>選項和題意關係較弱。提示：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="T110" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：同時看便利與依賴。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="U110" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11304,10 +11304,10 @@
         <x:v>同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="Z110" s="35" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AA110" s="35" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB110" s="35" t="str">
         <x:v>A</x:v>
@@ -11316,10 +11316,10 @@
         <x:v>這是判斷「電力與生活」時要使用的依據。電力延伸活動時間並替代部分火光，也形成停電時的新脆弱性。</x:v>
       </x:c>
       <x:c r="AD110" s="35" t="str">
-        <x:v>這是「地圖尺度」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
+        <x:v>這是「海岸變遷」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE110" s="35" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「電力與生活」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「電力與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF110" s="35" t="str">
         <x:v>停電演練要準備照明、交通與通訊備案。</x:v>
@@ -11354,13 +11354,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J111" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="K111" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="L111" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="M111" s="35" t="str">
         <x:v>A</x:v>
@@ -11378,13 +11378,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住電力與生活的關鍵條件。</x:v>
       </x:c>
       <x:c r="R111" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：同時看便利與依賴。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="S111" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：同時看便利與依賴。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="T111" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：同時看便利與依賴。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="U111" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11402,10 +11402,10 @@
         <x:v>同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="Z111" s="35" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AA111" s="35" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB111" s="35" t="str">
         <x:v>A</x:v>
@@ -11414,10 +11414,10 @@
         <x:v>這是判斷「電力與生活」時要使用的依據。電力延伸活動時間並替代部分火光，也形成停電時的新脆弱性。</x:v>
       </x:c>
       <x:c r="AD111" s="35" t="str">
-        <x:v>這是「永續漁業」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元資料」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE111" s="35" t="str">
-        <x:v>這項知識屬於「港市與文化」，無法支持本題的「電力與生活」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「電力與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF111" s="35" t="str">
         <x:v>停電演練要準備照明、交通與通訊備案。</x:v>
@@ -11452,13 +11452,13 @@
         <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="J112" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="K112" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="L112" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="M112" s="35" t="str">
         <x:v>A</x:v>
@@ -11476,13 +11476,13 @@
         <x:v>證據吻合。選項「電力帶來便利，也增加供電依賴」能把電力與生活的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R112" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：同時看便利與依賴。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="S112" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：同時看便利與依賴。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="T112" s="35" t="str">
-        <x:v>焦點放錯了。請回看：同時看便利與依賴。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「電力與生活」。請回看：同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="U112" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11500,10 +11500,10 @@
         <x:v>同時看便利與依賴。</x:v>
       </x:c>
       <x:c r="Z112" s="35" t="str">
-        <x:v>限定結論範圍並說明調查限制</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AA112" s="35" t="str">
-        <x:v>比較設置前後的發電、用電與環境</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="AB112" s="35" t="str">
         <x:v>A</x:v>
@@ -11512,10 +11512,10 @@
         <x:v>這是判斷「電力與生活」時要使用的依據。電力延伸活動時間並替代部分火光，也形成停電時的新脆弱性。</x:v>
       </x:c>
       <x:c r="AD112" s="35" t="str">
-        <x:v>這是「結論界線」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
+        <x:v>這是「港市與文化」的重點；本題要判斷的是「電力與生活」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE112" s="35" t="str">
-        <x:v>這項知識屬於「能源提問」，無法支持本題的「電力與生活」判斷。</x:v>
+        <x:v>這項知識屬於「史前證據」，無法支持本題的「電力與生活」判斷。</x:v>
       </x:c>
       <x:c r="AF112" s="35" t="str">
         <x:v>停電演練要準備照明、交通與通訊備案。</x:v>
@@ -11556,7 +11556,7 @@
         <x:v>電廠名稱有幾個字</x:v>
       </x:c>
       <x:c r="L113" s="35" t="str">
-        <x:v>只看發電地是否靠海</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="M113" s="35" t="str">
         <x:v>A</x:v>
@@ -11580,7 +11580,7 @@
         <x:v>這裡混淆了條件與結論。提示：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="T113" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先看來源，再看優缺點。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="U113" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11598,10 +11598,10 @@
         <x:v>先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="Z113" s="35" t="str">
-        <x:v>規範可調整，互助目的仍保留</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="AA113" s="35" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="AB113" s="35" t="str">
         <x:v>A</x:v>
@@ -11610,10 +11610,10 @@
         <x:v>這是判斷「能源分類」時要使用的依據。再生與非再生能源依來源補充性分類，後續還需比較穩定、成本與環境。</x:v>
       </x:c>
       <x:c r="AD113" s="35" t="str">
-        <x:v>這是「規範變遷」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
+        <x:v>這是「永續農業」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE113" s="35" t="str">
-        <x:v>這項知識屬於「移民與季風」，無法支持本題的「能源分類」判斷。</x:v>
+        <x:v>這項知識屬於「遷移原因」，無法支持本題的「能源分類」判斷。</x:v>
       </x:c>
       <x:c r="AF113" s="35" t="str">
         <x:v>讀能源圖表時不要把設備和能源來源混為一談。</x:v>
@@ -11648,13 +11648,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J114" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="K114" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="L114" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="M114" s="35" t="str">
         <x:v>A</x:v>
@@ -11672,13 +11672,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把能源分類的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R114" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先看來源，再看優缺點。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="S114" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先看來源，再看優缺點。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="T114" s="35" t="str">
-        <x:v>焦點放錯了。請回看：先看來源，再看優缺點。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="U114" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11696,10 +11696,10 @@
         <x:v>先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="Z114" s="35" t="str">
-        <x:v>貿易增加，也改變土地與族群關係</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AA114" s="35" t="str">
-        <x:v>保存證據，再循正式管道申訴</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AB114" s="35" t="str">
         <x:v>A</x:v>
@@ -11708,10 +11708,10 @@
         <x:v>這是判斷「能源分類」時要使用的依據。再生與非再生能源依來源補充性分類，後續還需比較穩定、成本與環境。</x:v>
       </x:c>
       <x:c r="AD114" s="35" t="str">
-        <x:v>這是「貿易影響」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
+        <x:v>這是「族群衝突」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE114" s="35" t="str">
-        <x:v>這項知識屬於「消費權益」，無法支持本題的「能源分類」判斷。</x:v>
+        <x:v>這項知識屬於「位置與交流」，無法支持本題的「能源分類」判斷。</x:v>
       </x:c>
       <x:c r="AF114" s="35" t="str">
         <x:v>讀能源圖表時不要把設備和能源來源混為一談。</x:v>
@@ -11746,13 +11746,13 @@
         <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="J115" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="K115" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="L115" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="M115" s="35" t="str">
         <x:v>A</x:v>
@@ -11770,13 +11770,13 @@
         <x:v>答對了；「依能源補充性與環境特性分類」同時保留了能源分類需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R115" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：先看來源，再看優缺點。</x:v>
+        <x:v>「設計耐用可修產品並回收再製」是「循環經濟」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="S115" s="35" t="str">
-        <x:v>焦點放錯了。請回看：先看來源，再看優缺點。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="T115" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：先看來源，再看優缺點。</x:v>
+        <x:v>「訪談多方並搭配噪音與發電資料」是「多元觀點」的重點，但不能回答本題的「能源分類」。請回看：先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="U115" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11794,10 +11794,10 @@
         <x:v>先看來源，再看優缺點。</x:v>
       </x:c>
       <x:c r="Z115" s="35" t="str">
-        <x:v>通商壓力、物產與航路共同促成開港</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="AA115" s="35" t="str">
-        <x:v>板塊交界造成多山與地震</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="AB115" s="35" t="str">
         <x:v>A</x:v>
@@ -11806,10 +11806,10 @@
         <x:v>這是判斷「能源分類」時要使用的依據。再生與非再生能源依來源補充性分類，後續還需比較穩定、成本與環境。</x:v>
       </x:c>
       <x:c r="AD115" s="35" t="str">
-        <x:v>這是「開港背景」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費權益」的重點；本題要判斷的是「能源分類」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE115" s="35" t="str">
-        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「能源分類」判斷。</x:v>
+        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「能源分類」判斷。</x:v>
       </x:c>
       <x:c r="AF115" s="35" t="str">
         <x:v>讀能源圖表時不要把設備和能源來源混為一談。</x:v>
@@ -11850,7 +11850,7 @@
         <x:v>內陸無風地區優先設離岸風機</x:v>
       </x:c>
       <x:c r="L116" s="35" t="str">
-        <x:v>有溫泉就能無限制地熱發電</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="M116" s="35" t="str">
         <x:v>A</x:v>
@@ -11874,7 +11874,7 @@
         <x:v>這項判斷忽略重要限制。請想想：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="T116" s="35" t="str">
-        <x:v>焦點放錯了。請回看：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="U116" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11892,10 +11892,10 @@
         <x:v>自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="Z116" s="35" t="str">
-        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="AA116" s="35" t="str">
-        <x:v>比較具體貢獻、限制與在地回應</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AB116" s="35" t="str">
         <x:v>A</x:v>
@@ -11904,10 +11904,10 @@
         <x:v>這是判斷「地理配對」時要使用的依據。能源資源有空間差異，適地發展仍要納入技術、環境和輸配電限制。</x:v>
       </x:c>
       <x:c r="AD116" s="35" t="str">
-        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元觀點」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE116" s="35" t="str">
-        <x:v>這項知識屬於「人物與交流」，無法支持本題的「地理配對」判斷。</x:v>
+        <x:v>這項知識屬於「消費安全」，無法支持本題的「地理配對」判斷。</x:v>
       </x:c>
       <x:c r="AF116" s="35" t="str">
         <x:v>評估校園光電時量測日照與屋頂條件。</x:v>
@@ -11942,13 +11942,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J117" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="K117" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="L117" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="M117" s="35" t="str">
         <x:v>A</x:v>
@@ -11966,13 +11966,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了地理配對需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R117" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="S117" s="35" t="str">
-        <x:v>焦點放錯了。請回看：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="T117" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="U117" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -11990,10 +11990,10 @@
         <x:v>自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="Z117" s="35" t="str">
-        <x:v>合作修水圳，訂分水與維修規則</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AA117" s="35" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AB117" s="35" t="str">
         <x:v>A</x:v>
@@ -12002,10 +12002,10 @@
         <x:v>這是判斷「地理配對」時要使用的依據。能源資源有空間差異，適地發展仍要納入技術、環境和輸配電限制。</x:v>
       </x:c>
       <x:c r="AD117" s="35" t="str">
-        <x:v>這是「水利開墾」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
+        <x:v>這是「消費安全」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE117" s="35" t="str">
-        <x:v>這項知識屬於「共識與程序」，無法支持本題的「地理配對」判斷。</x:v>
+        <x:v>這項知識屬於「規範與法律」，無法支持本題的「地理配對」判斷。</x:v>
       </x:c>
       <x:c r="AF117" s="35" t="str">
         <x:v>評估校園光電時量測日照與屋頂條件。</x:v>
@@ -12040,13 +12040,13 @@
         <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="J118" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="K118" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="L118" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="M118" s="35" t="str">
         <x:v>A</x:v>
@@ -12064,13 +12064,13 @@
         <x:v>你的判讀可被查證：依地理條件發展能源並評估影響。這正是地理配對要比較的核心。</x:v>
       </x:c>
       <x:c r="R118" s="35" t="str">
-        <x:v>焦點放錯了。請回看：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="S118" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="T118" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：自然條件只是起點，不是全部決策。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「地理配對」。請回看：自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="U118" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12088,10 +12088,10 @@
         <x:v>自然條件只是起點，不是全部決策。</x:v>
       </x:c>
       <x:c r="Z118" s="35" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="AA118" s="35" t="str">
-        <x:v>相關各方應依資料協商文化與保育</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AB118" s="35" t="str">
         <x:v>A</x:v>
@@ -12100,10 +12100,10 @@
         <x:v>這是判斷「地理配對」時要使用的依據。能源資源有空間差異，適地發展仍要納入技術、環境和輸配電限制。</x:v>
       </x:c>
       <x:c r="AD118" s="35" t="str">
-        <x:v>這是「理財風險」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
+        <x:v>這是「地圖尺度」的重點；本題要判斷的是「地理配對」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE118" s="35" t="str">
-        <x:v>這項知識屬於「權利權衡」，無法支持本題的「地理配對」判斷。</x:v>
+        <x:v>這項知識屬於「多元資料」，無法支持本題的「地理配對」判斷。</x:v>
       </x:c>
       <x:c r="AF118" s="35" t="str">
         <x:v>評估校園光電時量測日照與屋頂條件。</x:v>
@@ -12144,7 +12144,7 @@
         <x:v>只選發電量最大的能源即可</x:v>
       </x:c>
       <x:c r="L119" s="35" t="str">
-        <x:v>有爭議就停止使用所有電力</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="M119" s="35" t="str">
         <x:v>A</x:v>
@@ -12168,7 +12168,7 @@
         <x:v>焦點放錯了。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="T119" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="U119" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12186,10 +12186,10 @@
         <x:v>綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="Z119" s="35" t="str">
-        <x:v>核對單位、時間、尺度與原始數值</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="AA119" s="35" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AB119" s="35" t="str">
         <x:v>A</x:v>
@@ -12198,10 +12198,10 @@
         <x:v>這是判斷「能源代價」時要使用的依據。每種方式的優缺點不同，決策需比較供電、成本、環境、安全與公平。</x:v>
       </x:c>
       <x:c r="AD119" s="35" t="str">
-        <x:v>這是「圖表判讀」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
+        <x:v>這是「移民與季風」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE119" s="35" t="str">
-        <x:v>這項知識屬於「循環經濟」，無法支持本題的「能源代價」判斷。</x:v>
+        <x:v>這項知識屬於「分析權衡」，無法支持本題的「能源代價」判斷。</x:v>
       </x:c>
       <x:c r="AF119" s="35" t="str">
         <x:v>小組選方案時公開比較指標與權重。</x:v>
@@ -12236,13 +12236,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J120" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="K120" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="L120" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="M120" s="35" t="str">
         <x:v>A</x:v>
@@ -12260,13 +12260,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是能源代價要比較的核心。</x:v>
       </x:c>
       <x:c r="R120" s="35" t="str">
-        <x:v>焦點放錯了。請回看：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="S120" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「停止交易並改用官方查證與付款」是「消費安全」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="T120" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="U120" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12284,10 +12284,10 @@
         <x:v>綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="Z120" s="35" t="str">
-        <x:v>外力暴露治理不足，促使政策改變</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="AA120" s="35" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AB120" s="35" t="str">
         <x:v>A</x:v>
@@ -12296,10 +12296,10 @@
         <x:v>這是判斷「能源代價」時要使用的依據。每種方式的優缺點不同，決策需比較供電、成本、環境、安全與公平。</x:v>
       </x:c>
       <x:c r="AD120" s="35" t="str">
-        <x:v>這是「牡丹社事件」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
+        <x:v>這是「分析權衡」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE120" s="35" t="str">
-        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「能源代價」判斷。</x:v>
+        <x:v>這項知識屬於「地方轉型」，無法支持本題的「能源代價」判斷。</x:v>
       </x:c>
       <x:c r="AF120" s="35" t="str">
         <x:v>小組選方案時公開比較指標與權重。</x:v>
@@ -12334,13 +12334,13 @@
         <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="J121" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="K121" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="L121" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="M121" s="35" t="str">
         <x:v>A</x:v>
@@ -12358,13 +12358,13 @@
         <x:v>判斷精準。「用共同指標比較各能源的代價」直接回應能源代價，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R121" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="S121" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="T121" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：綠色或穩定都不等於沒有代價。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「能源代價」。請回看：綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="U121" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12382,10 +12382,10 @@
         <x:v>綠色或穩定都不等於沒有代價。</x:v>
       </x:c>
       <x:c r="Z121" s="35" t="str">
-        <x:v>設基準與措施，四週後同指標比較</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="AA121" s="35" t="str">
-        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AB121" s="35" t="str">
         <x:v>A</x:v>
@@ -12394,10 +12394,10 @@
         <x:v>這是判斷「能源代價」時要使用的依據。每種方式的優缺點不同，決策需比較供電、成本、環境、安全與公平。</x:v>
       </x:c>
       <x:c r="AD121" s="35" t="str">
-        <x:v>這是「行動評估」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範變遷」的重點；本題要判斷的是「能源代價」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE121" s="35" t="str">
-        <x:v>這項知識屬於「航海動機」，無法支持本題的「能源代價」判斷。</x:v>
+        <x:v>這項知識屬於「族群衝突」，無法支持本題的「能源代價」判斷。</x:v>
       </x:c>
       <x:c r="AF121" s="35" t="str">
         <x:v>小組選方案時公開比較指標與權重。</x:v>
@@ -12438,7 +12438,7 @@
         <x:v>多數人支持便可忽略少數權益</x:v>
       </x:c>
       <x:c r="L122" s="35" t="str">
-        <x:v>看不見的風險等於不存在</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="M122" s="35" t="str">
         <x:v>A</x:v>
@@ -12462,7 +12462,7 @@
         <x:v>這項推論缺少證據。請確認：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="T122" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="U122" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12480,10 +12480,10 @@
         <x:v>問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="Z122" s="35" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="AA122" s="35" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="AB122" s="35" t="str">
         <x:v>A</x:v>
@@ -12492,10 +12492,10 @@
         <x:v>這是判斷「環境正義」時要使用的依據。能源政策不只算總利益，也要處理風險落在誰身上、誰有決定權與長期責任。</x:v>
       </x:c>
       <x:c r="AD122" s="35" t="str">
-        <x:v>這是「港市與文化」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
+        <x:v>這是「人物與交流」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE122" s="35" t="str">
-        <x:v>這項知識屬於「地圖尺度」，無法支持本題的「環境正義」判斷。</x:v>
+        <x:v>這項知識屬於「史前證據」，無法支持本題的「環境正義」判斷。</x:v>
       </x:c>
       <x:c r="AF122" s="35" t="str">
         <x:v>設施設址要有監測、參與與補救機制。</x:v>
@@ -12530,13 +12530,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J123" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="K123" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="L123" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="M123" s="35" t="str">
         <x:v>A</x:v>
@@ -12554,13 +12554,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應環境正義，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R123" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="S123" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="T123" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="U123" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12578,10 +12578,10 @@
         <x:v>問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="Z123" s="35" t="str">
-        <x:v>比較設置前後的發電、用電與環境</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AA123" s="35" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="AB123" s="35" t="str">
         <x:v>A</x:v>
@@ -12590,10 +12590,10 @@
         <x:v>這是判斷「環境正義」時要使用的依據。能源政策不只算總利益，也要處理風險落在誰身上、誰有決定權與長期責任。</x:v>
       </x:c>
       <x:c r="AD123" s="35" t="str">
-        <x:v>這是「能源提問」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
+        <x:v>這是「文化多樣性」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE123" s="35" t="str">
-        <x:v>這項知識屬於「永續漁業」，無法支持本題的「環境正義」判斷。</x:v>
+        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「環境正義」判斷。</x:v>
       </x:c>
       <x:c r="AF123" s="35" t="str">
         <x:v>設施設址要有監測、參與與補救機制。</x:v>
@@ -12628,13 +12628,13 @@
         <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="J124" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="K124" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="L124" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="M124" s="35" t="str">
         <x:v>A</x:v>
@@ -12652,13 +12652,13 @@
         <x:v>這項選擇成立：風險分配與居民參與需要公平。它抓住環境正義的關鍵條件。</x:v>
       </x:c>
       <x:c r="R124" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="S124" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="T124" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：問誰受益、誰承擔、誰能決定。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「環境正義」。請回看：問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="U124" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -12676,10 +12676,10 @@
         <x:v>問誰受益、誰承擔、誰能決定。</x:v>
       </x:c>
       <x:c r="Z124" s="35" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="AA124" s="35" t="str">
-        <x:v>限定結論範圍並說明調查限制</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AB124" s="35" t="str">
         <x:v>A</x:v>
@@ -12688,10 +12688,10 @@
         <x:v>這是判斷「環境正義」時要使用的依據。能源政策不只算總利益，也要處理風險落在誰身上、誰有決定權與長期責任。</x:v>
       </x:c>
       <x:c r="AD124" s="35" t="str">
-        <x:v>這是「環境與生活」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
+        <x:v>這是「潟湖與港口」的重點；本題要判斷的是「環境正義」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE124" s="35" t="str">
-        <x:v>這項知識屬於「結論界線」，無法支持本題的「環境正義」判斷。</x:v>
+        <x:v>這項知識屬於「消費安全」，無法支持本題的「環境正義」判斷。</x:v>
       </x:c>
       <x:c r="AF124" s="35" t="str">
         <x:v>設施設址要有監測、參與與補救機制。</x:v>
@@ -12732,7 +12732,7 @@
         <x:v>提供密碼和驗證碼證明誠意</x:v>
       </x:c>
       <x:c r="L125" s="34" t="str">
-        <x:v>點開所有連結再決定</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="M125" s="34" t="str">
         <x:v>A</x:v>
@@ -12756,7 +12756,7 @@
         <x:v>選項和題意關係較弱。提示：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="T125" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="U125" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -12774,10 +12774,10 @@
         <x:v>把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="Z125" s="34" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="AA125" s="34" t="str">
-        <x:v>商品與港口帶動北部市鎮發展</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="AB125" s="34" t="str">
         <x:v>A</x:v>
@@ -12786,10 +12786,10 @@
         <x:v>這是判斷「消費安全」時要使用的依據。異常低價、催促和脫離平台是高風險訊號；查證與受保障付款能降低詐騙。</x:v>
       </x:c>
       <x:c r="AD125" s="34" t="str">
-        <x:v>這是「地方轉型」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
+        <x:v>這是「時序空間」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE125" s="34" t="str">
-        <x:v>這項知識屬於「經濟北移」，無法支持本題的「消費安全」判斷。</x:v>
+        <x:v>這項知識屬於「清法戰爭與建省」，無法支持本題的「消費安全」判斷。</x:v>
       </x:c>
       <x:c r="AF125" s="34" t="str">
         <x:v>包裹簡訊要從官方 App 查，不點訊息連結。</x:v>
@@ -12824,13 +12824,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J126" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="K126" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="L126" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="M126" s="34" t="str">
         <x:v>A</x:v>
@@ -12848,13 +12848,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住消費安全的關鍵條件。</x:v>
       </x:c>
       <x:c r="R126" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="S126" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="T126" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「合作修水圳，訂分水與維修規則」是「水利開墾」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="U126" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -12872,10 +12872,10 @@
         <x:v>把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="Z126" s="34" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="AA126" s="34" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="AB126" s="34" t="str">
         <x:v>A</x:v>
@@ -12884,10 +12884,10 @@
         <x:v>這是判斷「消費安全」時要使用的依據。異常低價、催促和脫離平台是高風險訊號；查證與受保障付款能降低詐騙。</x:v>
       </x:c>
       <x:c r="AD126" s="34" t="str">
-        <x:v>這是「移民與季風」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
+        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE126" s="34" t="str">
-        <x:v>這項知識屬於「分析權衡」，無法支持本題的「消費安全」判斷。</x:v>
+        <x:v>這項知識屬於「環境與生活」，無法支持本題的「消費安全」判斷。</x:v>
       </x:c>
       <x:c r="AF126" s="34" t="str">
         <x:v>包裹簡訊要從官方 App 查，不點訊息連結。</x:v>
@@ -12922,13 +12922,13 @@
         <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="J127" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="K127" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="L127" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>遺物顯示可能已有農耕定居生活</x:v>
       </x:c>
       <x:c r="M127" s="34" t="str">
         <x:v>A</x:v>
@@ -12946,13 +12946,13 @@
         <x:v>證據吻合。選項「停止交易並改用官方查證與付款」能把消費安全的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R127" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="S127" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="T127" s="34" t="str">
-        <x:v>焦點放錯了。請回看：把可疑訊號和正式查證管道配對。</x:v>
+        <x:v>「遺物顯示可能已有農耕定居生活」是「史前證據」的重點，但不能回答本題的「消費安全」。請回看：把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="U127" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -12970,10 +12970,10 @@
         <x:v>把可疑訊號和正式查證管道配對。</x:v>
       </x:c>
       <x:c r="Z127" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AA127" s="34" t="str">
-        <x:v>規範可調整，互助目的仍保留</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB127" s="34" t="str">
         <x:v>A</x:v>
@@ -12982,10 +12982,10 @@
         <x:v>這是判斷「消費安全」時要使用的依據。異常低價、催促和脫離平台是高風險訊號；查證與受保障付款能降低詐騙。</x:v>
       </x:c>
       <x:c r="AD127" s="34" t="str">
-        <x:v>這是「能源分類」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
+        <x:v>這是「位置與交流」的重點；本題要判斷的是「消費安全」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE127" s="34" t="str">
-        <x:v>這項知識屬於「規範變遷」，無法支持本題的「消費安全」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「消費安全」判斷。</x:v>
       </x:c>
       <x:c r="AF127" s="34" t="str">
         <x:v>包裹簡訊要從官方 App 查，不點訊息連結。</x:v>
@@ -13026,7 +13026,7 @@
         <x:v>公開個資逼店家處理</x:v>
       </x:c>
       <x:c r="L128" s="34" t="str">
-        <x:v>因流程麻煩就不留紀錄</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="M128" s="34" t="str">
         <x:v>A</x:v>
@@ -13050,7 +13050,7 @@
         <x:v>這裡混淆了條件與結論。提示：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="T128" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="U128" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13068,10 +13068,10 @@
         <x:v>保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="Z128" s="34" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="AA128" s="34" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AB128" s="34" t="str">
         <x:v>A</x:v>
@@ -13080,10 +13080,10 @@
         <x:v>這是判斷「消費權益」時要使用的依據。交易與瑕疵證據能支持申訴，消費者、企業和政府管道各有責任。</x:v>
       </x:c>
       <x:c r="AD128" s="34" t="str">
-        <x:v>這是「多元資料」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
+        <x:v>這是「行動省思」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE128" s="34" t="str">
-        <x:v>這項知識屬於「能源代價」，無法支持本題的「消費權益」判斷。</x:v>
+        <x:v>這項知識屬於「多元觀點」，無法支持本題的「消費權益」判斷。</x:v>
       </x:c>
       <x:c r="AF128" s="34" t="str">
         <x:v>需要時查詢 1950 等正式消保管道。</x:v>
@@ -13118,13 +13118,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J129" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="K129" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="L129" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>電力帶來便利，也增加供電依賴</x:v>
       </x:c>
       <x:c r="M129" s="34" t="str">
         <x:v>A</x:v>
@@ -13142,13 +13142,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把消費權益的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R129" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="S129" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="T129" s="34" t="str">
-        <x:v>焦點放錯了。請回看：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「電力帶來便利，也增加供電依賴」是「電力與生活」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="U129" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13166,10 +13166,10 @@
         <x:v>保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="Z129" s="34" t="str">
-        <x:v>比較具體貢獻、限制與在地回應</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AA129" s="34" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AB129" s="34" t="str">
         <x:v>A</x:v>
@@ -13178,10 +13178,10 @@
         <x:v>這是判斷「消費權益」時要使用的依據。交易與瑕疵證據能支持申訴，消費者、企業和政府管道各有責任。</x:v>
       </x:c>
       <x:c r="AD129" s="34" t="str">
-        <x:v>這是「人物與交流」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元觀點」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE129" s="34" t="str">
-        <x:v>這項知識屬於「史前證據」，無法支持本題的「消費權益」判斷。</x:v>
+        <x:v>這項知識屬於「森林供應鏈」，無法支持本題的「消費權益」判斷。</x:v>
       </x:c>
       <x:c r="AF129" s="34" t="str">
         <x:v>需要時查詢 1950 等正式消保管道。</x:v>
@@ -13216,13 +13216,13 @@
         <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="J130" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="K130" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="L130" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="M130" s="34" t="str">
         <x:v>A</x:v>
@@ -13240,13 +13240,13 @@
         <x:v>答對了；「保存證據，再循正式管道申訴」同時保留了消費權益需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R130" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="S130" s="34" t="str">
-        <x:v>焦點放錯了。請回看：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="T130" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：保留何時、向誰、買了什麼的證明。</x:v>
+        <x:v>「查明進口木材是否來自永續來源」是「森林供應鏈」的重點，但不能回答本題的「消費權益」。請回看：保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="U130" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13264,10 +13264,10 @@
         <x:v>保留何時、向誰、買了什麼的證明。</x:v>
       </x:c>
       <x:c r="Z130" s="34" t="str">
-        <x:v>用共同目標與相同標準調整方案</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AA130" s="34" t="str">
-        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="AB130" s="34" t="str">
         <x:v>A</x:v>
@@ -13276,10 +13276,10 @@
         <x:v>這是判斷「消費權益」時要使用的依據。交易與瑕疵證據能支持申訴，消費者、企業和政府管道各有責任。</x:v>
       </x:c>
       <x:c r="AD130" s="34" t="str">
-        <x:v>這是「共識與程序」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範與法律」的重點；本題要判斷的是「消費權益」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE130" s="34" t="str">
-        <x:v>這項知識屬於「潟湖與港口」，無法支持本題的「消費權益」判斷。</x:v>
+        <x:v>這項知識屬於「遷移原因」，無法支持本題的「消費權益」判斷。</x:v>
       </x:c>
       <x:c r="AF130" s="34" t="str">
         <x:v>需要時查詢 1950 等正式消保管道。</x:v>
@@ -13320,7 +13320,7 @@
         <x:v>報酬越高表示越安全</x:v>
       </x:c>
       <x:c r="L131" s="34" t="str">
-        <x:v>朋友推薦就不必了解內容</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="M131" s="34" t="str">
         <x:v>A</x:v>
@@ -13344,7 +13344,7 @@
         <x:v>這項判斷忽略重要限制。請想想：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="T131" s="34" t="str">
-        <x:v>焦點放錯了。請回看：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="U131" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13362,10 +13362,10 @@
         <x:v>沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="Z131" s="34" t="str">
-        <x:v>分析資源、語言、組織與治理</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AA131" s="34" t="str">
-        <x:v>臺灣是遷徙與交流的中繼點</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AB131" s="34" t="str">
         <x:v>A</x:v>
@@ -13374,10 +13374,10 @@
         <x:v>這是判斷「理財風險」時要使用的依據。投資具有不確定性，不合理保證可能是詐騙；需配合目的、期限與承受度。</x:v>
       </x:c>
       <x:c r="AD131" s="34" t="str">
-        <x:v>這是「族群衝突」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
+        <x:v>這是「經濟北移」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE131" s="34" t="str">
-        <x:v>這項知識屬於「位置與交流」，無法支持本題的「理財風險」判斷。</x:v>
+        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「理財風險」判斷。</x:v>
       </x:c>
       <x:c r="AF131" s="34" t="str">
         <x:v>金融資訊先向可信主管機關查證。</x:v>
@@ -13412,13 +13412,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J132" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="K132" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="L132" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="M132" s="34" t="str">
         <x:v>A</x:v>
@@ -13436,13 +13436,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了理財風險需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R132" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「比較對象、程度、證據與改善方法」是「分析權衡」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="S132" s="34" t="str">
-        <x:v>焦點放錯了。請回看：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「用共同目標與相同標準調整方案」是「共識與程序」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="T132" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「設基準與措施，四週後同指標比較」是「行動評估」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="U132" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13460,10 +13460,10 @@
         <x:v>沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="Z132" s="34" t="str">
-        <x:v>風險分配與居民參與需要公平</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AA132" s="34" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AB132" s="34" t="str">
         <x:v>A</x:v>
@@ -13472,10 +13472,10 @@
         <x:v>這是判斷「理財風險」時要使用的依據。投資具有不確定性，不合理保證可能是詐騙；需配合目的、期限與承受度。</x:v>
       </x:c>
       <x:c r="AD132" s="34" t="str">
-        <x:v>這是「環境正義」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
+        <x:v>這是「海岸變遷」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE132" s="34" t="str">
-        <x:v>這項知識屬於「畜牧權衡」，無法支持本題的「理財風險」判斷。</x:v>
+        <x:v>這項知識屬於「問題形成」，無法支持本題的「理財風險」判斷。</x:v>
       </x:c>
       <x:c r="AF132" s="34" t="str">
         <x:v>金融資訊先向可信主管機關查證。</x:v>
@@ -13510,13 +13510,13 @@
         <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="J133" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="K133" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="L133" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>核對單位、時間、尺度與原始數值</x:v>
       </x:c>
       <x:c r="M133" s="34" t="str">
         <x:v>A</x:v>
@@ -13534,13 +13534,13 @@
         <x:v>你的判讀可被查證：查合法性，不投入無法承受的資金。這正是理財風險要比較的核心。</x:v>
       </x:c>
       <x:c r="R133" s="34" t="str">
-        <x:v>焦點放錯了。請回看：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="S133" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="T133" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：沒有必然高報酬又零風險的商品。</x:v>
+        <x:v>「核對單位、時間、尺度與原始數值」是「圖表判讀」的重點，但不能回答本題的「理財風險」。請回看：沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="U133" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13558,10 +13558,10 @@
         <x:v>沒有必然高報酬又零風險的商品。</x:v>
       </x:c>
       <x:c r="Z133" s="34" t="str">
-        <x:v>分族查資料，再比較文化異同</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AA133" s="34" t="str">
-        <x:v>核對單位、時間、尺度與原始數值</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="AB133" s="34" t="str">
         <x:v>A</x:v>
@@ -13570,10 +13570,10 @@
         <x:v>這是判斷「理財風險」時要使用的依據。投資具有不確定性，不合理保證可能是詐騙；需配合目的、期限與承受度。</x:v>
       </x:c>
       <x:c r="AD133" s="34" t="str">
-        <x:v>這是「文化多樣性」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
+        <x:v>這是「地方轉型」的重點；本題要判斷的是「理財風險」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE133" s="34" t="str">
-        <x:v>這項知識屬於「圖表判讀」，無法支持本題的「理財風險」判斷。</x:v>
+        <x:v>這項知識屬於「清法戰爭與建省」，無法支持本題的「理財風險」判斷。</x:v>
       </x:c>
       <x:c r="AF133" s="34" t="str">
         <x:v>金融資訊先向可信主管機關查證。</x:v>
@@ -13614,7 +13614,7 @@
         <x:v>取消所有管理與損壞責任</x:v>
       </x:c>
       <x:c r="L134" s="34" t="str">
-        <x:v>讓每個人停在任何地方</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="M134" s="34" t="str">
         <x:v>A</x:v>
@@ -13638,7 +13638,7 @@
         <x:v>焦點放錯了。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="T134" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="U134" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13656,10 +13656,10 @@
         <x:v>共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="Z134" s="34" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="AA134" s="34" t="str">
-        <x:v>規範與法律的形成及強制力不同</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="AB134" s="34" t="str">
         <x:v>A</x:v>
@@ -13668,10 +13668,10 @@
         <x:v>這是判斷「共享資源」時要使用的依據。共享提高利用率，但不代表沒有管理；維護、秩序與責任決定服務品質。</x:v>
       </x:c>
       <x:c r="AD134" s="34" t="str">
-        <x:v>這是「電力與生活」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
+        <x:v>這是「能源代價」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE134" s="34" t="str">
-        <x:v>這項知識屬於「規範與法律」，無法支持本題的「共享資源」判斷。</x:v>
+        <x:v>這項知識屬於「永續農業」，無法支持本題的「共享資源」判斷。</x:v>
       </x:c>
       <x:c r="AF134" s="34" t="str">
         <x:v>借用公物要按時歸還並回報損壞。</x:v>
@@ -13706,13 +13706,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J135" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="K135" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="L135" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>規範可調整，互助目的仍保留</x:v>
       </x:c>
       <x:c r="M135" s="34" t="str">
         <x:v>A</x:v>
@@ -13730,13 +13730,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是共享資源要比較的核心。</x:v>
       </x:c>
       <x:c r="R135" s="34" t="str">
-        <x:v>焦點放錯了。請回看：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="S135" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="T135" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「規範可調整，互助目的仍保留」是「規範變遷」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="U135" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13754,10 +13754,10 @@
         <x:v>共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="Z135" s="34" t="str">
-        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AA135" s="34" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AB135" s="34" t="str">
         <x:v>A</x:v>
@@ -13766,10 +13766,10 @@
         <x:v>這是判斷「共享資源」時要使用的依據。共享提高利用率，但不代表沒有管理；維護、秩序與責任決定服務品質。</x:v>
       </x:c>
       <x:c r="AD135" s="34" t="str">
-        <x:v>這是「地圖尺度」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
+        <x:v>這是「森林供應鏈」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE135" s="34" t="str">
-        <x:v>這項知識屬於「多元觀點」，無法支持本題的「共享資源」判斷。</x:v>
+        <x:v>這項知識屬於「開港背景」，無法支持本題的「共享資源」判斷。</x:v>
       </x:c>
       <x:c r="AF135" s="34" t="str">
         <x:v>借用公物要按時歸還並回報損壞。</x:v>
@@ -13804,13 +13804,13 @@
         <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="J136" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="K136" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="L136" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="M136" s="34" t="str">
         <x:v>A</x:v>
@@ -13828,13 +13828,13 @@
         <x:v>判斷精準。「訂規則、維修配置與歸還責任」直接回應共享資源，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R136" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="S136" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="T136" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：共享改變的是所有方式，不是取消責任。</x:v>
+        <x:v>「商品與港口帶動北部市鎮發展」是「經濟北移」的重點，但不能回答本題的「共享資源」。請回看：共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="U136" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13852,10 +13852,10 @@
         <x:v>共享改變的是所有方式，不是取消責任。</x:v>
       </x:c>
       <x:c r="Z136" s="34" t="str">
-        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="AA136" s="34" t="str">
-        <x:v>港市帶動文化，但各族群影響不同</x:v>
+        <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="AB136" s="34" t="str">
         <x:v>A</x:v>
@@ -13864,10 +13864,10 @@
         <x:v>這是判斷「共享資源」時要使用的依據。共享提高利用率，但不代表沒有管理；維護、秩序與責任決定服務品質。</x:v>
       </x:c>
       <x:c r="AD136" s="34" t="str">
-        <x:v>這是「永續漁業」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
+        <x:v>這是「多元資料」的重點；本題要判斷的是「共享資源」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE136" s="34" t="str">
-        <x:v>這項知識屬於「港市與文化」，無法支持本題的「共享資源」判斷。</x:v>
+        <x:v>這項知識屬於「多元觀點」，無法支持本題的「共享資源」判斷。</x:v>
       </x:c>
       <x:c r="AF136" s="34" t="str">
         <x:v>借用公物要按時歸還並回報損壞。</x:v>
@@ -13908,7 +13908,7 @@
         <x:v>把可用物品全部換新</x:v>
       </x:c>
       <x:c r="L137" s="34" t="str">
-        <x:v>只把包裝改綠色，生產不變</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="M137" s="34" t="str">
         <x:v>A</x:v>
@@ -13932,7 +13932,7 @@
         <x:v>這項推論缺少證據。請確認：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="T137" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：循環要從產品出生前開始。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="U137" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -13950,10 +13950,10 @@
         <x:v>循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="Z137" s="34" t="str">
-        <x:v>比較對象、程度、證據與改善方法</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="AA137" s="34" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="AB137" s="34" t="str">
         <x:v>A</x:v>
@@ -13962,10 +13962,10 @@
         <x:v>這是判斷「循環經濟」時要使用的依據。循環經濟從設計、生產、使用到回收讓資源持續運作，不只是末端分類垃圾。</x:v>
       </x:c>
       <x:c r="AD137" s="34" t="str">
-        <x:v>這是「分析權衡」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
+        <x:v>這是「位置與交流」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE137" s="34" t="str">
-        <x:v>這項知識屬於「地方轉型」，無法支持本題的「循環經濟」判斷。</x:v>
+        <x:v>這項知識屬於「時序空間」，無法支持本題的「循環經濟」判斷。</x:v>
       </x:c>
       <x:c r="AF137" s="34" t="str">
         <x:v>選購時考慮耐用、可修與回收。</x:v>
@@ -14000,13 +14000,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J138" s="34" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="K138" s="34" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="L138" s="34" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
       </x:c>
       <x:c r="M138" s="34" t="str">
         <x:v>A</x:v>
@@ -14024,13 +14024,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應循環經濟，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R138" s="34" t="str">
-        <x:v>這項推論缺少證據。請確認：循環要從產品出生前開始。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="S138" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：循環要從產品出生前開始。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="T138" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：循環要從產品出生前開始。</x:v>
+        <x:v>「南荷北西，後由鄭成功驅逐荷蘭」是「時序空間」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="U138" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -14048,10 +14048,10 @@
         <x:v>循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="Z138" s="34" t="str">
-        <x:v>規範可調整，互助目的仍保留</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AA138" s="34" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AB138" s="34" t="str">
         <x:v>A</x:v>
@@ -14060,10 +14060,10 @@
         <x:v>這是判斷「循環經濟」時要使用的依據。循環經濟從設計、生產、使用到回收讓資源持續運作，不只是末端分類垃圾。</x:v>
       </x:c>
       <x:c r="AD138" s="34" t="str">
-        <x:v>這是「規範變遷」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
+        <x:v>這是「問題形成」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE138" s="34" t="str">
-        <x:v>這項知識屬於「移民與季風」，無法支持本題的「循環經濟」判斷。</x:v>
+        <x:v>這項知識屬於「地理配對」，無法支持本題的「循環經濟」判斷。</x:v>
       </x:c>
       <x:c r="AF138" s="34" t="str">
         <x:v>選購時考慮耐用、可修與回收。</x:v>
@@ -14098,13 +14098,13 @@
         <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="J139" s="34" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="K139" s="34" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="L139" s="34" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="M139" s="34" t="str">
         <x:v>A</x:v>
@@ -14122,13 +14122,13 @@
         <x:v>這項選擇成立：設計耐用可修產品並回收再製。它抓住循環經濟的關鍵條件。</x:v>
       </x:c>
       <x:c r="R139" s="34" t="str">
-        <x:v>選項和題意關係較弱。提示：循環要從產品出生前開始。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="S139" s="34" t="str">
-        <x:v>這裡混淆了條件與結論。提示：循環要從產品出生前開始。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="T139" s="34" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：循環要從產品出生前開始。</x:v>
+        <x:v>「比較設置前後的發電、用電與環境」是「能源提問」的重點，但不能回答本題的「循環經濟」。請回看：循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="U139" s="34" t="str">
         <x:v>判斷正確</x:v>
@@ -14146,10 +14146,10 @@
         <x:v>循環要從產品出生前開始。</x:v>
       </x:c>
       <x:c r="Z139" s="34" t="str">
-        <x:v>貿易增加，也改變土地與族群關係</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="AA139" s="34" t="str">
-        <x:v>依能源補充性與環境特性分類</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="AB139" s="34" t="str">
         <x:v>A</x:v>
@@ -14158,10 +14158,10 @@
         <x:v>這是判斷「循環經濟」時要使用的依據。循環經濟從設計、生產、使用到回收讓資源持續運作，不只是末端分類垃圾。</x:v>
       </x:c>
       <x:c r="AD139" s="34" t="str">
-        <x:v>這是「貿易影響」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
+        <x:v>這是「族群衝突」的重點；本題要判斷的是「循環經濟」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE139" s="34" t="str">
-        <x:v>這項知識屬於「能源分類」，無法支持本題的「循環經濟」判斷。</x:v>
+        <x:v>這項知識屬於「海岸變遷」，無法支持本題的「循環經濟」判斷。</x:v>
       </x:c>
       <x:c r="AF139" s="34" t="str">
         <x:v>選購時考慮耐用、可修與回收。</x:v>
@@ -14202,7 +14202,7 @@
         <x:v>屋頂顏色哪個最可愛</x:v>
       </x:c>
       <x:c r="L140" s="35" t="str">
-        <x:v>誰最先看到施工車</x:v>
+        <x:v>比較雙方立場、目的與證據</x:v>
       </x:c>
       <x:c r="M140" s="35" t="str">
         <x:v>A</x:v>
@@ -14226,7 +14226,7 @@
         <x:v>選項和題意關係較弱。提示：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="T140" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：加入時間、指標與影響面向。</x:v>
+        <x:v>「比較雙方立場、目的與證據」是「多元觀點」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="U140" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14244,10 +14244,10 @@
         <x:v>加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="Z140" s="35" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AA140" s="35" t="str">
-        <x:v>設計耐用可修產品並回收再製</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AB140" s="35" t="str">
         <x:v>A</x:v>
@@ -14256,10 +14256,10 @@
         <x:v>這是判斷「能源提問」時要使用的依據。好問題要能以資料比較效益與影響，而不是先預設唯一答案或問無關細節。</x:v>
       </x:c>
       <x:c r="AD140" s="35" t="str">
-        <x:v>這是「遷移原因」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
+        <x:v>這是「開港背景」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE140" s="35" t="str">
-        <x:v>這項知識屬於「循環經濟」，無法支持本題的「能源提問」判斷。</x:v>
+        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「能源提問」判斷。</x:v>
       </x:c>
       <x:c r="AF140" s="35" t="str">
         <x:v>從校園現象提出可測量問題。</x:v>
@@ -14294,13 +14294,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J141" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>保存證據，再循正式管道申訴</x:v>
       </x:c>
       <x:c r="K141" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>查合法性，不投入無法承受的資金</x:v>
       </x:c>
       <x:c r="L141" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="M141" s="35" t="str">
         <x:v>A</x:v>
@@ -14318,13 +14318,13 @@
         <x:v>這項選擇成立：和題目直接有關的資料。它抓住能源提問的關鍵條件。</x:v>
       </x:c>
       <x:c r="R141" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：加入時間、指標與影響面向。</x:v>
+        <x:v>「保存證據，再循正式管道申訴」是「消費權益」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="S141" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：加入時間、指標與影響面向。</x:v>
+        <x:v>「查合法性，不投入無法承受的資金」是「理財風險」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="T141" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：加入時間、指標與影響面向。</x:v>
+        <x:v>「訂規則、維修配置與歸還責任」是「共享資源」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="U141" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14342,10 +14342,10 @@
         <x:v>加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="Z141" s="35" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AA141" s="35" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AB141" s="35" t="str">
         <x:v>A</x:v>
@@ -14354,10 +14354,10 @@
         <x:v>這是判斷「能源提問」時要使用的依據。好問題要能以資料比較效益與影響，而不是先預設唯一答案或問無關細節。</x:v>
       </x:c>
       <x:c r="AD141" s="35" t="str">
-        <x:v>這是「能源代價」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
+        <x:v>這是「板塊與地形」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE141" s="35" t="str">
-        <x:v>這項知識屬於「永續農業」，無法支持本題的「能源提問」判斷。</x:v>
+        <x:v>這項知識屬於「貿易影響」，無法支持本題的「能源提問」判斷。</x:v>
       </x:c>
       <x:c r="AF141" s="35" t="str">
         <x:v>從校園現象提出可測量問題。</x:v>
@@ -14392,13 +14392,13 @@
         <x:v>比較設置前後的發電、用電與環境</x:v>
       </x:c>
       <x:c r="J142" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="K142" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="L142" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>結合檔案、觀察與多方訪談</x:v>
       </x:c>
       <x:c r="M142" s="35" t="str">
         <x:v>A</x:v>
@@ -14416,13 +14416,13 @@
         <x:v>證據吻合。選項「比較設置前後的發電、用電與環境」能把能源提問的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R142" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：加入時間、指標與影響面向。</x:v>
+        <x:v>「貿易增加，也改變土地與族群關係」是「貿易影響」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="S142" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：加入時間、指標與影響面向。</x:v>
+        <x:v>「聚焦特定海岸、時間與不同觀點」是「問題形成」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="T142" s="35" t="str">
-        <x:v>焦點放錯了。請回看：加入時間、指標與影響面向。</x:v>
+        <x:v>「結合檔案、觀察與多方訪談」是「多元資料」的重點，但不能回答本題的「能源提問」。請回看：加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="U142" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14440,10 +14440,10 @@
         <x:v>加入時間、指標與影響面向。</x:v>
       </x:c>
       <x:c r="Z142" s="35" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>查明進口木材是否來自永續來源</x:v>
       </x:c>
       <x:c r="AA142" s="35" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="AB142" s="35" t="str">
         <x:v>A</x:v>
@@ -14452,10 +14452,10 @@
         <x:v>這是判斷「能源提問」時要使用的依據。好問題要能以資料比較效益與影響，而不是先預設唯一答案或問無關細節。</x:v>
       </x:c>
       <x:c r="AD142" s="35" t="str">
-        <x:v>這是「史前證據」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
+        <x:v>這是「森林供應鏈」的重點；本題要判斷的是「能源提問」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE142" s="35" t="str">
-        <x:v>這項知識屬於「多元資料」，無法支持本題的「能源提問」判斷。</x:v>
+        <x:v>這項知識屬於「牡丹社事件」，無法支持本題的「能源提問」判斷。</x:v>
       </x:c>
       <x:c r="AF142" s="35" t="str">
         <x:v>從校園現象提出可測量問題。</x:v>
@@ -14496,7 +14496,7 @@
         <x:v>只看業者廣告</x:v>
       </x:c>
       <x:c r="L143" s="35" t="str">
-        <x:v>先把反對意見全部排除</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="M143" s="35" t="str">
         <x:v>A</x:v>
@@ -14520,7 +14520,7 @@
         <x:v>這裡混淆了條件與結論。提示：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="T143" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「生活、機會與政策共同影響移動」是「遷移原因」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="U143" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14538,10 +14538,10 @@
         <x:v>納入受到影響的人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="Z143" s="35" t="str">
-        <x:v>海防受重視，建省與建設強化治理</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AA143" s="35" t="str">
-        <x:v>環境、季節與歷史共同影響生活</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="AB143" s="35" t="str">
         <x:v>A</x:v>
@@ -14550,10 +14550,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。多元觀點需配合共同可查的資料，也要注意不同角色受到的影響程度。</x:v>
       </x:c>
       <x:c r="AD143" s="35" t="str">
-        <x:v>這是「清法戰爭與建省」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「地理配對」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE143" s="35" t="str">
-        <x:v>這項知識屬於「環境與生活」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「權利權衡」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF143" s="35" t="str">
         <x:v>訪談樣本要標記角色與受影響程度。</x:v>
@@ -14588,13 +14588,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J144" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="K144" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>環境、季節與歷史共同影響生活</x:v>
       </x:c>
       <x:c r="L144" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="M144" s="35" t="str">
         <x:v>A</x:v>
@@ -14612,13 +14612,13 @@
         <x:v>證據吻合。選項「和題目直接有關的資料」能把多元觀點的線索合理連起來。</x:v>
       </x:c>
       <x:c r="R144" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「分族查資料，再比較文化異同」是「文化多樣性」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="S144" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「環境、季節與歷史共同影響生活」是「環境與生活」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="T144" s="35" t="str">
-        <x:v>焦點放錯了。請回看：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「規範與法律的形成及強制力不同」是「規範與法律」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="U144" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14636,10 +14636,10 @@
         <x:v>納入受到影響的人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="Z144" s="35" t="str">
-        <x:v>臺灣是遷徙與交流的中繼點</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AA144" s="35" t="str">
-        <x:v>南荷北西，後由鄭成功驅逐荷蘭</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="AB144" s="35" t="str">
         <x:v>A</x:v>
@@ -14648,10 +14648,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。多元觀點需配合共同可查的資料，也要注意不同角色受到的影響程度。</x:v>
       </x:c>
       <x:c r="AD144" s="35" t="str">
-        <x:v>這是「位置與交流」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「永續漁業」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE144" s="35" t="str">
-        <x:v>這項知識屬於「時序空間」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「港市與文化」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF144" s="35" t="str">
         <x:v>訪談樣本要標記角色與受影響程度。</x:v>
@@ -14686,13 +14686,13 @@
         <x:v>訪談多方並搭配噪音與發電資料</x:v>
       </x:c>
       <x:c r="J145" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>分析資源、語言、組織與治理</x:v>
       </x:c>
       <x:c r="K145" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>港市帶動文化，但各族群影響不同</x:v>
       </x:c>
       <x:c r="L145" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="M145" s="35" t="str">
         <x:v>A</x:v>
@@ -14710,13 +14710,13 @@
         <x:v>答對了；「訪談多方並搭配噪音與發電資料」同時保留了多元觀點需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R145" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「分析資源、語言、組織與治理」是「族群衝突」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="S145" s="35" t="str">
-        <x:v>焦點放錯了。請回看：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「港市帶動文化，但各族群影響不同」是「港市與文化」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="T145" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：納入利害關係人，也使用客觀指標。</x:v>
+        <x:v>「通商壓力、物產與航路共同促成開港」是「開港背景」的重點，但不能回答本題的「多元觀點」。請回看：納入利害關係人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="U145" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14734,10 +14734,10 @@
         <x:v>納入受到影響的人，也使用客觀指標。</x:v>
       </x:c>
       <x:c r="Z145" s="35" t="str">
-        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
+        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
       </x:c>
       <x:c r="AA145" s="35" t="str">
-        <x:v>分析資源、語言、組織與治理</x:v>
+        <x:v>停止交易並改用官方查證與付款</x:v>
       </x:c>
       <x:c r="AB145" s="35" t="str">
         <x:v>A</x:v>
@@ -14746,10 +14746,10 @@
         <x:v>這是判斷「多元觀點」時要使用的依據。多元觀點需配合共同可查的資料，也要注意不同角色受到的影響程度。</x:v>
       </x:c>
       <x:c r="AD145" s="35" t="str">
-        <x:v>這是「畜牧權衡」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
+        <x:v>這是「問題形成」的重點；本題要判斷的是「多元觀點」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE145" s="35" t="str">
-        <x:v>這項知識屬於「族群衝突」，無法支持本題的「多元觀點」判斷。</x:v>
+        <x:v>這項知識屬於「消費安全」，無法支持本題的「多元觀點」判斷。</x:v>
       </x:c>
       <x:c r="AF145" s="35" t="str">
         <x:v>訪談樣本要標記角色與受影響程度。</x:v>
@@ -14790,7 +14790,7 @@
         <x:v>刪掉缺點欄才能推動綠能</x:v>
       </x:c>
       <x:c r="L146" s="35" t="str">
-        <x:v>只數優點和缺點各有幾項</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="M146" s="35" t="str">
         <x:v>A</x:v>
@@ -14814,7 +14814,7 @@
         <x:v>這項判斷忽略重要限制。請想想：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="T146" s="35" t="str">
-        <x:v>焦點放錯了。請回看：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「依能源補充性與環境特性分類」是「能源分類」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="U146" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14832,10 +14832,10 @@
         <x:v>追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="Z146" s="35" t="str">
-        <x:v>保存證據，再循正式管道申訴</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AA146" s="35" t="str">
-        <x:v>查明進口木材是否來自永續來源</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="AB146" s="35" t="str">
         <x:v>A</x:v>
@@ -14844,10 +14844,10 @@
         <x:v>這是判斷「分析權衡」時要使用的依據。優缺點數量不等於重要性，還需判斷影響多大、落在誰身上與能否降低。</x:v>
       </x:c>
       <x:c r="AD146" s="35" t="str">
-        <x:v>這是「消費權益」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「循環經濟」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE146" s="35" t="str">
-        <x:v>這項知識屬於「森林供應鏈」，無法支持本題的「分析權衡」判斷。</x:v>
+        <x:v>這項知識屬於「航海動機」，無法支持本題的「分析權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF146" s="35" t="str">
         <x:v>比較方案時加入指標與權重。</x:v>
@@ -14882,13 +14882,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J147" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="K147" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>泥沙堆積使船難進出，港口轉移</x:v>
       </x:c>
       <x:c r="L147" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>臺灣鄰近航路，利於貿易競爭</x:v>
       </x:c>
       <x:c r="M147" s="35" t="str">
         <x:v>A</x:v>
@@ -14906,13 +14906,13 @@
         <x:v>答對了；「和題目直接有關的資料」同時保留了分析權衡需要的範圍與限制。</x:v>
       </x:c>
       <x:c r="R147" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「長期追蹤保存、參與、就業與環境」是「地方轉型」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="S147" s="35" t="str">
-        <x:v>焦點放錯了。請回看：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「泥沙堆積使船難進出，港口轉移」是「潟湖與港口」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="T147" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「臺灣鄰近航路，利於貿易競爭」是「航海動機」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="U147" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -14930,10 +14930,10 @@
         <x:v>追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="Z147" s="35" t="str">
-        <x:v>規範與法律的形成及強制力不同</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AA147" s="35" t="str">
-        <x:v>查紀錄、調方法，再用同指標測量</x:v>
+        <x:v>依能源補充性與環境特性分類</x:v>
       </x:c>
       <x:c r="AB147" s="35" t="str">
         <x:v>A</x:v>
@@ -14942,10 +14942,10 @@
         <x:v>這是判斷「分析權衡」時要使用的依據。優缺點數量不等於重要性，還需判斷影響多大、落在誰身上與能否降低。</x:v>
       </x:c>
       <x:c r="AD147" s="35" t="str">
-        <x:v>這是「規範與法律」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「貿易影響」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE147" s="35" t="str">
-        <x:v>這項知識屬於「行動省思」，無法支持本題的「分析權衡」判斷。</x:v>
+        <x:v>這項知識屬於「能源分類」，無法支持本題的「分析權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF147" s="35" t="str">
         <x:v>比較方案時加入指標與權重。</x:v>
@@ -14980,13 +14980,13 @@
         <x:v>比較對象、程度、證據與改善方法</x:v>
       </x:c>
       <x:c r="J148" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="K148" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>用共同指標比較各能源的代價</x:v>
       </x:c>
       <x:c r="L148" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>風險分配與居民參與需要公平</x:v>
       </x:c>
       <x:c r="M148" s="35" t="str">
         <x:v>A</x:v>
@@ -15004,13 +15004,13 @@
         <x:v>你的判讀可被查證：比較對象、程度、證據與改善方法。這正是分析權衡要比較的核心。</x:v>
       </x:c>
       <x:c r="R148" s="35" t="str">
-        <x:v>焦點放錯了。請回看：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「依地理條件發展能源並評估影響」是「地理配對」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="S148" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「用共同指標比較各能源的代價」是「能源代價」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="T148" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：追問多大、對誰、多久、如何改善。</x:v>
+        <x:v>「風險分配與居民參與需要公平」是「環境正義」的重點，但不能回答本題的「分析權衡」。請回看：追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="U148" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15028,10 +15028,10 @@
         <x:v>追問多大、對誰、多久、如何改善。</x:v>
       </x:c>
       <x:c r="Z148" s="35" t="str">
-        <x:v>比較雙方立場、目的與證據</x:v>
+        <x:v>生活、機會與政策共同影響移動</x:v>
       </x:c>
       <x:c r="AA148" s="35" t="str">
-        <x:v>電力帶來便利，也增加供電依賴</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="AB148" s="35" t="str">
         <x:v>A</x:v>
@@ -15040,10 +15040,10 @@
         <x:v>這是判斷「分析權衡」時要使用的依據。優缺點數量不等於重要性，還需判斷影響多大、落在誰身上與能否降低。</x:v>
       </x:c>
       <x:c r="AD148" s="35" t="str">
-        <x:v>這是「多元觀點」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
+        <x:v>這是「遷移原因」的重點；本題要判斷的是「分析權衡」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE148" s="35" t="str">
-        <x:v>這項知識屬於「電力與生活」，無法支持本題的「分析權衡」判斷。</x:v>
+        <x:v>這項知識屬於「板塊與地形」，無法支持本題的「分析權衡」判斷。</x:v>
       </x:c>
       <x:c r="AF148" s="35" t="str">
         <x:v>比較方案時加入指標與權重。</x:v>
@@ -15084,7 +15084,7 @@
         <x:v>投票後刪除少數意見</x:v>
       </x:c>
       <x:c r="L149" s="35" t="str">
-        <x:v>為避免衝突而不談差異</x:v>
+        <x:v>臺灣是遷徙與交流的中繼點</x:v>
       </x:c>
       <x:c r="M149" s="35" t="str">
         <x:v>A</x:v>
@@ -15108,7 +15108,7 @@
         <x:v>焦點放錯了。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="T149" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：先找共同目標，再處理分歧。</x:v>
+        <x:v>「臺灣是遷徙與交流的中繼點」是「位置與交流」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="U149" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15126,10 +15126,10 @@
         <x:v>先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="Z149" s="35" t="str">
-        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
+        <x:v>規範與法律的形成及強制力不同</x:v>
       </x:c>
       <x:c r="AA149" s="35" t="str">
-        <x:v>聚焦特定海岸、時間與不同觀點</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="AB149" s="35" t="str">
         <x:v>A</x:v>
@@ -15138,10 +15138,10 @@
         <x:v>這是判斷「共識與程序」時要使用的依據。共識不是消除不同，而是在透明標準下找可接受方案並保留檢討空間。</x:v>
       </x:c>
       <x:c r="AD149" s="35" t="str">
-        <x:v>這是「海岸變遷」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
+        <x:v>這是「規範與法律」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE149" s="35" t="str">
-        <x:v>這項知識屬於「問題形成」，無法支持本題的「共識與程序」判斷。</x:v>
+        <x:v>這項知識屬於「行動省思」，無法支持本題的「共識與程序」判斷。</x:v>
       </x:c>
       <x:c r="AF149" s="35" t="str">
         <x:v>班級決策要記錄少數意見和檢討時間。</x:v>
@@ -15176,13 +15176,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J150" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>限定結論範圍並說明調查限制</x:v>
       </x:c>
       <x:c r="K150" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>查紀錄、調方法，再用同指標測量</x:v>
       </x:c>
       <x:c r="L150" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>季風影響航程與風險，但不保證安全</x:v>
       </x:c>
       <x:c r="M150" s="35" t="str">
         <x:v>A</x:v>
@@ -15200,13 +15200,13 @@
         <x:v>你的判讀可被查證：和題目直接有關的資料。這正是共識與程序要比較的核心。</x:v>
       </x:c>
       <x:c r="R150" s="35" t="str">
-        <x:v>焦點放錯了。請回看：先找共同目標，再處理分歧。</x:v>
+        <x:v>「限定結論範圍並說明調查限制」是「結論界線」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="S150" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：先找共同目標，再處理分歧。</x:v>
+        <x:v>「查紀錄、調方法，再用同指標測量」是「行動省思」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="T150" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：先找共同目標，再處理分歧。</x:v>
+        <x:v>「季風影響航程與風險，但不保證安全」是「移民與季風」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="U150" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15224,10 +15224,10 @@
         <x:v>先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="Z150" s="35" t="str">
-        <x:v>長期追蹤保存、參與、就業與環境</x:v>
+        <x:v>合作修水圳，訂分水與維修規則</x:v>
       </x:c>
       <x:c r="AA150" s="35" t="str">
-        <x:v>商品與港口帶動北部市鎮發展</x:v>
+        <x:v>訂規則、維修配置與歸還責任</x:v>
       </x:c>
       <x:c r="AB150" s="35" t="str">
         <x:v>A</x:v>
@@ -15236,10 +15236,10 @@
         <x:v>這是判斷「共識與程序」時要使用的依據。共識不是消除不同，而是在透明標準下找可接受方案並保留檢討空間。</x:v>
       </x:c>
       <x:c r="AD150" s="35" t="str">
-        <x:v>這是「地方轉型」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
+        <x:v>這是「水利開墾」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE150" s="35" t="str">
-        <x:v>這項知識屬於「經濟北移」，無法支持本題的「共識與程序」判斷。</x:v>
+        <x:v>這項知識屬於「共享資源」，無法支持本題的「共識與程序」判斷。</x:v>
       </x:c>
       <x:c r="AF150" s="35" t="str">
         <x:v>班級決策要記錄少數意見和檢討時間。</x:v>
@@ -15274,13 +15274,13 @@
         <x:v>用共同目標與相同標準調整方案</x:v>
       </x:c>
       <x:c r="J151" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>選能看見臺灣、鄰國與航線的區域圖</x:v>
       </x:c>
       <x:c r="K151" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>板塊交界造成多山與地震</x:v>
       </x:c>
       <x:c r="L151" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>比較地形、風浪、泥沙與停靠條件</x:v>
       </x:c>
       <x:c r="M151" s="35" t="str">
         <x:v>A</x:v>
@@ -15298,13 +15298,13 @@
         <x:v>判斷精準。「用共同目標與相同標準調整方案」直接回應共識與程序，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R151" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：先找共同目標，再處理分歧。</x:v>
+        <x:v>「選能看見臺灣、鄰國與航線的區域圖」是「地圖尺度」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="S151" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：先找共同目標，再處理分歧。</x:v>
+        <x:v>「板塊交界造成多山與地震」是「板塊與地形」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="T151" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：先找共同目標，再處理分歧。</x:v>
+        <x:v>「比較地形、風浪、泥沙與停靠條件」是「海岸變遷」的重點，但不能回答本題的「共識與程序」。請回看：先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="U151" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15322,10 +15322,10 @@
         <x:v>先找共同目標，再處理分歧。</x:v>
       </x:c>
       <x:c r="Z151" s="35" t="str">
-        <x:v>季風影響航程與風險，但不保證安全</x:v>
+        <x:v>依地理條件發展能源並評估影響</x:v>
       </x:c>
       <x:c r="AA151" s="35" t="str">
-        <x:v>查合法性，不投入無法承受的資金</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="AB151" s="35" t="str">
         <x:v>A</x:v>
@@ -15334,10 +15334,10 @@
         <x:v>這是判斷「共識與程序」時要使用的依據。共識不是消除不同，而是在透明標準下找可接受方案並保留檢討空間。</x:v>
       </x:c>
       <x:c r="AD151" s="35" t="str">
-        <x:v>這是「移民與季風」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
+        <x:v>這是「地理配對」的重點；本題要判斷的是「共識與程序」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE151" s="35" t="str">
-        <x:v>這項知識屬於「理財風險」，無法支持本題的「共識與程序」判斷。</x:v>
+        <x:v>這項知識屬於「永續漁業」，無法支持本題的「共識與程序」判斷。</x:v>
       </x:c>
       <x:c r="AF151" s="35" t="str">
         <x:v>班級決策要記錄少數意見和檢討時間。</x:v>
@@ -15378,7 +15378,7 @@
         <x:v>沒有基準值便說節省很多</x:v>
       </x:c>
       <x:c r="L152" s="35" t="str">
-        <x:v>只要求學生忍耐，不檢查設備</x:v>
+        <x:v>相關各方應依資料協商文化與保育</x:v>
       </x:c>
       <x:c r="M152" s="35" t="str">
         <x:v>A</x:v>
@@ -15402,7 +15402,7 @@
         <x:v>這項推論缺少證據。請確認：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="T152" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「相關各方應依資料協商文化與保育」是「權利權衡」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="U152" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15420,10 +15420,10 @@
         <x:v>寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="Z152" s="35" t="str">
-        <x:v>保留植被並依坡度調整耕作</x:v>
+        <x:v>長期追蹤保存、參與、就業與環境</x:v>
       </x:c>
       <x:c r="AA152" s="35" t="str">
-        <x:v>生活、機會與政策共同影響移動</x:v>
+        <x:v>商品與港口帶動北部市鎮發展</x:v>
       </x:c>
       <x:c r="AB152" s="35" t="str">
         <x:v>A</x:v>
@@ -15432,10 +15432,10 @@
         <x:v>這是判斷「行動評估」時要使用的依據。可評估行動需有基準、措施、時間和相同指標，才能判斷是否真的改善。</x:v>
       </x:c>
       <x:c r="AD152" s="35" t="str">
-        <x:v>這是「永續農業」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
+        <x:v>這是「地方轉型」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE152" s="35" t="str">
-        <x:v>這項知識屬於「遷移原因」，無法支持本題的「行動評估」判斷。</x:v>
+        <x:v>這項知識屬於「經濟北移」，無法支持本題的「行動評估」判斷。</x:v>
       </x:c>
       <x:c r="AF152" s="35" t="str">
         <x:v>讓各班追蹤一項設備的用電變化。</x:v>
@@ -15470,13 +15470,13 @@
         <x:v>和題目直接有關的資料</x:v>
       </x:c>
       <x:c r="J153" s="35" t="str">
-        <x:v>只找支持自己的說法</x:v>
+        <x:v>比較具體貢獻、限制與在地回應</x:v>
       </x:c>
       <x:c r="K153" s="35" t="str">
-        <x:v>沒有時間地點的數字</x:v>
+        <x:v>外力暴露治理不足，促使政策改變</x:v>
       </x:c>
       <x:c r="L153" s="35" t="str">
-        <x:v>和問題無關的照片</x:v>
+        <x:v>海防受重視，建省與建設強化治理</x:v>
       </x:c>
       <x:c r="M153" s="35" t="str">
         <x:v>A</x:v>
@@ -15494,13 +15494,13 @@
         <x:v>判斷精準。「和題目直接有關的資料」直接回應行動評估，推論沒有超過資料。</x:v>
       </x:c>
       <x:c r="R153" s="35" t="str">
-        <x:v>這項推論缺少證據。請確認：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「比較具體貢獻、限制與在地回應」是「人物與交流」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="S153" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「外力暴露治理不足，促使政策改變」是「牡丹社事件」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="T153" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「海防受重視，建省與建設強化治理」是「清法戰爭與建省」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="U153" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15518,10 +15518,10 @@
         <x:v>寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="Z153" s="35" t="str">
-        <x:v>結合檔案、觀察與多方訪談</x:v>
+        <x:v>通商壓力、物產與航路共同促成開港</x:v>
       </x:c>
       <x:c r="AA153" s="35" t="str">
-        <x:v>用共同指標比較各能源的代價</x:v>
+        <x:v>分族查資料，再比較文化異同</x:v>
       </x:c>
       <x:c r="AB153" s="35" t="str">
         <x:v>A</x:v>
@@ -15530,10 +15530,10 @@
         <x:v>這是判斷「行動評估」時要使用的依據。可評估行動需有基準、措施、時間和相同指標，才能判斷是否真的改善。</x:v>
       </x:c>
       <x:c r="AD153" s="35" t="str">
-        <x:v>這是「多元資料」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
+        <x:v>這是「開港背景」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE153" s="35" t="str">
-        <x:v>這項知識屬於「能源代價」，無法支持本題的「行動評估」判斷。</x:v>
+        <x:v>這項知識屬於「文化多樣性」，無法支持本題的「行動評估」判斷。</x:v>
       </x:c>
       <x:c r="AF153" s="35" t="str">
         <x:v>讓各班追蹤一項設備的用電變化。</x:v>
@@ -15568,13 +15568,13 @@
         <x:v>設基準與措施，四週後同指標比較</x:v>
       </x:c>
       <x:c r="J154" s="35" t="str">
-        <x:v>不用查資料，照原來的說法</x:v>
+        <x:v>保留植被並依坡度調整耕作</x:v>
       </x:c>
       <x:c r="K154" s="35" t="str">
-        <x:v>刪掉不同意見後才下結論</x:v>
+        <x:v>比較供應、動物、傳染病與廢水管理</x:v>
       </x:c>
       <x:c r="L154" s="35" t="str">
-        <x:v>選文字最少的說法當答案</x:v>
+        <x:v>設禁漁期、尺寸限制並協助轉型</x:v>
       </x:c>
       <x:c r="M154" s="35" t="str">
         <x:v>A</x:v>
@@ -15592,13 +15592,13 @@
         <x:v>這項選擇成立：設基準與措施，四週後同指標比較。它抓住行動評估的關鍵條件。</x:v>
       </x:c>
       <x:c r="R154" s="35" t="str">
-        <x:v>選項和題意關係較弱。提示：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「保留植被並依坡度調整耕作」是「永續農業」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="S154" s="35" t="str">
-        <x:v>這裡混淆了條件與結論。提示：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「比較供應、動物、傳染病與廢水管理」是「畜牧權衡」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="T154" s="35" t="str">
-        <x:v>這項判斷忽略重要限制。請想想：寫清楚改什麼、誰執行、何時再量。</x:v>
+        <x:v>「設禁漁期、尺寸限制並協助轉型」是「永續漁業」的重點，但不能回答本題的「行動評估」。請回看：寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="U154" s="35" t="str">
         <x:v>判斷正確</x:v>
@@ -15616,10 +15616,10 @@
         <x:v>寫清楚改什麼、誰執行、何時再量。</x:v>
       </x:c>
       <x:c r="Z154" s="35" t="str">
-        <x:v>比較具體貢獻、限制與在地回應</x:v>
+        <x:v>設計耐用可修產品並回收再製</x:v>
       </x:c>
       <x:c r="AA154" s="35" t="str">
-        <x:v>遺物顯示可能已有農耕定居生活</x:v>
+        <x:v>貿易增加，也改變土地與族群關係</x:v>
       </x:c>
       <x:c r="AB154" s="35" t="str">
         <x:v>A</x:v>
@@ -15628,10 +15628,10 @@
         <x:v>這是判斷「行動評估」時要使用的依據。可評估行動需有基準、措施、時間和相同指標，才能判斷是否真的改善。</x:v>
       </x:c>
       <x:c r="AD154" s="35" t="str">
-        <x:v>這是「人物與交流」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
+        <x:v>這是「循環經濟」的重點；本題要判斷的是「行動評估」，兩者不能互相代替。</x:v>
       </x:c>
       <x:c r="AE154" s="35" t="str">
-        <x:v>這項知識屬於「史前證據」，無法支持本題的「行動評估」判斷。</x:v>
+        <x:v>這項知識屬於「貿易影響」，無法支持本題的「行動評估」判斷。</x:v>
       </x:c>
       <x:c r="AF154" s="35" t="str">
         <x:v>讓各班追蹤一項設備的用電變化。</x:v>
